--- a/veri.xlsx
+++ b/veri.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12060"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8820"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sayfa1!$A$1:$G$201</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sayfa1!$A$1:$G$204</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="129">
   <si>
     <t>Sıra No</t>
   </si>
@@ -348,9 +348,6 @@
     <t xml:space="preserve">IBR PCR </t>
   </si>
   <si>
-    <t>Sat</t>
-  </si>
-  <si>
     <t>Enes Fatih Biçer</t>
   </si>
   <si>
@@ -376,6 +373,42 @@
   </si>
   <si>
     <t xml:space="preserve">BVDV Ab </t>
+  </si>
+  <si>
+    <t>Bahar Özer Adsız</t>
+  </si>
+  <si>
+    <t>Total Aflatoksin</t>
+  </si>
+  <si>
+    <t>Yusuf Arslan</t>
+  </si>
+  <si>
+    <t>Actimoo (Akbulut)</t>
+  </si>
+  <si>
+    <t>Mustafa Ertürk</t>
+  </si>
+  <si>
+    <t>Clostridium perfringens PCR</t>
+  </si>
+  <si>
+    <t>Emre Can Topuz</t>
+  </si>
+  <si>
+    <t>Karacabey TİGEM</t>
+  </si>
+  <si>
+    <t>Bluetongue Ab</t>
+  </si>
+  <si>
+    <t>BVDV Total Ab</t>
+  </si>
+  <si>
+    <t>Mycoplasma Bovis Ab</t>
+  </si>
+  <si>
+    <t>Bedelsiz yapıldı</t>
   </si>
 </sst>
 </file>
@@ -478,7 +511,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -527,10 +560,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -541,9 +574,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -560,6 +590,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -840,7 +875,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G610"/>
+  <dimension ref="A1:G616"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="10" customWidth="1"/>
@@ -866,7 +901,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>4</v>
@@ -905,12 +940,12 @@
       <c r="C3" s="8">
         <v>46027</v>
       </c>
-      <c r="D3" s="22"/>
+      <c r="D3" s="23"/>
       <c r="E3" s="4">
         <v>37</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -923,7 +958,7 @@
       <c r="C4" s="8">
         <v>46027</v>
       </c>
-      <c r="D4" s="22"/>
+      <c r="D4" s="23"/>
       <c r="E4" s="4">
         <v>37</v>
       </c>
@@ -941,7 +976,7 @@
       <c r="C5" s="8">
         <v>46027</v>
       </c>
-      <c r="D5" s="22"/>
+      <c r="D5" s="23"/>
       <c r="E5" s="4">
         <v>37</v>
       </c>
@@ -959,7 +994,7 @@
       <c r="C6" s="8">
         <v>46027</v>
       </c>
-      <c r="D6" s="23"/>
+      <c r="D6" s="22"/>
       <c r="E6" s="4">
         <v>37</v>
       </c>
@@ -997,7 +1032,7 @@
       <c r="C8" s="8">
         <v>46029</v>
       </c>
-      <c r="D8" s="22"/>
+      <c r="D8" s="23"/>
       <c r="E8" s="4">
         <v>1</v>
       </c>
@@ -1015,7 +1050,7 @@
       <c r="C9" s="8">
         <v>46029</v>
       </c>
-      <c r="D9" s="22"/>
+      <c r="D9" s="23"/>
       <c r="E9" s="4">
         <v>1</v>
       </c>
@@ -1033,7 +1068,7 @@
       <c r="C10" s="8">
         <v>46029</v>
       </c>
-      <c r="D10" s="22"/>
+      <c r="D10" s="23"/>
       <c r="E10" s="4">
         <v>1</v>
       </c>
@@ -1051,7 +1086,7 @@
       <c r="C11" s="8">
         <v>46029</v>
       </c>
-      <c r="D11" s="23"/>
+      <c r="D11" s="22"/>
       <c r="E11" s="4">
         <v>1</v>
       </c>
@@ -1089,7 +1124,7 @@
       <c r="C13" s="8">
         <v>46030</v>
       </c>
-      <c r="D13" s="23"/>
+      <c r="D13" s="22"/>
       <c r="E13" s="4">
         <v>2</v>
       </c>
@@ -1147,7 +1182,7 @@
       <c r="C16" s="8">
         <v>46031</v>
       </c>
-      <c r="D16" s="22"/>
+      <c r="D16" s="23"/>
       <c r="E16" s="4">
         <v>21</v>
       </c>
@@ -1165,7 +1200,7 @@
       <c r="C17" s="8">
         <v>46031</v>
       </c>
-      <c r="D17" s="22"/>
+      <c r="D17" s="23"/>
       <c r="E17" s="4">
         <v>21</v>
       </c>
@@ -1183,7 +1218,7 @@
       <c r="C18" s="8">
         <v>46031</v>
       </c>
-      <c r="D18" s="22"/>
+      <c r="D18" s="23"/>
       <c r="E18" s="4">
         <v>21</v>
       </c>
@@ -1201,7 +1236,7 @@
       <c r="C19" s="8">
         <v>46031</v>
       </c>
-      <c r="D19" s="23"/>
+      <c r="D19" s="22"/>
       <c r="E19" s="4">
         <v>1</v>
       </c>
@@ -1239,7 +1274,7 @@
       <c r="C21" s="8">
         <v>46031</v>
       </c>
-      <c r="D21" s="22"/>
+      <c r="D21" s="23"/>
       <c r="E21" s="4">
         <v>1</v>
       </c>
@@ -1257,7 +1292,7 @@
       <c r="C22" s="8">
         <v>46031</v>
       </c>
-      <c r="D22" s="22"/>
+      <c r="D22" s="23"/>
       <c r="E22" s="4">
         <v>1</v>
       </c>
@@ -1275,7 +1310,7 @@
       <c r="C23" s="8">
         <v>46031</v>
       </c>
-      <c r="D23" s="23"/>
+      <c r="D23" s="22"/>
       <c r="E23" s="4">
         <v>1</v>
       </c>
@@ -1451,7 +1486,7 @@
       <c r="C32" s="8">
         <v>46035</v>
       </c>
-      <c r="D32" s="22"/>
+      <c r="D32" s="23"/>
       <c r="E32" s="4">
         <v>1789</v>
       </c>
@@ -1469,7 +1504,7 @@
       <c r="C33" s="8">
         <v>46035</v>
       </c>
-      <c r="D33" s="23"/>
+      <c r="D33" s="22"/>
       <c r="E33" s="4">
         <v>1789</v>
       </c>
@@ -1547,7 +1582,7 @@
       <c r="C37" s="8">
         <v>46042</v>
       </c>
-      <c r="D37" s="22"/>
+      <c r="D37" s="23"/>
       <c r="E37" s="4">
         <v>1</v>
       </c>
@@ -1565,7 +1600,7 @@
       <c r="C38" s="8">
         <v>46042</v>
       </c>
-      <c r="D38" s="22"/>
+      <c r="D38" s="23"/>
       <c r="E38" s="4">
         <v>1</v>
       </c>
@@ -1583,7 +1618,7 @@
       <c r="C39" s="8">
         <v>46042</v>
       </c>
-      <c r="D39" s="22"/>
+      <c r="D39" s="23"/>
       <c r="E39" s="4">
         <v>1</v>
       </c>
@@ -1601,7 +1636,7 @@
       <c r="C40" s="8">
         <v>46042</v>
       </c>
-      <c r="D40" s="22"/>
+      <c r="D40" s="23"/>
       <c r="E40" s="4">
         <v>7</v>
       </c>
@@ -1619,7 +1654,7 @@
       <c r="C41" s="8">
         <v>46042</v>
       </c>
-      <c r="D41" s="23"/>
+      <c r="D41" s="22"/>
       <c r="E41" s="4">
         <v>2</v>
       </c>
@@ -1697,7 +1732,7 @@
       <c r="C45" s="8">
         <v>46042</v>
       </c>
-      <c r="D45" s="22"/>
+      <c r="D45" s="23"/>
       <c r="E45" s="4">
         <v>2</v>
       </c>
@@ -1715,7 +1750,7 @@
       <c r="C46" s="8">
         <v>46042</v>
       </c>
-      <c r="D46" s="22"/>
+      <c r="D46" s="23"/>
       <c r="E46" s="4">
         <v>2</v>
       </c>
@@ -1733,7 +1768,7 @@
       <c r="C47" s="8">
         <v>46042</v>
       </c>
-      <c r="D47" s="22"/>
+      <c r="D47" s="23"/>
       <c r="E47" s="4">
         <v>2</v>
       </c>
@@ -1751,7 +1786,7 @@
       <c r="C48" s="8">
         <v>46042</v>
       </c>
-      <c r="D48" s="22"/>
+      <c r="D48" s="23"/>
       <c r="E48" s="4">
         <v>2</v>
       </c>
@@ -1769,7 +1804,7 @@
       <c r="C49" s="8">
         <v>46042</v>
       </c>
-      <c r="D49" s="23"/>
+      <c r="D49" s="22"/>
       <c r="E49" s="4">
         <v>2</v>
       </c>
@@ -2047,7 +2082,7 @@
       <c r="C64" s="8">
         <v>46049</v>
       </c>
-      <c r="D64" s="22"/>
+      <c r="D64" s="23"/>
       <c r="E64" s="4">
         <v>13</v>
       </c>
@@ -2065,7 +2100,7 @@
       <c r="C65" s="8">
         <v>46049</v>
       </c>
-      <c r="D65" s="22"/>
+      <c r="D65" s="23"/>
       <c r="E65" s="4">
         <v>13</v>
       </c>
@@ -2083,7 +2118,7 @@
       <c r="C66" s="8">
         <v>46049</v>
       </c>
-      <c r="D66" s="22"/>
+      <c r="D66" s="23"/>
       <c r="E66" s="4">
         <v>13</v>
       </c>
@@ -2101,7 +2136,7 @@
       <c r="C67" s="8">
         <v>46049</v>
       </c>
-      <c r="D67" s="22"/>
+      <c r="D67" s="23"/>
       <c r="E67" s="4">
         <v>13</v>
       </c>
@@ -2119,7 +2154,7 @@
       <c r="C68" s="8">
         <v>46049</v>
       </c>
-      <c r="D68" s="23"/>
+      <c r="D68" s="22"/>
       <c r="E68" s="4">
         <v>13</v>
       </c>
@@ -2157,7 +2192,7 @@
       <c r="C70" s="8">
         <v>46050</v>
       </c>
-      <c r="D70" s="22"/>
+      <c r="D70" s="23"/>
       <c r="E70" s="4">
         <v>10</v>
       </c>
@@ -2175,7 +2210,7 @@
       <c r="C71" s="8">
         <v>46050</v>
       </c>
-      <c r="D71" s="23"/>
+      <c r="D71" s="22"/>
       <c r="E71" s="4">
         <v>10</v>
       </c>
@@ -2213,7 +2248,7 @@
       <c r="C73" s="8">
         <v>46050</v>
       </c>
-      <c r="D73" s="22"/>
+      <c r="D73" s="23"/>
       <c r="E73" s="4">
         <v>14</v>
       </c>
@@ -2231,7 +2266,7 @@
       <c r="C74" s="8">
         <v>46050</v>
       </c>
-      <c r="D74" s="23"/>
+      <c r="D74" s="22"/>
       <c r="E74" s="4">
         <v>14</v>
       </c>
@@ -2401,7 +2436,7 @@
       <c r="C83" s="8">
         <v>46052</v>
       </c>
-      <c r="D83" s="22"/>
+      <c r="D83" s="23"/>
       <c r="E83" s="4">
         <v>25</v>
       </c>
@@ -2419,7 +2454,7 @@
       <c r="C84" s="8">
         <v>46052</v>
       </c>
-      <c r="D84" s="22"/>
+      <c r="D84" s="23"/>
       <c r="E84" s="4">
         <v>25</v>
       </c>
@@ -2437,7 +2472,7 @@
       <c r="C85" s="8">
         <v>46052</v>
       </c>
-      <c r="D85" s="22"/>
+      <c r="D85" s="23"/>
       <c r="E85" s="4">
         <v>25</v>
       </c>
@@ -2455,7 +2490,7 @@
       <c r="C86" s="8">
         <v>46052</v>
       </c>
-      <c r="D86" s="22"/>
+      <c r="D86" s="23"/>
       <c r="E86" s="4">
         <v>25</v>
       </c>
@@ -2473,7 +2508,7 @@
       <c r="C87" s="8">
         <v>46052</v>
       </c>
-      <c r="D87" s="22"/>
+      <c r="D87" s="23"/>
       <c r="E87" s="4">
         <v>25</v>
       </c>
@@ -2491,7 +2526,7 @@
       <c r="C88" s="8">
         <v>46052</v>
       </c>
-      <c r="D88" s="22"/>
+      <c r="D88" s="23"/>
       <c r="E88" s="4">
         <v>25</v>
       </c>
@@ -2509,7 +2544,7 @@
       <c r="C89" s="8">
         <v>46052</v>
       </c>
-      <c r="D89" s="22"/>
+      <c r="D89" s="23"/>
       <c r="E89" s="4">
         <v>25</v>
       </c>
@@ -2527,7 +2562,7 @@
       <c r="C90" s="8">
         <v>46052</v>
       </c>
-      <c r="D90" s="22"/>
+      <c r="D90" s="23"/>
       <c r="E90" s="4">
         <v>25</v>
       </c>
@@ -2545,7 +2580,7 @@
       <c r="C91" s="8">
         <v>46052</v>
       </c>
-      <c r="D91" s="23"/>
+      <c r="D91" s="22"/>
       <c r="E91" s="4">
         <v>25</v>
       </c>
@@ -2583,7 +2618,7 @@
       <c r="C93" s="8">
         <v>46055</v>
       </c>
-      <c r="D93" s="22"/>
+      <c r="D93" s="23"/>
       <c r="E93" s="4">
         <v>17</v>
       </c>
@@ -2601,7 +2636,7 @@
       <c r="C94" s="8">
         <v>46055</v>
       </c>
-      <c r="D94" s="22"/>
+      <c r="D94" s="23"/>
       <c r="E94" s="4">
         <v>17</v>
       </c>
@@ -2619,7 +2654,7 @@
       <c r="C95" s="8">
         <v>46055</v>
       </c>
-      <c r="D95" s="23"/>
+      <c r="D95" s="22"/>
       <c r="E95" s="4">
         <v>17</v>
       </c>
@@ -2749,7 +2784,7 @@
       <c r="C102" s="8">
         <v>46057</v>
       </c>
-      <c r="D102" s="27">
+      <c r="D102" s="32">
         <v>21</v>
       </c>
       <c r="E102" s="11">
@@ -2769,7 +2804,7 @@
       <c r="C103" s="8">
         <v>46057</v>
       </c>
-      <c r="D103" s="27"/>
+      <c r="D103" s="32"/>
       <c r="E103" s="11">
         <v>21</v>
       </c>
@@ -2787,7 +2822,7 @@
       <c r="C104" s="8">
         <v>46057</v>
       </c>
-      <c r="D104" s="27"/>
+      <c r="D104" s="32"/>
       <c r="E104" s="11">
         <v>21</v>
       </c>
@@ -2805,7 +2840,7 @@
       <c r="C105" s="8">
         <v>46057</v>
       </c>
-      <c r="D105" s="27"/>
+      <c r="D105" s="32"/>
       <c r="E105" s="11">
         <v>2</v>
       </c>
@@ -2823,7 +2858,7 @@
       <c r="C106" s="8">
         <v>46057</v>
       </c>
-      <c r="D106" s="27"/>
+      <c r="D106" s="32"/>
       <c r="E106" s="11">
         <v>2</v>
       </c>
@@ -2841,7 +2876,7 @@
       <c r="C107" s="8">
         <v>46057</v>
       </c>
-      <c r="D107" s="27"/>
+      <c r="D107" s="32"/>
       <c r="E107" s="11">
         <v>2</v>
       </c>
@@ -2879,7 +2914,7 @@
       <c r="C109" s="8">
         <v>46058</v>
       </c>
-      <c r="D109" s="22"/>
+      <c r="D109" s="23"/>
       <c r="E109" s="4">
         <v>10</v>
       </c>
@@ -2897,7 +2932,7 @@
       <c r="C110" s="8">
         <v>46058</v>
       </c>
-      <c r="D110" s="23"/>
+      <c r="D110" s="22"/>
       <c r="E110" s="4">
         <v>10</v>
       </c>
@@ -2935,7 +2970,7 @@
       <c r="C112" s="8">
         <v>46058</v>
       </c>
-      <c r="D112" s="22"/>
+      <c r="D112" s="23"/>
       <c r="E112" s="4">
         <v>35</v>
       </c>
@@ -2953,7 +2988,7 @@
       <c r="C113" s="8">
         <v>46058</v>
       </c>
-      <c r="D113" s="22"/>
+      <c r="D113" s="23"/>
       <c r="E113" s="4">
         <v>35</v>
       </c>
@@ -2971,7 +3006,7 @@
       <c r="C114" s="8">
         <v>46058</v>
       </c>
-      <c r="D114" s="22"/>
+      <c r="D114" s="23"/>
       <c r="E114" s="4">
         <v>35</v>
       </c>
@@ -2989,7 +3024,7 @@
       <c r="C115" s="8">
         <v>46058</v>
       </c>
-      <c r="D115" s="22"/>
+      <c r="D115" s="23"/>
       <c r="E115" s="4">
         <v>35</v>
       </c>
@@ -3007,7 +3042,7 @@
       <c r="C116" s="8">
         <v>46058</v>
       </c>
-      <c r="D116" s="22"/>
+      <c r="D116" s="23"/>
       <c r="E116" s="4">
         <v>35</v>
       </c>
@@ -3025,7 +3060,7 @@
       <c r="C117" s="8">
         <v>46058</v>
       </c>
-      <c r="D117" s="22"/>
+      <c r="D117" s="23"/>
       <c r="E117" s="4">
         <v>35</v>
       </c>
@@ -3043,7 +3078,7 @@
       <c r="C118" s="8">
         <v>46058</v>
       </c>
-      <c r="D118" s="22"/>
+      <c r="D118" s="23"/>
       <c r="E118" s="4">
         <v>35</v>
       </c>
@@ -3061,7 +3096,7 @@
       <c r="C119" s="8">
         <v>46058</v>
       </c>
-      <c r="D119" s="22"/>
+      <c r="D119" s="23"/>
       <c r="E119" s="4">
         <v>35</v>
       </c>
@@ -3079,7 +3114,7 @@
       <c r="C120" s="8">
         <v>46058</v>
       </c>
-      <c r="D120" s="23"/>
+      <c r="D120" s="22"/>
       <c r="E120" s="4"/>
       <c r="F120" s="6" t="s">
         <v>72</v>
@@ -3115,7 +3150,7 @@
       <c r="C122" s="8">
         <v>46058</v>
       </c>
-      <c r="D122" s="22"/>
+      <c r="D122" s="23"/>
       <c r="E122" s="4">
         <v>12</v>
       </c>
@@ -3133,7 +3168,7 @@
       <c r="C123" s="8">
         <v>46058</v>
       </c>
-      <c r="D123" s="22"/>
+      <c r="D123" s="23"/>
       <c r="E123" s="4">
         <v>12</v>
       </c>
@@ -3151,7 +3186,7 @@
       <c r="C124" s="8">
         <v>46058</v>
       </c>
-      <c r="D124" s="22"/>
+      <c r="D124" s="23"/>
       <c r="E124" s="4">
         <v>12</v>
       </c>
@@ -3169,7 +3204,7 @@
       <c r="C125" s="8">
         <v>46058</v>
       </c>
-      <c r="D125" s="23"/>
+      <c r="D125" s="22"/>
       <c r="E125" s="4">
         <v>12</v>
       </c>
@@ -3245,7 +3280,7 @@
       <c r="C129" s="8">
         <v>46059</v>
       </c>
-      <c r="D129" s="22"/>
+      <c r="D129" s="23"/>
       <c r="E129" s="4">
         <v>4</v>
       </c>
@@ -3263,7 +3298,7 @@
       <c r="C130" s="8">
         <v>46059</v>
       </c>
-      <c r="D130" s="22"/>
+      <c r="D130" s="23"/>
       <c r="E130" s="4">
         <v>4</v>
       </c>
@@ -3281,7 +3316,7 @@
       <c r="C131" s="8">
         <v>46059</v>
       </c>
-      <c r="D131" s="23"/>
+      <c r="D131" s="22"/>
       <c r="E131" s="4">
         <v>4</v>
       </c>
@@ -3319,7 +3354,7 @@
       <c r="C133" s="8">
         <v>46059</v>
       </c>
-      <c r="D133" s="22"/>
+      <c r="D133" s="23"/>
       <c r="E133" s="4">
         <v>20</v>
       </c>
@@ -3337,7 +3372,7 @@
       <c r="C134" s="8">
         <v>46059</v>
       </c>
-      <c r="D134" s="22"/>
+      <c r="D134" s="23"/>
       <c r="E134" s="4">
         <v>20</v>
       </c>
@@ -3355,7 +3390,7 @@
       <c r="C135" s="8">
         <v>46059</v>
       </c>
-      <c r="D135" s="23"/>
+      <c r="D135" s="22"/>
       <c r="E135" s="4">
         <v>20</v>
       </c>
@@ -3393,7 +3428,7 @@
       <c r="C137" s="8">
         <v>46065</v>
       </c>
-      <c r="D137" s="22"/>
+      <c r="D137" s="23"/>
       <c r="E137" s="4">
         <v>16</v>
       </c>
@@ -3411,7 +3446,7 @@
       <c r="C138" s="8">
         <v>46065</v>
       </c>
-      <c r="D138" s="22"/>
+      <c r="D138" s="23"/>
       <c r="E138" s="4">
         <v>16</v>
       </c>
@@ -3429,7 +3464,7 @@
       <c r="C139" s="8">
         <v>46065</v>
       </c>
-      <c r="D139" s="22"/>
+      <c r="D139" s="23"/>
       <c r="E139" s="4">
         <v>16</v>
       </c>
@@ -3447,7 +3482,7 @@
       <c r="C140" s="8">
         <v>46065</v>
       </c>
-      <c r="D140" s="22"/>
+      <c r="D140" s="23"/>
       <c r="E140" s="4">
         <v>16</v>
       </c>
@@ -3465,7 +3500,7 @@
       <c r="C141" s="8">
         <v>46065</v>
       </c>
-      <c r="D141" s="22"/>
+      <c r="D141" s="23"/>
       <c r="E141" s="4">
         <v>15</v>
       </c>
@@ -3483,7 +3518,7 @@
       <c r="C142" s="8">
         <v>46065</v>
       </c>
-      <c r="D142" s="22"/>
+      <c r="D142" s="23"/>
       <c r="E142" s="4">
         <v>16</v>
       </c>
@@ -3501,7 +3536,7 @@
       <c r="C143" s="8">
         <v>46065</v>
       </c>
-      <c r="D143" s="22"/>
+      <c r="D143" s="23"/>
       <c r="E143" s="4">
         <v>15</v>
       </c>
@@ -3519,7 +3554,7 @@
       <c r="C144" s="8">
         <v>46065</v>
       </c>
-      <c r="D144" s="22"/>
+      <c r="D144" s="23"/>
       <c r="E144" s="4">
         <v>16</v>
       </c>
@@ -3537,7 +3572,7 @@
       <c r="C145" s="8">
         <v>46065</v>
       </c>
-      <c r="D145" s="23"/>
+      <c r="D145" s="22"/>
       <c r="E145" s="4">
         <v>16</v>
       </c>
@@ -3555,7 +3590,7 @@
       <c r="C146" s="8">
         <v>46066</v>
       </c>
-      <c r="D146" s="31">
+      <c r="D146" s="30">
         <v>5</v>
       </c>
       <c r="E146" s="4">
@@ -3575,7 +3610,7 @@
       <c r="C147" s="8">
         <v>46066</v>
       </c>
-      <c r="D147" s="32"/>
+      <c r="D147" s="31"/>
       <c r="E147" s="4">
         <v>5</v>
       </c>
@@ -3633,7 +3668,7 @@
       <c r="C150" s="8">
         <v>46068</v>
       </c>
-      <c r="D150" s="22"/>
+      <c r="D150" s="23"/>
       <c r="E150" s="4">
         <v>21</v>
       </c>
@@ -3651,7 +3686,7 @@
       <c r="C151" s="8">
         <v>46068</v>
       </c>
-      <c r="D151" s="22"/>
+      <c r="D151" s="23"/>
       <c r="E151" s="4">
         <v>21</v>
       </c>
@@ -3669,7 +3704,7 @@
       <c r="C152" s="8">
         <v>46068</v>
       </c>
-      <c r="D152" s="22"/>
+      <c r="D152" s="23"/>
       <c r="E152" s="4">
         <v>21</v>
       </c>
@@ -3687,7 +3722,7 @@
       <c r="C153" s="8">
         <v>46068</v>
       </c>
-      <c r="D153" s="22"/>
+      <c r="D153" s="23"/>
       <c r="E153" s="4">
         <v>21</v>
       </c>
@@ -3705,7 +3740,7 @@
       <c r="C154" s="8">
         <v>46068</v>
       </c>
-      <c r="D154" s="22"/>
+      <c r="D154" s="23"/>
       <c r="E154" s="4">
         <v>21</v>
       </c>
@@ -3723,7 +3758,7 @@
       <c r="C155" s="8">
         <v>46068</v>
       </c>
-      <c r="D155" s="22"/>
+      <c r="D155" s="23"/>
       <c r="E155" s="4">
         <v>21</v>
       </c>
@@ -3741,7 +3776,7 @@
       <c r="C156" s="8">
         <v>46068</v>
       </c>
-      <c r="D156" s="22"/>
+      <c r="D156" s="23"/>
       <c r="E156" s="4">
         <v>21</v>
       </c>
@@ -3759,7 +3794,7 @@
       <c r="C157" s="8">
         <v>46068</v>
       </c>
-      <c r="D157" s="23"/>
+      <c r="D157" s="22"/>
       <c r="E157" s="4">
         <v>21</v>
       </c>
@@ -3835,7 +3870,7 @@
       <c r="C161" s="8">
         <v>46069</v>
       </c>
-      <c r="D161" s="22"/>
+      <c r="D161" s="23"/>
       <c r="E161" s="4">
         <v>24</v>
       </c>
@@ -3853,7 +3888,7 @@
       <c r="C162" s="8">
         <v>46069</v>
       </c>
-      <c r="D162" s="22"/>
+      <c r="D162" s="23"/>
       <c r="E162" s="4">
         <v>24</v>
       </c>
@@ -3871,7 +3906,7 @@
       <c r="C163" s="8">
         <v>46069</v>
       </c>
-      <c r="D163" s="22"/>
+      <c r="D163" s="23"/>
       <c r="E163" s="4">
         <v>24</v>
       </c>
@@ -3889,7 +3924,7 @@
       <c r="C164" s="8">
         <v>46069</v>
       </c>
-      <c r="D164" s="22"/>
+      <c r="D164" s="23"/>
       <c r="E164" s="4">
         <v>24</v>
       </c>
@@ -3907,7 +3942,7 @@
       <c r="C165" s="8">
         <v>46069</v>
       </c>
-      <c r="D165" s="23"/>
+      <c r="D165" s="22"/>
       <c r="E165" s="4">
         <v>24</v>
       </c>
@@ -3925,7 +3960,7 @@
       <c r="C166" s="19">
         <v>46069</v>
       </c>
-      <c r="D166" s="28">
+      <c r="D166" s="27">
         <v>9</v>
       </c>
       <c r="E166" s="17">
@@ -3945,7 +3980,7 @@
       <c r="C167" s="19">
         <v>46069</v>
       </c>
-      <c r="D167" s="29"/>
+      <c r="D167" s="28"/>
       <c r="E167" s="17">
         <v>9</v>
       </c>
@@ -3963,7 +3998,7 @@
       <c r="C168" s="19">
         <v>46069</v>
       </c>
-      <c r="D168" s="30"/>
+      <c r="D168" s="29"/>
       <c r="E168" s="17">
         <v>9</v>
       </c>
@@ -4021,7 +4056,7 @@
       <c r="C171" s="8">
         <v>46069</v>
       </c>
-      <c r="D171" s="22"/>
+      <c r="D171" s="23"/>
       <c r="E171" s="4">
         <v>3</v>
       </c>
@@ -4039,7 +4074,7 @@
       <c r="C172" s="8">
         <v>46069</v>
       </c>
-      <c r="D172" s="22"/>
+      <c r="D172" s="23"/>
       <c r="E172" s="4">
         <v>1</v>
       </c>
@@ -4057,7 +4092,7 @@
       <c r="C173" s="8">
         <v>46069</v>
       </c>
-      <c r="D173" s="23"/>
+      <c r="D173" s="22"/>
       <c r="E173" s="4">
         <v>1</v>
       </c>
@@ -4095,7 +4130,7 @@
       <c r="C175" s="8">
         <v>46070</v>
       </c>
-      <c r="D175" s="22"/>
+      <c r="D175" s="23"/>
       <c r="E175" s="4">
         <v>10</v>
       </c>
@@ -4113,7 +4148,7 @@
       <c r="C176" s="8">
         <v>46070</v>
       </c>
-      <c r="D176" s="23"/>
+      <c r="D176" s="22"/>
       <c r="E176" s="4">
         <v>10</v>
       </c>
@@ -4151,7 +4186,7 @@
       <c r="C178" s="8">
         <v>46073</v>
       </c>
-      <c r="D178" s="22"/>
+      <c r="D178" s="23"/>
       <c r="E178" s="4">
         <v>5</v>
       </c>
@@ -4169,7 +4204,7 @@
       <c r="C179" s="8">
         <v>46073</v>
       </c>
-      <c r="D179" s="23"/>
+      <c r="D179" s="22"/>
       <c r="E179" s="4">
         <v>5</v>
       </c>
@@ -4207,7 +4242,7 @@
       <c r="C181" s="8">
         <v>46073</v>
       </c>
-      <c r="D181" s="22"/>
+      <c r="D181" s="23"/>
       <c r="E181" s="4">
         <v>2</v>
       </c>
@@ -4225,7 +4260,7 @@
       <c r="C182" s="8">
         <v>46073</v>
       </c>
-      <c r="D182" s="23"/>
+      <c r="D182" s="22"/>
       <c r="E182" s="4">
         <v>2</v>
       </c>
@@ -4263,7 +4298,7 @@
       <c r="C184" s="8">
         <v>46073</v>
       </c>
-      <c r="D184" s="22"/>
+      <c r="D184" s="23"/>
       <c r="E184" s="4">
         <v>24</v>
       </c>
@@ -4281,7 +4316,7 @@
       <c r="C185" s="8">
         <v>46073</v>
       </c>
-      <c r="D185" s="23"/>
+      <c r="D185" s="22"/>
       <c r="E185" s="4">
         <v>24</v>
       </c>
@@ -4322,7 +4357,7 @@
       <c r="C187" s="8">
         <v>46073</v>
       </c>
-      <c r="D187" s="22"/>
+      <c r="D187" s="23"/>
       <c r="E187" s="4">
         <v>5</v>
       </c>
@@ -4340,12 +4375,12 @@
       <c r="C188" s="8">
         <v>46073</v>
       </c>
-      <c r="D188" s="22"/>
+      <c r="D188" s="23"/>
       <c r="E188" s="4">
         <v>6</v>
       </c>
       <c r="F188" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">
@@ -4358,7 +4393,7 @@
       <c r="C189" s="8">
         <v>46073</v>
       </c>
-      <c r="D189" s="22"/>
+      <c r="D189" s="23"/>
       <c r="E189" s="4">
         <v>6</v>
       </c>
@@ -4376,7 +4411,7 @@
       <c r="C190" s="8">
         <v>46073</v>
       </c>
-      <c r="D190" s="22"/>
+      <c r="D190" s="23"/>
       <c r="E190" s="4">
         <v>6</v>
       </c>
@@ -4394,7 +4429,7 @@
       <c r="C191" s="8">
         <v>46073</v>
       </c>
-      <c r="D191" s="23"/>
+      <c r="D191" s="22"/>
       <c r="E191" s="4">
         <v>6</v>
       </c>
@@ -4439,7 +4474,7 @@
         <v>22</v>
       </c>
       <c r="F193" s="6" t="s">
-        <v>108</v>
+        <v>61</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
@@ -4452,7 +4487,7 @@
       <c r="C194" s="8">
         <v>46076</v>
       </c>
-      <c r="D194" s="23"/>
+      <c r="D194" s="22"/>
       <c r="E194" s="4">
         <v>22</v>
       </c>
@@ -4465,7 +4500,7 @@
         <v>378</v>
       </c>
       <c r="B195" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C195" s="8">
         <v>46077</v>
@@ -4485,17 +4520,17 @@
         <v>378</v>
       </c>
       <c r="B196" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C196" s="8">
         <v>46077</v>
       </c>
-      <c r="D196" s="22"/>
+      <c r="D196" s="23"/>
       <c r="E196" s="4">
         <v>1</v>
       </c>
       <c r="F196" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
@@ -4503,17 +4538,17 @@
         <v>378</v>
       </c>
       <c r="B197" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C197" s="8">
         <v>46077</v>
       </c>
-      <c r="D197" s="22"/>
+      <c r="D197" s="23"/>
       <c r="E197" s="4">
         <v>1</v>
       </c>
       <c r="F197" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
@@ -4521,17 +4556,17 @@
         <v>378</v>
       </c>
       <c r="B198" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C198" s="8">
         <v>46077</v>
       </c>
-      <c r="D198" s="22"/>
+      <c r="D198" s="23"/>
       <c r="E198" s="4">
         <v>1</v>
       </c>
       <c r="F198" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
@@ -4539,17 +4574,17 @@
         <v>378</v>
       </c>
       <c r="B199" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C199" s="8">
         <v>46077</v>
       </c>
-      <c r="D199" s="23"/>
+      <c r="D199" s="22"/>
       <c r="E199" s="4">
         <v>1</v>
       </c>
       <c r="F199" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
@@ -4557,7 +4592,7 @@
         <v>379</v>
       </c>
       <c r="B200" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C200" s="8">
         <v>46076</v>
@@ -4569,7 +4604,7 @@
         <v>1</v>
       </c>
       <c r="F200" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
@@ -4577,12 +4612,12 @@
         <v>379</v>
       </c>
       <c r="B201" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C201" s="8">
         <v>46076</v>
       </c>
-      <c r="D201" s="23"/>
+      <c r="D201" s="22"/>
       <c r="E201" s="4">
         <v>1</v>
       </c>
@@ -4591,204 +4626,473 @@
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A202" s="4"/>
-      <c r="B202" s="6"/>
-      <c r="C202" s="13"/>
-      <c r="D202" s="6"/>
-      <c r="E202" s="4"/>
-      <c r="F202" s="6"/>
+      <c r="A202" s="4">
+        <v>380</v>
+      </c>
+      <c r="B202" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C202" s="8">
+        <v>46080</v>
+      </c>
+      <c r="D202" s="21">
+        <v>34</v>
+      </c>
+      <c r="E202" s="4">
+        <v>34</v>
+      </c>
+      <c r="F202" s="6" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A203" s="4"/>
-      <c r="B203" s="6"/>
-      <c r="C203" s="13"/>
-      <c r="D203" s="6"/>
-      <c r="E203" s="4"/>
-      <c r="F203" s="6"/>
+      <c r="A203" s="4">
+        <v>380</v>
+      </c>
+      <c r="B203" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C203" s="8">
+        <v>46080</v>
+      </c>
+      <c r="D203" s="23"/>
+      <c r="E203" s="4">
+        <v>34</v>
+      </c>
+      <c r="F203" s="6" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A204" s="4"/>
-      <c r="B204" s="6"/>
-      <c r="C204" s="13"/>
-      <c r="D204" s="6"/>
-      <c r="E204" s="4"/>
-      <c r="F204" s="6"/>
+      <c r="A204" s="4">
+        <v>380</v>
+      </c>
+      <c r="B204" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C204" s="8">
+        <v>46080</v>
+      </c>
+      <c r="D204" s="22"/>
+      <c r="E204" s="4">
+        <v>34</v>
+      </c>
+      <c r="F204" s="6" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A205" s="4"/>
-      <c r="B205" s="6"/>
-      <c r="C205" s="13"/>
-      <c r="D205" s="6"/>
-      <c r="E205" s="4"/>
-      <c r="F205" s="6"/>
+      <c r="A205" s="4">
+        <v>381</v>
+      </c>
+      <c r="B205" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="C205" s="8">
+        <v>46083</v>
+      </c>
+      <c r="D205" s="21">
+        <v>2</v>
+      </c>
+      <c r="E205" s="4">
+        <v>1</v>
+      </c>
+      <c r="F205" s="6" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A206" s="4"/>
-      <c r="B206" s="6"/>
-      <c r="C206" s="13"/>
-      <c r="D206" s="6"/>
-      <c r="E206" s="4"/>
-      <c r="F206" s="6"/>
+      <c r="A206" s="4">
+        <v>381</v>
+      </c>
+      <c r="B206" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="C206" s="8">
+        <v>46083</v>
+      </c>
+      <c r="D206" s="23"/>
+      <c r="E206" s="4">
+        <v>1</v>
+      </c>
+      <c r="F206" s="6" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A207" s="4"/>
-      <c r="B207" s="6"/>
-      <c r="C207" s="13"/>
-      <c r="D207" s="6"/>
-      <c r="E207" s="4"/>
-      <c r="F207" s="6"/>
+      <c r="A207" s="4">
+        <v>381</v>
+      </c>
+      <c r="B207" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="C207" s="8">
+        <v>46083</v>
+      </c>
+      <c r="D207" s="23"/>
+      <c r="E207" s="4">
+        <v>1</v>
+      </c>
+      <c r="F207" s="6" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A208" s="4"/>
-      <c r="B208" s="6"/>
-      <c r="C208" s="13"/>
-      <c r="D208" s="6"/>
-      <c r="E208" s="4"/>
-      <c r="F208" s="6"/>
-    </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A209" s="4"/>
-      <c r="B209" s="6"/>
-      <c r="C209" s="13"/>
-      <c r="D209" s="6"/>
-      <c r="E209" s="4"/>
-      <c r="F209" s="6"/>
-    </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A210" s="4"/>
-      <c r="B210" s="6"/>
-      <c r="C210" s="13"/>
-      <c r="D210" s="6"/>
-      <c r="E210" s="4"/>
-      <c r="F210" s="6"/>
-    </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A211" s="4"/>
-      <c r="B211" s="6"/>
-      <c r="C211" s="13"/>
-      <c r="D211" s="6"/>
-      <c r="E211" s="4"/>
-      <c r="F211" s="6"/>
-    </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A212" s="4"/>
-      <c r="B212" s="6"/>
-      <c r="C212" s="13"/>
-      <c r="D212" s="6"/>
-      <c r="E212" s="4"/>
-      <c r="F212" s="6"/>
-    </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A213" s="4"/>
-      <c r="B213" s="6"/>
-      <c r="C213" s="13"/>
-      <c r="D213" s="6"/>
-      <c r="E213" s="4"/>
-      <c r="F213" s="6"/>
-    </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A214" s="4"/>
-      <c r="B214" s="6"/>
-      <c r="C214" s="13"/>
-      <c r="D214" s="6"/>
-      <c r="E214" s="4"/>
-      <c r="F214" s="6"/>
-    </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A215" s="4"/>
-      <c r="B215" s="6"/>
-      <c r="C215" s="13"/>
-      <c r="D215" s="6"/>
-      <c r="E215" s="4"/>
-      <c r="F215" s="6"/>
-    </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A216" s="4"/>
-      <c r="B216" s="6"/>
-      <c r="C216" s="13"/>
-      <c r="D216" s="6"/>
-      <c r="E216" s="4"/>
-      <c r="F216" s="6"/>
-    </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A217" s="4"/>
-      <c r="B217" s="6"/>
-      <c r="C217" s="13"/>
-      <c r="D217" s="6"/>
-      <c r="E217" s="4"/>
-      <c r="F217" s="6"/>
-    </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A218" s="4"/>
-      <c r="B218" s="6"/>
-      <c r="C218" s="13"/>
-      <c r="D218" s="6"/>
-      <c r="E218" s="4"/>
-      <c r="F218" s="6"/>
-    </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A219" s="4"/>
-      <c r="B219" s="6"/>
-      <c r="C219" s="13"/>
-      <c r="D219" s="6"/>
-      <c r="E219" s="4"/>
-      <c r="F219" s="6"/>
-    </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A220" s="4"/>
-      <c r="B220" s="6"/>
-      <c r="C220" s="13"/>
-      <c r="D220" s="6"/>
-      <c r="E220" s="4"/>
-      <c r="F220" s="6"/>
-    </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A221" s="4"/>
-      <c r="B221" s="6"/>
-      <c r="C221" s="13"/>
-      <c r="D221" s="6"/>
-      <c r="E221" s="4"/>
-      <c r="F221" s="6"/>
-    </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A222" s="4"/>
-      <c r="B222" s="6"/>
-      <c r="C222" s="13"/>
-      <c r="D222" s="6"/>
-      <c r="E222" s="4"/>
-      <c r="F222" s="6"/>
-    </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A223" s="4"/>
-      <c r="B223" s="6"/>
-      <c r="C223" s="13"/>
-      <c r="D223" s="6"/>
-      <c r="E223" s="4"/>
-      <c r="F223" s="6"/>
-    </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A224" s="4"/>
-      <c r="B224" s="6"/>
-      <c r="C224" s="13"/>
-      <c r="D224" s="6"/>
-      <c r="E224" s="4"/>
-      <c r="F224" s="6"/>
+      <c r="A208" s="4">
+        <v>381</v>
+      </c>
+      <c r="B208" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="C208" s="8">
+        <v>46083</v>
+      </c>
+      <c r="D208" s="23"/>
+      <c r="E208" s="4">
+        <v>1</v>
+      </c>
+      <c r="F208" s="6" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A209" s="4">
+        <v>381</v>
+      </c>
+      <c r="B209" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="C209" s="8">
+        <v>46083</v>
+      </c>
+      <c r="D209" s="22"/>
+      <c r="E209" s="4">
+        <v>1</v>
+      </c>
+      <c r="F209" s="6" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A210" s="4">
+        <v>382</v>
+      </c>
+      <c r="B210" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C210" s="8">
+        <v>46083</v>
+      </c>
+      <c r="D210" s="21">
+        <v>19</v>
+      </c>
+      <c r="E210" s="4">
+        <v>19</v>
+      </c>
+      <c r="F210" s="6" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A211" s="4">
+        <v>382</v>
+      </c>
+      <c r="B211" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C211" s="8">
+        <v>46083</v>
+      </c>
+      <c r="D211" s="23"/>
+      <c r="E211" s="4">
+        <v>19</v>
+      </c>
+      <c r="F211" s="6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A212" s="4">
+        <v>382</v>
+      </c>
+      <c r="B212" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C212" s="8">
+        <v>46083</v>
+      </c>
+      <c r="D212" s="22"/>
+      <c r="E212" s="4">
+        <v>19</v>
+      </c>
+      <c r="F212" s="6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A213" s="4">
+        <v>383</v>
+      </c>
+      <c r="B213" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C213" s="8">
+        <v>46084</v>
+      </c>
+      <c r="D213" s="4">
+        <v>71</v>
+      </c>
+      <c r="E213" s="4">
+        <v>71</v>
+      </c>
+      <c r="F213" s="6" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A214" s="4">
+        <v>384</v>
+      </c>
+      <c r="B214" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="C214" s="8">
+        <v>46084</v>
+      </c>
+      <c r="D214" s="4">
+        <v>108</v>
+      </c>
+      <c r="E214" s="4">
+        <v>108</v>
+      </c>
+      <c r="F214" s="6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A215" s="4">
+        <v>385</v>
+      </c>
+      <c r="B215" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="C215" s="8">
+        <v>46084</v>
+      </c>
+      <c r="D215" s="4">
+        <v>2</v>
+      </c>
+      <c r="E215" s="4">
+        <v>2</v>
+      </c>
+      <c r="F215" s="6" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A216" s="4">
+        <v>386</v>
+      </c>
+      <c r="B216" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C216" s="8">
+        <v>46086</v>
+      </c>
+      <c r="D216" s="32">
+        <v>7</v>
+      </c>
+      <c r="E216" s="4">
+        <v>7</v>
+      </c>
+      <c r="F216" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A217" s="4">
+        <v>386</v>
+      </c>
+      <c r="B217" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C217" s="8">
+        <v>46086</v>
+      </c>
+      <c r="D217" s="32"/>
+      <c r="E217" s="4">
+        <v>7</v>
+      </c>
+      <c r="F217" s="33" t="s">
+        <v>125</v>
+      </c>
+      <c r="G217" s="34" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A218" s="4">
+        <v>386</v>
+      </c>
+      <c r="B218" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C218" s="8">
+        <v>46086</v>
+      </c>
+      <c r="D218" s="32"/>
+      <c r="E218" s="4">
+        <v>7</v>
+      </c>
+      <c r="F218" s="6" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A219" s="4">
+        <v>386</v>
+      </c>
+      <c r="B219" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C219" s="8">
+        <v>46086</v>
+      </c>
+      <c r="D219" s="32"/>
+      <c r="E219" s="4">
+        <v>1</v>
+      </c>
+      <c r="F219" s="6" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A220" s="4">
+        <v>386</v>
+      </c>
+      <c r="B220" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C220" s="8">
+        <v>46086</v>
+      </c>
+      <c r="D220" s="32"/>
+      <c r="E220" s="4">
+        <v>1</v>
+      </c>
+      <c r="F220" s="6" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A221" s="4">
+        <v>387</v>
+      </c>
+      <c r="B221" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="C221" s="8">
+        <v>46086</v>
+      </c>
+      <c r="D221" s="21">
+        <v>120</v>
+      </c>
+      <c r="E221" s="4">
+        <v>120</v>
+      </c>
+      <c r="F221" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A222" s="4">
+        <v>387</v>
+      </c>
+      <c r="B222" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="C222" s="8">
+        <v>46086</v>
+      </c>
+      <c r="D222" s="23"/>
+      <c r="E222" s="4">
+        <v>120</v>
+      </c>
+      <c r="F222" s="6" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A223" s="4">
+        <v>387</v>
+      </c>
+      <c r="B223" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="C223" s="8">
+        <v>46086</v>
+      </c>
+      <c r="D223" s="23"/>
+      <c r="E223" s="4">
+        <v>120</v>
+      </c>
+      <c r="F223" s="6" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A224" s="4">
+        <v>387</v>
+      </c>
+      <c r="B224" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="C224" s="8">
+        <v>46086</v>
+      </c>
+      <c r="D224" s="23"/>
+      <c r="E224" s="4">
+        <v>120</v>
+      </c>
+      <c r="F224" s="6" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A225" s="4"/>
-      <c r="B225" s="6"/>
-      <c r="C225" s="13"/>
-      <c r="D225" s="6"/>
-      <c r="E225" s="4"/>
-      <c r="F225" s="6"/>
+      <c r="A225" s="4">
+        <v>387</v>
+      </c>
+      <c r="B225" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="C225" s="8">
+        <v>46086</v>
+      </c>
+      <c r="D225" s="23"/>
+      <c r="E225" s="4">
+        <v>120</v>
+      </c>
+      <c r="F225" s="6" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A226" s="4"/>
-      <c r="B226" s="6"/>
-      <c r="C226" s="13"/>
-      <c r="D226" s="6"/>
-      <c r="E226" s="4"/>
-      <c r="F226" s="6"/>
+      <c r="A226" s="4">
+        <v>387</v>
+      </c>
+      <c r="B226" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="C226" s="8">
+        <v>46086</v>
+      </c>
+      <c r="D226" s="22"/>
+      <c r="E226" s="4">
+        <v>120</v>
+      </c>
+      <c r="F226" s="6" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" s="4"/>
@@ -7862,10 +8166,93 @@
       <c r="E610" s="4"/>
       <c r="F610" s="6"/>
     </row>
+    <row r="611" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A611" s="4"/>
+      <c r="B611" s="6"/>
+      <c r="C611" s="13"/>
+      <c r="D611" s="6"/>
+      <c r="E611" s="4"/>
+      <c r="F611" s="6"/>
+    </row>
+    <row r="612" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A612" s="4"/>
+      <c r="B612" s="6"/>
+      <c r="C612" s="13"/>
+      <c r="D612" s="6"/>
+      <c r="E612" s="4"/>
+      <c r="F612" s="6"/>
+    </row>
+    <row r="613" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A613" s="4"/>
+      <c r="B613" s="6"/>
+      <c r="C613" s="13"/>
+      <c r="D613" s="6"/>
+      <c r="E613" s="4"/>
+      <c r="F613" s="6"/>
+    </row>
+    <row r="614" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A614" s="4"/>
+      <c r="B614" s="6"/>
+      <c r="C614" s="13"/>
+      <c r="D614" s="6"/>
+      <c r="E614" s="4"/>
+      <c r="F614" s="6"/>
+    </row>
+    <row r="615" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A615" s="4"/>
+      <c r="B615" s="6"/>
+      <c r="C615" s="13"/>
+      <c r="D615" s="6"/>
+      <c r="E615" s="4"/>
+      <c r="F615" s="6"/>
+    </row>
+    <row r="616" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A616" s="4"/>
+      <c r="B616" s="6"/>
+      <c r="C616" s="13"/>
+      <c r="D616" s="6"/>
+      <c r="E616" s="4"/>
+      <c r="F616" s="6"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G201"/>
-  <mergeCells count="43">
+  <autoFilter ref="A1:G204"/>
+  <mergeCells count="48">
+    <mergeCell ref="D202:D204"/>
+    <mergeCell ref="D183:D185"/>
+    <mergeCell ref="D186:D191"/>
+    <mergeCell ref="D77:D79"/>
+    <mergeCell ref="D80:D81"/>
+    <mergeCell ref="D82:D91"/>
+    <mergeCell ref="D102:D107"/>
+    <mergeCell ref="D177:D179"/>
+    <mergeCell ref="D99:D101"/>
+    <mergeCell ref="D170:D173"/>
+    <mergeCell ref="D128:D131"/>
+    <mergeCell ref="D132:D135"/>
+    <mergeCell ref="D174:D176"/>
     <mergeCell ref="D200:D201"/>
+    <mergeCell ref="D92:D95"/>
+    <mergeCell ref="D180:D182"/>
+    <mergeCell ref="D2:D6"/>
+    <mergeCell ref="D7:D11"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="D15:D19"/>
+    <mergeCell ref="D20:D23"/>
+    <mergeCell ref="D111:D120"/>
+    <mergeCell ref="D121:D125"/>
+    <mergeCell ref="D126:D127"/>
+    <mergeCell ref="D72:D74"/>
+    <mergeCell ref="D31:D33"/>
+    <mergeCell ref="D36:D41"/>
+    <mergeCell ref="D44:D49"/>
+    <mergeCell ref="D50:D51"/>
+    <mergeCell ref="D54:D58"/>
+    <mergeCell ref="D75:D76"/>
+    <mergeCell ref="D69:D71"/>
+    <mergeCell ref="D216:D220"/>
+    <mergeCell ref="D221:D226"/>
+    <mergeCell ref="D210:D212"/>
+    <mergeCell ref="D205:D209"/>
     <mergeCell ref="D59:D61"/>
     <mergeCell ref="D108:D110"/>
     <mergeCell ref="D96:D98"/>
@@ -7878,36 +8265,6 @@
     <mergeCell ref="D146:D147"/>
     <mergeCell ref="D149:D157"/>
     <mergeCell ref="D158:D159"/>
-    <mergeCell ref="D111:D120"/>
-    <mergeCell ref="D121:D125"/>
-    <mergeCell ref="D126:D127"/>
-    <mergeCell ref="D31:D33"/>
-    <mergeCell ref="D36:D41"/>
-    <mergeCell ref="D44:D49"/>
-    <mergeCell ref="D50:D51"/>
-    <mergeCell ref="D54:D58"/>
-    <mergeCell ref="D2:D6"/>
-    <mergeCell ref="D7:D11"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="D15:D19"/>
-    <mergeCell ref="D20:D23"/>
-    <mergeCell ref="D72:D74"/>
-    <mergeCell ref="D75:D76"/>
-    <mergeCell ref="D92:D95"/>
-    <mergeCell ref="D69:D71"/>
-    <mergeCell ref="D180:D182"/>
-    <mergeCell ref="D183:D185"/>
-    <mergeCell ref="D186:D191"/>
-    <mergeCell ref="D77:D79"/>
-    <mergeCell ref="D80:D81"/>
-    <mergeCell ref="D82:D91"/>
-    <mergeCell ref="D102:D107"/>
-    <mergeCell ref="D177:D179"/>
-    <mergeCell ref="D99:D101"/>
-    <mergeCell ref="D170:D173"/>
-    <mergeCell ref="D128:D131"/>
-    <mergeCell ref="D132:D135"/>
-    <mergeCell ref="D174:D176"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/veri.xlsx
+++ b/veri.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8820"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11775"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="145">
   <si>
     <t>Sıra No</t>
   </si>
@@ -409,6 +409,54 @@
   </si>
   <si>
     <t>Bedelsiz yapıldı</t>
+  </si>
+  <si>
+    <t>Umut İnce</t>
+  </si>
+  <si>
+    <t>Ersan Galvaniz</t>
+  </si>
+  <si>
+    <t>Gözlü TİGEM</t>
+  </si>
+  <si>
+    <t>Toxoplasma Ab</t>
+  </si>
+  <si>
+    <t>Seher Veteriner Kliniği (HİPRA)</t>
+  </si>
+  <si>
+    <t>Border P80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FATİH ŞERBETÇİ </t>
+  </si>
+  <si>
+    <t>Bandırma Besi Hayvancılık A.Ş.</t>
+  </si>
+  <si>
+    <t>Leptospira Hardjo IgG/IgM</t>
+  </si>
+  <si>
+    <t>BVDV Ag SP</t>
+  </si>
+  <si>
+    <t>Yunus Tanrıverdi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAT </t>
+  </si>
+  <si>
+    <t>Niyazi Atak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADF </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matlı </t>
+  </si>
+  <si>
+    <t>A1/A2 Süt Tiplendirme</t>
   </si>
 </sst>
 </file>
@@ -511,7 +559,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -544,12 +592,8 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -557,13 +601,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -574,6 +634,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -590,11 +653,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -875,15 +933,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G616"/>
+  <dimension ref="A1:G617"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="10" customWidth="1"/>
     <col min="2" max="2" width="31.85546875" customWidth="1"/>
     <col min="3" max="3" width="24.7109375" style="9" customWidth="1"/>
-    <col min="4" max="4" width="12.85546875" customWidth="1"/>
+    <col min="4" max="4" width="12.85546875" style="10" customWidth="1"/>
     <col min="5" max="5" width="21.5703125" style="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="37.28515625" customWidth="1"/>
+    <col min="6" max="6" width="37.28515625" style="24" customWidth="1"/>
     <col min="7" max="7" width="15.42578125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -900,7 +958,7 @@
       <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="14" t="s">
         <v>115</v>
       </c>
       <c r="F1" s="2" t="s">
@@ -920,13 +978,13 @@
       <c r="C2" s="8">
         <v>46027</v>
       </c>
-      <c r="D2" s="21">
+      <c r="D2" s="25">
         <v>37</v>
       </c>
       <c r="E2" s="4">
         <v>37</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="5" t="s">
         <v>72</v>
       </c>
     </row>
@@ -940,11 +998,11 @@
       <c r="C3" s="8">
         <v>46027</v>
       </c>
-      <c r="D3" s="23"/>
+      <c r="D3" s="26"/>
       <c r="E3" s="4">
         <v>37</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="5" t="s">
         <v>116</v>
       </c>
     </row>
@@ -958,11 +1016,11 @@
       <c r="C4" s="8">
         <v>46027</v>
       </c>
-      <c r="D4" s="23"/>
+      <c r="D4" s="26"/>
       <c r="E4" s="4">
         <v>37</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="5" t="s">
         <v>56</v>
       </c>
     </row>
@@ -976,11 +1034,11 @@
       <c r="C5" s="8">
         <v>46027</v>
       </c>
-      <c r="D5" s="23"/>
+      <c r="D5" s="26"/>
       <c r="E5" s="4">
         <v>37</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="5" t="s">
         <v>57</v>
       </c>
     </row>
@@ -994,11 +1052,11 @@
       <c r="C6" s="8">
         <v>46027</v>
       </c>
-      <c r="D6" s="22"/>
+      <c r="D6" s="27"/>
       <c r="E6" s="4">
         <v>37</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="5" t="s">
         <v>58</v>
       </c>
     </row>
@@ -1012,13 +1070,13 @@
       <c r="C7" s="8">
         <v>46029</v>
       </c>
-      <c r="D7" s="21">
+      <c r="D7" s="25">
         <v>1</v>
       </c>
       <c r="E7" s="4">
         <v>1</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="5" t="s">
         <v>59</v>
       </c>
     </row>
@@ -1032,11 +1090,11 @@
       <c r="C8" s="8">
         <v>46029</v>
       </c>
-      <c r="D8" s="23"/>
+      <c r="D8" s="26"/>
       <c r="E8" s="4">
         <v>1</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="5" t="s">
         <v>60</v>
       </c>
     </row>
@@ -1050,11 +1108,11 @@
       <c r="C9" s="8">
         <v>46029</v>
       </c>
-      <c r="D9" s="23"/>
+      <c r="D9" s="26"/>
       <c r="E9" s="4">
         <v>1</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="5" t="s">
         <v>61</v>
       </c>
     </row>
@@ -1068,11 +1126,11 @@
       <c r="C10" s="8">
         <v>46029</v>
       </c>
-      <c r="D10" s="23"/>
+      <c r="D10" s="26"/>
       <c r="E10" s="4">
         <v>1</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F10" s="5" t="s">
         <v>58</v>
       </c>
     </row>
@@ -1086,11 +1144,11 @@
       <c r="C11" s="8">
         <v>46029</v>
       </c>
-      <c r="D11" s="22"/>
+      <c r="D11" s="27"/>
       <c r="E11" s="4">
         <v>1</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="F11" s="5" t="s">
         <v>62</v>
       </c>
     </row>
@@ -1104,13 +1162,13 @@
       <c r="C12" s="8">
         <v>46030</v>
       </c>
-      <c r="D12" s="21">
+      <c r="D12" s="25">
         <v>2</v>
       </c>
       <c r="E12" s="4">
         <v>2</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="F12" s="5" t="s">
         <v>63</v>
       </c>
     </row>
@@ -1124,11 +1182,11 @@
       <c r="C13" s="8">
         <v>46030</v>
       </c>
-      <c r="D13" s="22"/>
+      <c r="D13" s="27"/>
       <c r="E13" s="4">
         <v>2</v>
       </c>
-      <c r="F13" s="6" t="s">
+      <c r="F13" s="5" t="s">
         <v>64</v>
       </c>
     </row>
@@ -1148,7 +1206,7 @@
       <c r="E14" s="4">
         <v>5</v>
       </c>
-      <c r="F14" s="6" t="s">
+      <c r="F14" s="5" t="s">
         <v>65</v>
       </c>
     </row>
@@ -1162,13 +1220,13 @@
       <c r="C15" s="8">
         <v>46031</v>
       </c>
-      <c r="D15" s="21">
+      <c r="D15" s="25">
         <v>21</v>
       </c>
       <c r="E15" s="4">
         <v>21</v>
       </c>
-      <c r="F15" s="6" t="s">
+      <c r="F15" s="5" t="s">
         <v>58</v>
       </c>
     </row>
@@ -1182,11 +1240,11 @@
       <c r="C16" s="8">
         <v>46031</v>
       </c>
-      <c r="D16" s="23"/>
+      <c r="D16" s="26"/>
       <c r="E16" s="4">
         <v>21</v>
       </c>
-      <c r="F16" s="6" t="s">
+      <c r="F16" s="5" t="s">
         <v>61</v>
       </c>
     </row>
@@ -1200,11 +1258,11 @@
       <c r="C17" s="8">
         <v>46031</v>
       </c>
-      <c r="D17" s="23"/>
+      <c r="D17" s="26"/>
       <c r="E17" s="4">
         <v>21</v>
       </c>
-      <c r="F17" s="6" t="s">
+      <c r="F17" s="5" t="s">
         <v>66</v>
       </c>
     </row>
@@ -1218,11 +1276,11 @@
       <c r="C18" s="8">
         <v>46031</v>
       </c>
-      <c r="D18" s="23"/>
+      <c r="D18" s="26"/>
       <c r="E18" s="4">
         <v>21</v>
       </c>
-      <c r="F18" s="6" t="s">
+      <c r="F18" s="5" t="s">
         <v>67</v>
       </c>
     </row>
@@ -1236,11 +1294,11 @@
       <c r="C19" s="8">
         <v>46031</v>
       </c>
-      <c r="D19" s="22"/>
+      <c r="D19" s="27"/>
       <c r="E19" s="4">
         <v>1</v>
       </c>
-      <c r="F19" s="6" t="s">
+      <c r="F19" s="5" t="s">
         <v>68</v>
       </c>
     </row>
@@ -1254,13 +1312,13 @@
       <c r="C20" s="8">
         <v>46031</v>
       </c>
-      <c r="D20" s="21">
+      <c r="D20" s="25">
         <v>1</v>
       </c>
       <c r="E20" s="4">
         <v>1</v>
       </c>
-      <c r="F20" s="6" t="s">
+      <c r="F20" s="5" t="s">
         <v>69</v>
       </c>
     </row>
@@ -1274,11 +1332,11 @@
       <c r="C21" s="8">
         <v>46031</v>
       </c>
-      <c r="D21" s="23"/>
+      <c r="D21" s="26"/>
       <c r="E21" s="4">
         <v>1</v>
       </c>
-      <c r="F21" s="6" t="s">
+      <c r="F21" s="5" t="s">
         <v>70</v>
       </c>
     </row>
@@ -1292,11 +1350,11 @@
       <c r="C22" s="8">
         <v>46031</v>
       </c>
-      <c r="D22" s="23"/>
+      <c r="D22" s="26"/>
       <c r="E22" s="4">
         <v>1</v>
       </c>
-      <c r="F22" s="6" t="s">
+      <c r="F22" s="5" t="s">
         <v>63</v>
       </c>
     </row>
@@ -1310,11 +1368,11 @@
       <c r="C23" s="8">
         <v>46031</v>
       </c>
-      <c r="D23" s="22"/>
+      <c r="D23" s="27"/>
       <c r="E23" s="4">
         <v>1</v>
       </c>
-      <c r="F23" s="6" t="s">
+      <c r="F23" s="5" t="s">
         <v>64</v>
       </c>
     </row>
@@ -1334,7 +1392,7 @@
       <c r="E24" s="4">
         <v>125</v>
       </c>
-      <c r="F24" s="6" t="s">
+      <c r="F24" s="5" t="s">
         <v>61</v>
       </c>
     </row>
@@ -1354,7 +1412,7 @@
       <c r="E25" s="4">
         <v>125</v>
       </c>
-      <c r="F25" s="6" t="s">
+      <c r="F25" s="5" t="s">
         <v>58</v>
       </c>
     </row>
@@ -1374,7 +1432,7 @@
       <c r="E26" s="4">
         <v>125</v>
       </c>
-      <c r="F26" s="6" t="s">
+      <c r="F26" s="5" t="s">
         <v>62</v>
       </c>
     </row>
@@ -1392,7 +1450,7 @@
       <c r="E27" s="4">
         <v>9</v>
       </c>
-      <c r="F27" s="6" t="s">
+      <c r="F27" s="5" t="s">
         <v>71</v>
       </c>
     </row>
@@ -1412,7 +1470,7 @@
       <c r="E28" s="4">
         <v>186</v>
       </c>
-      <c r="F28" s="6" t="s">
+      <c r="F28" s="5" t="s">
         <v>58</v>
       </c>
     </row>
@@ -1432,7 +1490,7 @@
       <c r="E29" s="4">
         <v>274</v>
       </c>
-      <c r="F29" s="6" t="s">
+      <c r="F29" s="5" t="s">
         <v>72</v>
       </c>
     </row>
@@ -1452,7 +1510,7 @@
       <c r="E30" s="4">
         <v>2</v>
       </c>
-      <c r="F30" s="6" t="s">
+      <c r="F30" s="5" t="s">
         <v>59</v>
       </c>
     </row>
@@ -1466,13 +1524,13 @@
       <c r="C31" s="8">
         <v>46035</v>
       </c>
-      <c r="D31" s="21">
+      <c r="D31" s="25">
         <v>1789</v>
       </c>
       <c r="E31" s="4">
         <v>1789</v>
       </c>
-      <c r="F31" s="6" t="s">
+      <c r="F31" s="5" t="s">
         <v>58</v>
       </c>
     </row>
@@ -1486,11 +1544,11 @@
       <c r="C32" s="8">
         <v>46035</v>
       </c>
-      <c r="D32" s="23"/>
+      <c r="D32" s="26"/>
       <c r="E32" s="4">
         <v>1789</v>
       </c>
-      <c r="F32" s="6" t="s">
+      <c r="F32" s="5" t="s">
         <v>62</v>
       </c>
     </row>
@@ -1504,11 +1562,11 @@
       <c r="C33" s="8">
         <v>46035</v>
       </c>
-      <c r="D33" s="22"/>
+      <c r="D33" s="27"/>
       <c r="E33" s="4">
         <v>1789</v>
       </c>
-      <c r="F33" s="6" t="s">
+      <c r="F33" s="5" t="s">
         <v>61</v>
       </c>
     </row>
@@ -1528,7 +1586,7 @@
       <c r="E34" s="4">
         <v>3</v>
       </c>
-      <c r="F34" s="6" t="s">
+      <c r="F34" s="5" t="s">
         <v>73</v>
       </c>
     </row>
@@ -1548,7 +1606,7 @@
       <c r="E35" s="4">
         <v>3</v>
       </c>
-      <c r="F35" s="6" t="s">
+      <c r="F35" s="5" t="s">
         <v>77</v>
       </c>
     </row>
@@ -1562,13 +1620,13 @@
       <c r="C36" s="8">
         <v>46042</v>
       </c>
-      <c r="D36" s="21">
+      <c r="D36" s="25">
         <v>7</v>
       </c>
       <c r="E36" s="4">
         <v>1</v>
       </c>
-      <c r="F36" s="6" t="s">
+      <c r="F36" s="5" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1582,11 +1640,11 @@
       <c r="C37" s="8">
         <v>46042</v>
       </c>
-      <c r="D37" s="23"/>
+      <c r="D37" s="26"/>
       <c r="E37" s="4">
         <v>1</v>
       </c>
-      <c r="F37" s="6" t="s">
+      <c r="F37" s="5" t="s">
         <v>75</v>
       </c>
     </row>
@@ -1600,11 +1658,11 @@
       <c r="C38" s="8">
         <v>46042</v>
       </c>
-      <c r="D38" s="23"/>
+      <c r="D38" s="26"/>
       <c r="E38" s="4">
         <v>1</v>
       </c>
-      <c r="F38" s="6" t="s">
+      <c r="F38" s="5" t="s">
         <v>73</v>
       </c>
     </row>
@@ -1618,11 +1676,11 @@
       <c r="C39" s="8">
         <v>46042</v>
       </c>
-      <c r="D39" s="23"/>
+      <c r="D39" s="26"/>
       <c r="E39" s="4">
         <v>1</v>
       </c>
-      <c r="F39" s="6" t="s">
+      <c r="F39" s="5" t="s">
         <v>76</v>
       </c>
     </row>
@@ -1636,11 +1694,11 @@
       <c r="C40" s="8">
         <v>46042</v>
       </c>
-      <c r="D40" s="23"/>
+      <c r="D40" s="26"/>
       <c r="E40" s="4">
         <v>7</v>
       </c>
-      <c r="F40" s="6" t="s">
+      <c r="F40" s="5" t="s">
         <v>63</v>
       </c>
     </row>
@@ -1654,11 +1712,11 @@
       <c r="C41" s="8">
         <v>46042</v>
       </c>
-      <c r="D41" s="22"/>
+      <c r="D41" s="27"/>
       <c r="E41" s="4">
         <v>2</v>
       </c>
-      <c r="F41" s="6" t="s">
+      <c r="F41" s="5" t="s">
         <v>64</v>
       </c>
     </row>
@@ -1678,7 +1736,7 @@
       <c r="E42" s="4">
         <v>39</v>
       </c>
-      <c r="F42" s="6" t="s">
+      <c r="F42" s="5" t="s">
         <v>58</v>
       </c>
     </row>
@@ -1698,7 +1756,7 @@
       <c r="E43" s="4">
         <v>8</v>
       </c>
-      <c r="F43" s="6" t="s">
+      <c r="F43" s="5" t="s">
         <v>58</v>
       </c>
     </row>
@@ -1712,13 +1770,13 @@
       <c r="C44" s="8">
         <v>46042</v>
       </c>
-      <c r="D44" s="21">
+      <c r="D44" s="25">
         <v>2</v>
       </c>
       <c r="E44" s="4">
         <v>2</v>
       </c>
-      <c r="F44" s="6" t="s">
+      <c r="F44" s="5" t="s">
         <v>68</v>
       </c>
     </row>
@@ -1732,11 +1790,11 @@
       <c r="C45" s="8">
         <v>46042</v>
       </c>
-      <c r="D45" s="23"/>
+      <c r="D45" s="26"/>
       <c r="E45" s="4">
         <v>2</v>
       </c>
-      <c r="F45" s="6" t="s">
+      <c r="F45" s="5" t="s">
         <v>60</v>
       </c>
     </row>
@@ -1750,11 +1808,11 @@
       <c r="C46" s="8">
         <v>46042</v>
       </c>
-      <c r="D46" s="23"/>
+      <c r="D46" s="26"/>
       <c r="E46" s="4">
         <v>2</v>
       </c>
-      <c r="F46" s="6" t="s">
+      <c r="F46" s="5" t="s">
         <v>59</v>
       </c>
     </row>
@@ -1768,11 +1826,11 @@
       <c r="C47" s="8">
         <v>46042</v>
       </c>
-      <c r="D47" s="23"/>
+      <c r="D47" s="26"/>
       <c r="E47" s="4">
         <v>2</v>
       </c>
-      <c r="F47" s="6" t="s">
+      <c r="F47" s="5" t="s">
         <v>58</v>
       </c>
     </row>
@@ -1786,11 +1844,11 @@
       <c r="C48" s="8">
         <v>46042</v>
       </c>
-      <c r="D48" s="23"/>
+      <c r="D48" s="26"/>
       <c r="E48" s="4">
         <v>2</v>
       </c>
-      <c r="F48" s="6" t="s">
+      <c r="F48" s="5" t="s">
         <v>66</v>
       </c>
     </row>
@@ -1804,11 +1862,11 @@
       <c r="C49" s="8">
         <v>46042</v>
       </c>
-      <c r="D49" s="22"/>
+      <c r="D49" s="27"/>
       <c r="E49" s="4">
         <v>2</v>
       </c>
-      <c r="F49" s="6" t="s">
+      <c r="F49" s="5" t="s">
         <v>77</v>
       </c>
     </row>
@@ -1822,13 +1880,13 @@
       <c r="C50" s="8">
         <v>46043</v>
       </c>
-      <c r="D50" s="24">
+      <c r="D50" s="28">
         <v>21</v>
       </c>
       <c r="E50" s="4">
         <v>21</v>
       </c>
-      <c r="F50" s="6" t="s">
+      <c r="F50" s="5" t="s">
         <v>61</v>
       </c>
     </row>
@@ -1842,11 +1900,11 @@
       <c r="C51" s="8">
         <v>46043</v>
       </c>
-      <c r="D51" s="26"/>
+      <c r="D51" s="30"/>
       <c r="E51" s="4">
         <v>21</v>
       </c>
-      <c r="F51" s="6" t="s">
+      <c r="F51" s="5" t="s">
         <v>58</v>
       </c>
     </row>
@@ -1864,7 +1922,7 @@
       <c r="E52" s="4">
         <v>1</v>
       </c>
-      <c r="F52" s="6" t="s">
+      <c r="F52" s="5" t="s">
         <v>78</v>
       </c>
     </row>
@@ -1882,7 +1940,7 @@
       <c r="E53" s="4">
         <v>1</v>
       </c>
-      <c r="F53" s="6" t="s">
+      <c r="F53" s="5" t="s">
         <v>79</v>
       </c>
     </row>
@@ -1896,13 +1954,13 @@
       <c r="C54" s="8">
         <v>46044</v>
       </c>
-      <c r="D54" s="24">
+      <c r="D54" s="28">
         <v>11</v>
       </c>
       <c r="E54" s="4">
         <v>10</v>
       </c>
-      <c r="F54" s="6" t="s">
+      <c r="F54" s="5" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1916,11 +1974,11 @@
       <c r="C55" s="8">
         <v>46044</v>
       </c>
-      <c r="D55" s="25"/>
+      <c r="D55" s="29"/>
       <c r="E55" s="4">
         <v>10</v>
       </c>
-      <c r="F55" s="6" t="s">
+      <c r="F55" s="5" t="s">
         <v>75</v>
       </c>
     </row>
@@ -1934,11 +1992,11 @@
       <c r="C56" s="8">
         <v>46044</v>
       </c>
-      <c r="D56" s="25"/>
+      <c r="D56" s="29"/>
       <c r="E56" s="4">
         <v>10</v>
       </c>
-      <c r="F56" s="6" t="s">
+      <c r="F56" s="5" t="s">
         <v>63</v>
       </c>
     </row>
@@ -1952,9 +2010,9 @@
       <c r="C57" s="8">
         <v>46044</v>
       </c>
-      <c r="D57" s="25"/>
+      <c r="D57" s="29"/>
       <c r="E57" s="4"/>
-      <c r="F57" s="6" t="s">
+      <c r="F57" s="5" t="s">
         <v>64</v>
       </c>
     </row>
@@ -1968,11 +2026,11 @@
       <c r="C58" s="8">
         <v>46044</v>
       </c>
-      <c r="D58" s="26"/>
+      <c r="D58" s="30"/>
       <c r="E58" s="4">
         <v>1</v>
       </c>
-      <c r="F58" s="6" t="s">
+      <c r="F58" s="5" t="s">
         <v>72</v>
       </c>
     </row>
@@ -1986,13 +2044,13 @@
       <c r="C59" s="8">
         <v>46041</v>
       </c>
-      <c r="D59" s="24">
+      <c r="D59" s="28">
         <v>1</v>
       </c>
       <c r="E59" s="4">
         <v>1</v>
       </c>
-      <c r="F59" s="6" t="s">
+      <c r="F59" s="5" t="s">
         <v>80</v>
       </c>
     </row>
@@ -2006,11 +2064,11 @@
       <c r="C60" s="8">
         <v>46041</v>
       </c>
-      <c r="D60" s="25"/>
+      <c r="D60" s="29"/>
       <c r="E60" s="4">
         <v>1</v>
       </c>
-      <c r="F60" s="6" t="s">
+      <c r="F60" s="5" t="s">
         <v>63</v>
       </c>
     </row>
@@ -2024,11 +2082,11 @@
       <c r="C61" s="8">
         <v>46041</v>
       </c>
-      <c r="D61" s="26"/>
+      <c r="D61" s="30"/>
       <c r="E61" s="4">
         <v>1</v>
       </c>
-      <c r="F61" s="6" t="s">
+      <c r="F61" s="5" t="s">
         <v>64</v>
       </c>
     </row>
@@ -2048,7 +2106,7 @@
       <c r="E62" s="4">
         <v>3</v>
       </c>
-      <c r="F62" s="6" t="s">
+      <c r="F62" s="5" t="s">
         <v>82</v>
       </c>
     </row>
@@ -2062,13 +2120,13 @@
       <c r="C63" s="8">
         <v>46049</v>
       </c>
-      <c r="D63" s="21">
+      <c r="D63" s="25">
         <v>13</v>
       </c>
       <c r="E63" s="4">
         <v>10</v>
       </c>
-      <c r="F63" s="6" t="s">
+      <c r="F63" s="5" t="s">
         <v>61</v>
       </c>
     </row>
@@ -2082,11 +2140,11 @@
       <c r="C64" s="8">
         <v>46049</v>
       </c>
-      <c r="D64" s="23"/>
+      <c r="D64" s="26"/>
       <c r="E64" s="4">
         <v>13</v>
       </c>
-      <c r="F64" s="6" t="s">
+      <c r="F64" s="5" t="s">
         <v>60</v>
       </c>
     </row>
@@ -2100,11 +2158,11 @@
       <c r="C65" s="8">
         <v>46049</v>
       </c>
-      <c r="D65" s="23"/>
+      <c r="D65" s="26"/>
       <c r="E65" s="4">
         <v>13</v>
       </c>
-      <c r="F65" s="6" t="s">
+      <c r="F65" s="5" t="s">
         <v>81</v>
       </c>
     </row>
@@ -2118,11 +2176,11 @@
       <c r="C66" s="8">
         <v>46049</v>
       </c>
-      <c r="D66" s="23"/>
+      <c r="D66" s="26"/>
       <c r="E66" s="4">
         <v>13</v>
       </c>
-      <c r="F66" s="6" t="s">
+      <c r="F66" s="5" t="s">
         <v>72</v>
       </c>
     </row>
@@ -2136,11 +2194,11 @@
       <c r="C67" s="8">
         <v>46049</v>
       </c>
-      <c r="D67" s="23"/>
+      <c r="D67" s="26"/>
       <c r="E67" s="4">
         <v>13</v>
       </c>
-      <c r="F67" s="6" t="s">
+      <c r="F67" s="5" t="s">
         <v>58</v>
       </c>
     </row>
@@ -2154,11 +2212,11 @@
       <c r="C68" s="8">
         <v>46049</v>
       </c>
-      <c r="D68" s="22"/>
+      <c r="D68" s="27"/>
       <c r="E68" s="4">
         <v>13</v>
       </c>
-      <c r="F68" s="6" t="s">
+      <c r="F68" s="5" t="s">
         <v>59</v>
       </c>
     </row>
@@ -2172,13 +2230,13 @@
       <c r="C69" s="8">
         <v>46050</v>
       </c>
-      <c r="D69" s="21">
+      <c r="D69" s="25">
         <v>10</v>
       </c>
       <c r="E69" s="4">
         <v>10</v>
       </c>
-      <c r="F69" s="6" t="s">
+      <c r="F69" s="5" t="s">
         <v>58</v>
       </c>
     </row>
@@ -2192,11 +2250,11 @@
       <c r="C70" s="8">
         <v>46050</v>
       </c>
-      <c r="D70" s="23"/>
+      <c r="D70" s="26"/>
       <c r="E70" s="4">
         <v>10</v>
       </c>
-      <c r="F70" s="6" t="s">
+      <c r="F70" s="5" t="s">
         <v>61</v>
       </c>
     </row>
@@ -2210,11 +2268,11 @@
       <c r="C71" s="8">
         <v>46050</v>
       </c>
-      <c r="D71" s="22"/>
+      <c r="D71" s="27"/>
       <c r="E71" s="4">
         <v>10</v>
       </c>
-      <c r="F71" s="6" t="s">
+      <c r="F71" s="5" t="s">
         <v>62</v>
       </c>
     </row>
@@ -2228,13 +2286,13 @@
       <c r="C72" s="8">
         <v>46050</v>
       </c>
-      <c r="D72" s="21">
+      <c r="D72" s="25">
         <v>14</v>
       </c>
       <c r="E72" s="4">
         <v>14</v>
       </c>
-      <c r="F72" s="6" t="s">
+      <c r="F72" s="5" t="s">
         <v>82</v>
       </c>
     </row>
@@ -2248,11 +2306,11 @@
       <c r="C73" s="8">
         <v>46050</v>
       </c>
-      <c r="D73" s="23"/>
+      <c r="D73" s="26"/>
       <c r="E73" s="4">
         <v>14</v>
       </c>
-      <c r="F73" s="6" t="s">
+      <c r="F73" s="5" t="s">
         <v>58</v>
       </c>
     </row>
@@ -2266,11 +2324,11 @@
       <c r="C74" s="8">
         <v>46050</v>
       </c>
-      <c r="D74" s="22"/>
+      <c r="D74" s="27"/>
       <c r="E74" s="4">
         <v>14</v>
       </c>
-      <c r="F74" s="6" t="s">
+      <c r="F74" s="5" t="s">
         <v>83</v>
       </c>
     </row>
@@ -2284,13 +2342,13 @@
       <c r="C75" s="8">
         <v>46051</v>
       </c>
-      <c r="D75" s="24">
+      <c r="D75" s="28">
         <v>8</v>
       </c>
       <c r="E75" s="4">
         <v>8</v>
       </c>
-      <c r="F75" s="6" t="s">
+      <c r="F75" s="5" t="s">
         <v>59</v>
       </c>
     </row>
@@ -2304,11 +2362,11 @@
       <c r="C76" s="8">
         <v>46051</v>
       </c>
-      <c r="D76" s="26"/>
+      <c r="D76" s="30"/>
       <c r="E76" s="4">
         <v>8</v>
       </c>
-      <c r="F76" s="6" t="s">
+      <c r="F76" s="5" t="s">
         <v>60</v>
       </c>
     </row>
@@ -2322,13 +2380,13 @@
       <c r="C77" s="8">
         <v>46051</v>
       </c>
-      <c r="D77" s="24">
+      <c r="D77" s="28">
         <v>27</v>
       </c>
       <c r="E77" s="4">
         <v>27</v>
       </c>
-      <c r="F77" s="6" t="s">
+      <c r="F77" s="5" t="s">
         <v>82</v>
       </c>
     </row>
@@ -2342,11 +2400,11 @@
       <c r="C78" s="8">
         <v>46051</v>
       </c>
-      <c r="D78" s="25"/>
+      <c r="D78" s="29"/>
       <c r="E78" s="4">
         <v>27</v>
       </c>
-      <c r="F78" s="6" t="s">
+      <c r="F78" s="5" t="s">
         <v>58</v>
       </c>
     </row>
@@ -2360,11 +2418,11 @@
       <c r="C79" s="8">
         <v>46051</v>
       </c>
-      <c r="D79" s="26"/>
+      <c r="D79" s="30"/>
       <c r="E79" s="4">
         <v>27</v>
       </c>
-      <c r="F79" s="6" t="s">
+      <c r="F79" s="5" t="s">
         <v>62</v>
       </c>
     </row>
@@ -2378,13 +2436,13 @@
       <c r="C80" s="8">
         <v>46051</v>
       </c>
-      <c r="D80" s="24">
+      <c r="D80" s="28">
         <v>5</v>
       </c>
       <c r="E80" s="4">
         <v>5</v>
       </c>
-      <c r="F80" s="6" t="s">
+      <c r="F80" s="5" t="s">
         <v>63</v>
       </c>
     </row>
@@ -2398,11 +2456,11 @@
       <c r="C81" s="8">
         <v>46051</v>
       </c>
-      <c r="D81" s="26"/>
+      <c r="D81" s="30"/>
       <c r="E81" s="4">
         <v>5</v>
       </c>
-      <c r="F81" s="6" t="s">
+      <c r="F81" s="5" t="s">
         <v>69</v>
       </c>
     </row>
@@ -2416,13 +2474,13 @@
       <c r="C82" s="8">
         <v>46052</v>
       </c>
-      <c r="D82" s="21">
+      <c r="D82" s="25">
         <v>25</v>
       </c>
       <c r="E82" s="4">
         <v>25</v>
       </c>
-      <c r="F82" s="6" t="s">
+      <c r="F82" s="5" t="s">
         <v>84</v>
       </c>
     </row>
@@ -2436,11 +2494,11 @@
       <c r="C83" s="8">
         <v>46052</v>
       </c>
-      <c r="D83" s="23"/>
+      <c r="D83" s="26"/>
       <c r="E83" s="4">
         <v>25</v>
       </c>
-      <c r="F83" s="6" t="s">
+      <c r="F83" s="5" t="s">
         <v>85</v>
       </c>
     </row>
@@ -2454,11 +2512,11 @@
       <c r="C84" s="8">
         <v>46052</v>
       </c>
-      <c r="D84" s="23"/>
+      <c r="D84" s="26"/>
       <c r="E84" s="4">
         <v>25</v>
       </c>
-      <c r="F84" s="6" t="s">
+      <c r="F84" s="5" t="s">
         <v>81</v>
       </c>
     </row>
@@ -2472,11 +2530,11 @@
       <c r="C85" s="8">
         <v>46052</v>
       </c>
-      <c r="D85" s="23"/>
+      <c r="D85" s="26"/>
       <c r="E85" s="4">
         <v>25</v>
       </c>
-      <c r="F85" s="6" t="s">
+      <c r="F85" s="5" t="s">
         <v>60</v>
       </c>
     </row>
@@ -2490,11 +2548,11 @@
       <c r="C86" s="8">
         <v>46052</v>
       </c>
-      <c r="D86" s="23"/>
+      <c r="D86" s="26"/>
       <c r="E86" s="4">
         <v>25</v>
       </c>
-      <c r="F86" s="6" t="s">
+      <c r="F86" s="5" t="s">
         <v>66</v>
       </c>
     </row>
@@ -2508,11 +2566,11 @@
       <c r="C87" s="8">
         <v>46052</v>
       </c>
-      <c r="D87" s="23"/>
+      <c r="D87" s="26"/>
       <c r="E87" s="4">
         <v>25</v>
       </c>
-      <c r="F87" s="6" t="s">
+      <c r="F87" s="5" t="s">
         <v>61</v>
       </c>
     </row>
@@ -2526,11 +2584,11 @@
       <c r="C88" s="8">
         <v>46052</v>
       </c>
-      <c r="D88" s="23"/>
+      <c r="D88" s="26"/>
       <c r="E88" s="4">
         <v>25</v>
       </c>
-      <c r="F88" s="6" t="s">
+      <c r="F88" s="5" t="s">
         <v>58</v>
       </c>
     </row>
@@ -2544,11 +2602,11 @@
       <c r="C89" s="8">
         <v>46052</v>
       </c>
-      <c r="D89" s="23"/>
+      <c r="D89" s="26"/>
       <c r="E89" s="4">
         <v>25</v>
       </c>
-      <c r="F89" s="6" t="s">
+      <c r="F89" s="5" t="s">
         <v>62</v>
       </c>
     </row>
@@ -2562,11 +2620,11 @@
       <c r="C90" s="8">
         <v>46052</v>
       </c>
-      <c r="D90" s="23"/>
+      <c r="D90" s="26"/>
       <c r="E90" s="4">
         <v>25</v>
       </c>
-      <c r="F90" s="6" t="s">
+      <c r="F90" s="5" t="s">
         <v>72</v>
       </c>
     </row>
@@ -2580,11 +2638,11 @@
       <c r="C91" s="8">
         <v>46052</v>
       </c>
-      <c r="D91" s="22"/>
+      <c r="D91" s="27"/>
       <c r="E91" s="4">
         <v>25</v>
       </c>
-      <c r="F91" s="6" t="s">
+      <c r="F91" s="5" t="s">
         <v>59</v>
       </c>
     </row>
@@ -2598,13 +2656,13 @@
       <c r="C92" s="8">
         <v>46055</v>
       </c>
-      <c r="D92" s="21">
+      <c r="D92" s="25">
         <v>17</v>
       </c>
       <c r="E92" s="4">
         <v>17</v>
       </c>
-      <c r="F92" s="6" t="s">
+      <c r="F92" s="5" t="s">
         <v>59</v>
       </c>
     </row>
@@ -2618,11 +2676,11 @@
       <c r="C93" s="8">
         <v>46055</v>
       </c>
-      <c r="D93" s="23"/>
+      <c r="D93" s="26"/>
       <c r="E93" s="4">
         <v>17</v>
       </c>
-      <c r="F93" s="6" t="s">
+      <c r="F93" s="5" t="s">
         <v>60</v>
       </c>
     </row>
@@ -2636,11 +2694,11 @@
       <c r="C94" s="8">
         <v>46055</v>
       </c>
-      <c r="D94" s="23"/>
+      <c r="D94" s="26"/>
       <c r="E94" s="4">
         <v>17</v>
       </c>
-      <c r="F94" s="6" t="s">
+      <c r="F94" s="5" t="s">
         <v>58</v>
       </c>
     </row>
@@ -2654,11 +2712,11 @@
       <c r="C95" s="8">
         <v>46055</v>
       </c>
-      <c r="D95" s="22"/>
+      <c r="D95" s="27"/>
       <c r="E95" s="4">
         <v>17</v>
       </c>
-      <c r="F95" s="6" t="s">
+      <c r="F95" s="5" t="s">
         <v>61</v>
       </c>
     </row>
@@ -2672,13 +2730,13 @@
       <c r="C96" s="8">
         <v>46055</v>
       </c>
-      <c r="D96" s="24">
+      <c r="D96" s="28">
         <v>51</v>
       </c>
       <c r="E96" s="4">
         <v>51</v>
       </c>
-      <c r="F96" s="6" t="s">
+      <c r="F96" s="5" t="s">
         <v>58</v>
       </c>
     </row>
@@ -2692,11 +2750,11 @@
       <c r="C97" s="8">
         <v>46055</v>
       </c>
-      <c r="D97" s="25"/>
+      <c r="D97" s="29"/>
       <c r="E97" s="4">
         <v>51</v>
       </c>
-      <c r="F97" s="6" t="s">
+      <c r="F97" s="5" t="s">
         <v>61</v>
       </c>
     </row>
@@ -2710,11 +2768,11 @@
       <c r="C98" s="8">
         <v>46055</v>
       </c>
-      <c r="D98" s="26"/>
+      <c r="D98" s="30"/>
       <c r="E98" s="4">
         <v>51</v>
       </c>
-      <c r="F98" s="6" t="s">
+      <c r="F98" s="5" t="s">
         <v>62</v>
       </c>
     </row>
@@ -2728,13 +2786,13 @@
       <c r="C99" s="8">
         <v>46055</v>
       </c>
-      <c r="D99" s="24">
+      <c r="D99" s="28">
         <v>78</v>
       </c>
       <c r="E99" s="4">
         <v>78</v>
       </c>
-      <c r="F99" s="6" t="s">
+      <c r="F99" s="5" t="s">
         <v>58</v>
       </c>
     </row>
@@ -2748,11 +2806,11 @@
       <c r="C100" s="8">
         <v>46055</v>
       </c>
-      <c r="D100" s="25"/>
+      <c r="D100" s="29"/>
       <c r="E100" s="4">
         <v>78</v>
       </c>
-      <c r="F100" s="6" t="s">
+      <c r="F100" s="5" t="s">
         <v>61</v>
       </c>
     </row>
@@ -2766,11 +2824,11 @@
       <c r="C101" s="8">
         <v>46055</v>
       </c>
-      <c r="D101" s="26"/>
+      <c r="D101" s="30"/>
       <c r="E101" s="4">
         <v>78</v>
       </c>
-      <c r="F101" s="6" t="s">
+      <c r="F101" s="5" t="s">
         <v>62</v>
       </c>
     </row>
@@ -2784,13 +2842,13 @@
       <c r="C102" s="8">
         <v>46057</v>
       </c>
-      <c r="D102" s="32">
+      <c r="D102" s="31">
         <v>21</v>
       </c>
       <c r="E102" s="11">
         <v>21</v>
       </c>
-      <c r="F102" s="6" t="s">
+      <c r="F102" s="5" t="s">
         <v>58</v>
       </c>
     </row>
@@ -2804,11 +2862,11 @@
       <c r="C103" s="8">
         <v>46057</v>
       </c>
-      <c r="D103" s="32"/>
+      <c r="D103" s="31"/>
       <c r="E103" s="11">
         <v>21</v>
       </c>
-      <c r="F103" s="6" t="s">
+      <c r="F103" s="5" t="s">
         <v>61</v>
       </c>
     </row>
@@ -2822,11 +2880,11 @@
       <c r="C104" s="8">
         <v>46057</v>
       </c>
-      <c r="D104" s="32"/>
+      <c r="D104" s="31"/>
       <c r="E104" s="11">
         <v>21</v>
       </c>
-      <c r="F104" s="6" t="s">
+      <c r="F104" s="5" t="s">
         <v>62</v>
       </c>
     </row>
@@ -2840,11 +2898,11 @@
       <c r="C105" s="8">
         <v>46057</v>
       </c>
-      <c r="D105" s="32"/>
+      <c r="D105" s="31"/>
       <c r="E105" s="11">
         <v>2</v>
       </c>
-      <c r="F105" s="14" t="s">
+      <c r="F105" s="12" t="s">
         <v>72</v>
       </c>
     </row>
@@ -2858,11 +2916,11 @@
       <c r="C106" s="8">
         <v>46057</v>
       </c>
-      <c r="D106" s="32"/>
+      <c r="D106" s="31"/>
       <c r="E106" s="11">
         <v>2</v>
       </c>
-      <c r="F106" s="14" t="s">
+      <c r="F106" s="12" t="s">
         <v>81</v>
       </c>
     </row>
@@ -2876,11 +2934,11 @@
       <c r="C107" s="8">
         <v>46057</v>
       </c>
-      <c r="D107" s="32"/>
+      <c r="D107" s="31"/>
       <c r="E107" s="11">
         <v>2</v>
       </c>
-      <c r="F107" s="14" t="s">
+      <c r="F107" s="12" t="s">
         <v>99</v>
       </c>
     </row>
@@ -2894,13 +2952,13 @@
       <c r="C108" s="8">
         <v>46058</v>
       </c>
-      <c r="D108" s="21">
+      <c r="D108" s="25">
         <v>10</v>
       </c>
       <c r="E108" s="4">
         <v>10</v>
       </c>
-      <c r="F108" s="6" t="s">
+      <c r="F108" s="5" t="s">
         <v>58</v>
       </c>
     </row>
@@ -2914,11 +2972,11 @@
       <c r="C109" s="8">
         <v>46058</v>
       </c>
-      <c r="D109" s="23"/>
+      <c r="D109" s="26"/>
       <c r="E109" s="4">
         <v>10</v>
       </c>
-      <c r="F109" s="6" t="s">
+      <c r="F109" s="5" t="s">
         <v>61</v>
       </c>
     </row>
@@ -2932,11 +2990,11 @@
       <c r="C110" s="8">
         <v>46058</v>
       </c>
-      <c r="D110" s="22"/>
+      <c r="D110" s="27"/>
       <c r="E110" s="4">
         <v>10</v>
       </c>
-      <c r="F110" s="6" t="s">
+      <c r="F110" s="5" t="s">
         <v>62</v>
       </c>
     </row>
@@ -2950,13 +3008,13 @@
       <c r="C111" s="8">
         <v>46058</v>
       </c>
-      <c r="D111" s="21">
+      <c r="D111" s="25">
         <v>35</v>
       </c>
       <c r="E111" s="4">
         <v>35</v>
       </c>
-      <c r="F111" s="6" t="s">
+      <c r="F111" s="5" t="s">
         <v>58</v>
       </c>
     </row>
@@ -2970,11 +3028,11 @@
       <c r="C112" s="8">
         <v>46058</v>
       </c>
-      <c r="D112" s="23"/>
+      <c r="D112" s="26"/>
       <c r="E112" s="4">
         <v>35</v>
       </c>
-      <c r="F112" s="6" t="s">
+      <c r="F112" s="5" t="s">
         <v>61</v>
       </c>
     </row>
@@ -2988,11 +3046,11 @@
       <c r="C113" s="8">
         <v>46058</v>
       </c>
-      <c r="D113" s="23"/>
+      <c r="D113" s="26"/>
       <c r="E113" s="4">
         <v>35</v>
       </c>
-      <c r="F113" s="6" t="s">
+      <c r="F113" s="5" t="s">
         <v>62</v>
       </c>
     </row>
@@ -3006,11 +3064,11 @@
       <c r="C114" s="8">
         <v>46058</v>
       </c>
-      <c r="D114" s="23"/>
+      <c r="D114" s="26"/>
       <c r="E114" s="4">
         <v>35</v>
       </c>
-      <c r="F114" s="6" t="s">
+      <c r="F114" s="5" t="s">
         <v>60</v>
       </c>
     </row>
@@ -3024,11 +3082,11 @@
       <c r="C115" s="8">
         <v>46058</v>
       </c>
-      <c r="D115" s="23"/>
+      <c r="D115" s="26"/>
       <c r="E115" s="4">
         <v>35</v>
       </c>
-      <c r="F115" s="6" t="s">
+      <c r="F115" s="5" t="s">
         <v>59</v>
       </c>
     </row>
@@ -3042,11 +3100,11 @@
       <c r="C116" s="8">
         <v>46058</v>
       </c>
-      <c r="D116" s="23"/>
+      <c r="D116" s="26"/>
       <c r="E116" s="4">
         <v>35</v>
       </c>
-      <c r="F116" s="6" t="s">
+      <c r="F116" s="5" t="s">
         <v>81</v>
       </c>
     </row>
@@ -3060,11 +3118,11 @@
       <c r="C117" s="8">
         <v>46058</v>
       </c>
-      <c r="D117" s="23"/>
+      <c r="D117" s="26"/>
       <c r="E117" s="4">
         <v>35</v>
       </c>
-      <c r="F117" s="6" t="s">
+      <c r="F117" s="5" t="s">
         <v>84</v>
       </c>
     </row>
@@ -3078,11 +3136,11 @@
       <c r="C118" s="8">
         <v>46058</v>
       </c>
-      <c r="D118" s="23"/>
+      <c r="D118" s="26"/>
       <c r="E118" s="4">
         <v>35</v>
       </c>
-      <c r="F118" s="6" t="s">
+      <c r="F118" s="5" t="s">
         <v>66</v>
       </c>
     </row>
@@ -3096,11 +3154,11 @@
       <c r="C119" s="8">
         <v>46058</v>
       </c>
-      <c r="D119" s="23"/>
+      <c r="D119" s="26"/>
       <c r="E119" s="4">
         <v>35</v>
       </c>
-      <c r="F119" s="6" t="s">
+      <c r="F119" s="5" t="s">
         <v>85</v>
       </c>
     </row>
@@ -3114,9 +3172,9 @@
       <c r="C120" s="8">
         <v>46058</v>
       </c>
-      <c r="D120" s="22"/>
+      <c r="D120" s="27"/>
       <c r="E120" s="4"/>
-      <c r="F120" s="6" t="s">
+      <c r="F120" s="5" t="s">
         <v>72</v>
       </c>
     </row>
@@ -3130,13 +3188,13 @@
       <c r="C121" s="8">
         <v>46058</v>
       </c>
-      <c r="D121" s="21">
+      <c r="D121" s="25">
         <v>12</v>
       </c>
       <c r="E121" s="4">
         <v>12</v>
       </c>
-      <c r="F121" s="6" t="s">
+      <c r="F121" s="5" t="s">
         <v>58</v>
       </c>
     </row>
@@ -3150,11 +3208,11 @@
       <c r="C122" s="8">
         <v>46058</v>
       </c>
-      <c r="D122" s="23"/>
+      <c r="D122" s="26"/>
       <c r="E122" s="4">
         <v>12</v>
       </c>
-      <c r="F122" s="6" t="s">
+      <c r="F122" s="5" t="s">
         <v>73</v>
       </c>
     </row>
@@ -3168,11 +3226,11 @@
       <c r="C123" s="8">
         <v>46058</v>
       </c>
-      <c r="D123" s="23"/>
+      <c r="D123" s="26"/>
       <c r="E123" s="4">
         <v>12</v>
       </c>
-      <c r="F123" s="6" t="s">
+      <c r="F123" s="5" t="s">
         <v>85</v>
       </c>
     </row>
@@ -3186,11 +3244,11 @@
       <c r="C124" s="8">
         <v>46058</v>
       </c>
-      <c r="D124" s="23"/>
+      <c r="D124" s="26"/>
       <c r="E124" s="4">
         <v>12</v>
       </c>
-      <c r="F124" s="6" t="s">
+      <c r="F124" s="5" t="s">
         <v>81</v>
       </c>
     </row>
@@ -3204,11 +3262,11 @@
       <c r="C125" s="8">
         <v>46058</v>
       </c>
-      <c r="D125" s="22"/>
+      <c r="D125" s="27"/>
       <c r="E125" s="4">
         <v>12</v>
       </c>
-      <c r="F125" s="6" t="s">
+      <c r="F125" s="5" t="s">
         <v>84</v>
       </c>
     </row>
@@ -3222,13 +3280,13 @@
       <c r="C126" s="8">
         <v>46055</v>
       </c>
-      <c r="D126" s="24">
+      <c r="D126" s="28">
         <v>11</v>
       </c>
       <c r="E126" s="4">
         <v>11</v>
       </c>
-      <c r="F126" s="6" t="s">
+      <c r="F126" s="5" t="s">
         <v>63</v>
       </c>
     </row>
@@ -3242,11 +3300,11 @@
       <c r="C127" s="8">
         <v>46055</v>
       </c>
-      <c r="D127" s="26"/>
+      <c r="D127" s="30"/>
       <c r="E127" s="4">
         <v>2</v>
       </c>
-      <c r="F127" s="6" t="s">
+      <c r="F127" s="5" t="s">
         <v>64</v>
       </c>
     </row>
@@ -3260,13 +3318,13 @@
       <c r="C128" s="8">
         <v>46059</v>
       </c>
-      <c r="D128" s="21">
+      <c r="D128" s="25">
         <v>4</v>
       </c>
       <c r="E128" s="4">
         <v>4</v>
       </c>
-      <c r="F128" s="6" t="s">
+      <c r="F128" s="5" t="s">
         <v>84</v>
       </c>
     </row>
@@ -3280,11 +3338,11 @@
       <c r="C129" s="8">
         <v>46059</v>
       </c>
-      <c r="D129" s="23"/>
+      <c r="D129" s="26"/>
       <c r="E129" s="4">
         <v>4</v>
       </c>
-      <c r="F129" s="6" t="s">
+      <c r="F129" s="5" t="s">
         <v>85</v>
       </c>
     </row>
@@ -3298,11 +3356,11 @@
       <c r="C130" s="8">
         <v>46059</v>
       </c>
-      <c r="D130" s="23"/>
+      <c r="D130" s="26"/>
       <c r="E130" s="4">
         <v>4</v>
       </c>
-      <c r="F130" s="6" t="s">
+      <c r="F130" s="5" t="s">
         <v>73</v>
       </c>
     </row>
@@ -3316,11 +3374,11 @@
       <c r="C131" s="8">
         <v>46059</v>
       </c>
-      <c r="D131" s="22"/>
+      <c r="D131" s="27"/>
       <c r="E131" s="4">
         <v>4</v>
       </c>
-      <c r="F131" s="6" t="s">
+      <c r="F131" s="5" t="s">
         <v>58</v>
       </c>
     </row>
@@ -3334,13 +3392,13 @@
       <c r="C132" s="8">
         <v>46059</v>
       </c>
-      <c r="D132" s="21">
+      <c r="D132" s="25">
         <v>20</v>
       </c>
       <c r="E132" s="4">
         <v>20</v>
       </c>
-      <c r="F132" s="6" t="s">
+      <c r="F132" s="5" t="s">
         <v>84</v>
       </c>
     </row>
@@ -3354,11 +3412,11 @@
       <c r="C133" s="8">
         <v>46059</v>
       </c>
-      <c r="D133" s="23"/>
+      <c r="D133" s="26"/>
       <c r="E133" s="4">
         <v>20</v>
       </c>
-      <c r="F133" s="6" t="s">
+      <c r="F133" s="5" t="s">
         <v>85</v>
       </c>
     </row>
@@ -3372,11 +3430,11 @@
       <c r="C134" s="8">
         <v>46059</v>
       </c>
-      <c r="D134" s="23"/>
+      <c r="D134" s="26"/>
       <c r="E134" s="4">
         <v>20</v>
       </c>
-      <c r="F134" s="6" t="s">
+      <c r="F134" s="5" t="s">
         <v>59</v>
       </c>
     </row>
@@ -3390,11 +3448,11 @@
       <c r="C135" s="8">
         <v>46059</v>
       </c>
-      <c r="D135" s="22"/>
+      <c r="D135" s="27"/>
       <c r="E135" s="4">
         <v>20</v>
       </c>
-      <c r="F135" s="6" t="s">
+      <c r="F135" s="5" t="s">
         <v>58</v>
       </c>
     </row>
@@ -3408,13 +3466,13 @@
       <c r="C136" s="8">
         <v>46065</v>
       </c>
-      <c r="D136" s="21">
+      <c r="D136" s="25">
         <v>16</v>
       </c>
       <c r="E136" s="4">
         <v>16</v>
       </c>
-      <c r="F136" s="6" t="s">
+      <c r="F136" s="5" t="s">
         <v>60</v>
       </c>
     </row>
@@ -3428,11 +3486,11 @@
       <c r="C137" s="8">
         <v>46065</v>
       </c>
-      <c r="D137" s="23"/>
+      <c r="D137" s="26"/>
       <c r="E137" s="4">
         <v>16</v>
       </c>
-      <c r="F137" s="6" t="s">
+      <c r="F137" s="5" t="s">
         <v>81</v>
       </c>
     </row>
@@ -3446,11 +3504,11 @@
       <c r="C138" s="8">
         <v>46065</v>
       </c>
-      <c r="D138" s="23"/>
+      <c r="D138" s="26"/>
       <c r="E138" s="4">
         <v>16</v>
       </c>
-      <c r="F138" s="6" t="s">
+      <c r="F138" s="5" t="s">
         <v>61</v>
       </c>
     </row>
@@ -3464,11 +3522,11 @@
       <c r="C139" s="8">
         <v>46065</v>
       </c>
-      <c r="D139" s="23"/>
+      <c r="D139" s="26"/>
       <c r="E139" s="4">
         <v>16</v>
       </c>
-      <c r="F139" s="6" t="s">
+      <c r="F139" s="5" t="s">
         <v>58</v>
       </c>
     </row>
@@ -3482,11 +3540,11 @@
       <c r="C140" s="8">
         <v>46065</v>
       </c>
-      <c r="D140" s="23"/>
+      <c r="D140" s="26"/>
       <c r="E140" s="4">
         <v>16</v>
       </c>
-      <c r="F140" s="6" t="s">
+      <c r="F140" s="5" t="s">
         <v>62</v>
       </c>
     </row>
@@ -3500,11 +3558,11 @@
       <c r="C141" s="8">
         <v>46065</v>
       </c>
-      <c r="D141" s="23"/>
+      <c r="D141" s="26"/>
       <c r="E141" s="4">
         <v>15</v>
       </c>
-      <c r="F141" s="6" t="s">
+      <c r="F141" s="5" t="s">
         <v>59</v>
       </c>
     </row>
@@ -3518,11 +3576,11 @@
       <c r="C142" s="8">
         <v>46065</v>
       </c>
-      <c r="D142" s="23"/>
+      <c r="D142" s="26"/>
       <c r="E142" s="4">
         <v>16</v>
       </c>
-      <c r="F142" s="6" t="s">
+      <c r="F142" s="5" t="s">
         <v>66</v>
       </c>
     </row>
@@ -3536,11 +3594,11 @@
       <c r="C143" s="8">
         <v>46065</v>
       </c>
-      <c r="D143" s="23"/>
+      <c r="D143" s="26"/>
       <c r="E143" s="4">
         <v>15</v>
       </c>
-      <c r="F143" s="6" t="s">
+      <c r="F143" s="5" t="s">
         <v>72</v>
       </c>
     </row>
@@ -3554,11 +3612,11 @@
       <c r="C144" s="8">
         <v>46065</v>
       </c>
-      <c r="D144" s="23"/>
+      <c r="D144" s="26"/>
       <c r="E144" s="4">
         <v>16</v>
       </c>
-      <c r="F144" s="6" t="s">
+      <c r="F144" s="5" t="s">
         <v>92</v>
       </c>
     </row>
@@ -3572,11 +3630,11 @@
       <c r="C145" s="8">
         <v>46065</v>
       </c>
-      <c r="D145" s="22"/>
+      <c r="D145" s="27"/>
       <c r="E145" s="4">
         <v>16</v>
       </c>
-      <c r="F145" s="6" t="s">
+      <c r="F145" s="5" t="s">
         <v>83</v>
       </c>
     </row>
@@ -3590,13 +3648,13 @@
       <c r="C146" s="8">
         <v>46066</v>
       </c>
-      <c r="D146" s="30">
+      <c r="D146" s="35">
         <v>5</v>
       </c>
       <c r="E146" s="4">
         <v>5</v>
       </c>
-      <c r="F146" s="6" t="s">
+      <c r="F146" s="5" t="s">
         <v>59</v>
       </c>
     </row>
@@ -3610,11 +3668,11 @@
       <c r="C147" s="8">
         <v>46066</v>
       </c>
-      <c r="D147" s="31"/>
+      <c r="D147" s="36"/>
       <c r="E147" s="4">
         <v>5</v>
       </c>
-      <c r="F147" s="6" t="s">
+      <c r="F147" s="5" t="s">
         <v>60</v>
       </c>
     </row>
@@ -3628,13 +3686,13 @@
       <c r="C148" s="8">
         <v>46069</v>
       </c>
-      <c r="D148" s="16">
+      <c r="D148" s="21">
         <v>1</v>
       </c>
       <c r="E148" s="4">
         <v>1</v>
       </c>
-      <c r="F148" s="6" t="s">
+      <c r="F148" s="5" t="s">
         <v>94</v>
       </c>
     </row>
@@ -3648,13 +3706,13 @@
       <c r="C149" s="8">
         <v>46068</v>
       </c>
-      <c r="D149" s="21">
+      <c r="D149" s="25">
         <v>21</v>
       </c>
       <c r="E149" s="4">
         <v>21</v>
       </c>
-      <c r="F149" s="6" t="s">
+      <c r="F149" s="5" t="s">
         <v>59</v>
       </c>
     </row>
@@ -3668,11 +3726,11 @@
       <c r="C150" s="8">
         <v>46068</v>
       </c>
-      <c r="D150" s="23"/>
+      <c r="D150" s="26"/>
       <c r="E150" s="4">
         <v>21</v>
       </c>
-      <c r="F150" s="6" t="s">
+      <c r="F150" s="5" t="s">
         <v>61</v>
       </c>
     </row>
@@ -3686,11 +3744,11 @@
       <c r="C151" s="8">
         <v>46068</v>
       </c>
-      <c r="D151" s="23"/>
+      <c r="D151" s="26"/>
       <c r="E151" s="4">
         <v>21</v>
       </c>
-      <c r="F151" s="6" t="s">
+      <c r="F151" s="5" t="s">
         <v>58</v>
       </c>
     </row>
@@ -3704,11 +3762,11 @@
       <c r="C152" s="8">
         <v>46068</v>
       </c>
-      <c r="D152" s="23"/>
+      <c r="D152" s="26"/>
       <c r="E152" s="4">
         <v>21</v>
       </c>
-      <c r="F152" s="6" t="s">
+      <c r="F152" s="5" t="s">
         <v>62</v>
       </c>
     </row>
@@ -3722,11 +3780,11 @@
       <c r="C153" s="8">
         <v>46068</v>
       </c>
-      <c r="D153" s="23"/>
+      <c r="D153" s="26"/>
       <c r="E153" s="4">
         <v>21</v>
       </c>
-      <c r="F153" s="6" t="s">
+      <c r="F153" s="5" t="s">
         <v>60</v>
       </c>
     </row>
@@ -3740,11 +3798,11 @@
       <c r="C154" s="8">
         <v>46068</v>
       </c>
-      <c r="D154" s="23"/>
+      <c r="D154" s="26"/>
       <c r="E154" s="4">
         <v>21</v>
       </c>
-      <c r="F154" s="6" t="s">
+      <c r="F154" s="5" t="s">
         <v>95</v>
       </c>
     </row>
@@ -3758,11 +3816,11 @@
       <c r="C155" s="8">
         <v>46068</v>
       </c>
-      <c r="D155" s="23"/>
+      <c r="D155" s="26"/>
       <c r="E155" s="4">
         <v>21</v>
       </c>
-      <c r="F155" s="6" t="s">
+      <c r="F155" s="5" t="s">
         <v>96</v>
       </c>
     </row>
@@ -3776,11 +3834,11 @@
       <c r="C156" s="8">
         <v>46068</v>
       </c>
-      <c r="D156" s="23"/>
+      <c r="D156" s="26"/>
       <c r="E156" s="4">
         <v>21</v>
       </c>
-      <c r="F156" s="6" t="s">
+      <c r="F156" s="5" t="s">
         <v>100</v>
       </c>
     </row>
@@ -3794,11 +3852,11 @@
       <c r="C157" s="8">
         <v>46068</v>
       </c>
-      <c r="D157" s="22"/>
+      <c r="D157" s="27"/>
       <c r="E157" s="4">
         <v>21</v>
       </c>
-      <c r="F157" s="6" t="s">
+      <c r="F157" s="5" t="s">
         <v>84</v>
       </c>
     </row>
@@ -3812,13 +3870,13 @@
       <c r="C158" s="8">
         <v>46068</v>
       </c>
-      <c r="D158" s="24">
+      <c r="D158" s="28">
         <v>13</v>
       </c>
       <c r="E158" s="4">
         <v>13</v>
       </c>
-      <c r="F158" s="6" t="s">
+      <c r="F158" s="5" t="s">
         <v>59</v>
       </c>
     </row>
@@ -3832,11 +3890,11 @@
       <c r="C159" s="8">
         <v>46068</v>
       </c>
-      <c r="D159" s="26"/>
+      <c r="D159" s="30"/>
       <c r="E159" s="4">
         <v>13</v>
       </c>
-      <c r="F159" s="6" t="s">
+      <c r="F159" s="5" t="s">
         <v>58</v>
       </c>
     </row>
@@ -3850,13 +3908,13 @@
       <c r="C160" s="8">
         <v>46069</v>
       </c>
-      <c r="D160" s="21">
+      <c r="D160" s="25">
         <v>24</v>
       </c>
       <c r="E160" s="4">
         <v>24</v>
       </c>
-      <c r="F160" s="6" t="s">
+      <c r="F160" s="5" t="s">
         <v>59</v>
       </c>
     </row>
@@ -3870,11 +3928,11 @@
       <c r="C161" s="8">
         <v>46069</v>
       </c>
-      <c r="D161" s="23"/>
+      <c r="D161" s="26"/>
       <c r="E161" s="4">
         <v>24</v>
       </c>
-      <c r="F161" s="6" t="s">
+      <c r="F161" s="5" t="s">
         <v>58</v>
       </c>
     </row>
@@ -3888,11 +3946,11 @@
       <c r="C162" s="8">
         <v>46069</v>
       </c>
-      <c r="D162" s="23"/>
+      <c r="D162" s="26"/>
       <c r="E162" s="4">
         <v>24</v>
       </c>
-      <c r="F162" s="6" t="s">
+      <c r="F162" s="5" t="s">
         <v>62</v>
       </c>
     </row>
@@ -3906,11 +3964,11 @@
       <c r="C163" s="8">
         <v>46069</v>
       </c>
-      <c r="D163" s="23"/>
+      <c r="D163" s="26"/>
       <c r="E163" s="4">
         <v>24</v>
       </c>
-      <c r="F163" s="6" t="s">
+      <c r="F163" s="5" t="s">
         <v>100</v>
       </c>
     </row>
@@ -3924,11 +3982,11 @@
       <c r="C164" s="8">
         <v>46069</v>
       </c>
-      <c r="D164" s="23"/>
+      <c r="D164" s="26"/>
       <c r="E164" s="4">
         <v>24</v>
       </c>
-      <c r="F164" s="6" t="s">
+      <c r="F164" s="5" t="s">
         <v>60</v>
       </c>
     </row>
@@ -3942,87 +4000,87 @@
       <c r="C165" s="8">
         <v>46069</v>
       </c>
-      <c r="D165" s="22"/>
+      <c r="D165" s="27"/>
       <c r="E165" s="4">
         <v>24</v>
       </c>
-      <c r="F165" s="6" t="s">
+      <c r="F165" s="5" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A166" s="17">
+      <c r="A166" s="15">
         <v>368</v>
       </c>
       <c r="B166" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="C166" s="19">
+      <c r="C166" s="17">
         <v>46069</v>
       </c>
-      <c r="D166" s="27">
+      <c r="D166" s="32">
         <v>9</v>
       </c>
-      <c r="E166" s="17">
+      <c r="E166" s="15">
         <v>9</v>
       </c>
-      <c r="F166" s="18" t="s">
+      <c r="F166" s="22" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A167" s="17">
+      <c r="A167" s="15">
         <v>368</v>
       </c>
       <c r="B167" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="C167" s="19">
+      <c r="C167" s="17">
         <v>46069</v>
       </c>
-      <c r="D167" s="28"/>
-      <c r="E167" s="17">
+      <c r="D167" s="33"/>
+      <c r="E167" s="15">
         <v>9</v>
       </c>
-      <c r="F167" s="18" t="s">
+      <c r="F167" s="22" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A168" s="17">
+      <c r="A168" s="15">
         <v>368</v>
       </c>
       <c r="B168" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="C168" s="19">
+      <c r="C168" s="17">
         <v>46069</v>
       </c>
-      <c r="D168" s="29"/>
-      <c r="E168" s="17">
+      <c r="D168" s="34"/>
+      <c r="E168" s="15">
         <v>9</v>
       </c>
-      <c r="F168" s="18" t="s">
+      <c r="F168" s="22" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A169" s="17">
+      <c r="A169" s="15">
         <v>369</v>
       </c>
-      <c r="B169" s="18" t="s">
+      <c r="B169" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="C169" s="19">
+      <c r="C169" s="17">
         <v>46069</v>
       </c>
-      <c r="D169" s="17">
+      <c r="D169" s="15">
         <v>4</v>
       </c>
-      <c r="E169" s="17">
+      <c r="E169" s="15">
         <v>4</v>
       </c>
-      <c r="F169" s="18" t="s">
+      <c r="F169" s="22" t="s">
         <v>75</v>
       </c>
     </row>
@@ -4036,13 +4094,13 @@
       <c r="C170" s="8">
         <v>46069</v>
       </c>
-      <c r="D170" s="21">
+      <c r="D170" s="25">
         <v>3</v>
       </c>
       <c r="E170" s="4">
         <v>3</v>
       </c>
-      <c r="F170" s="6" t="s">
+      <c r="F170" s="5" t="s">
         <v>63</v>
       </c>
     </row>
@@ -4056,11 +4114,11 @@
       <c r="C171" s="8">
         <v>46069</v>
       </c>
-      <c r="D171" s="23"/>
+      <c r="D171" s="26"/>
       <c r="E171" s="4">
         <v>3</v>
       </c>
-      <c r="F171" s="6" t="s">
+      <c r="F171" s="5" t="s">
         <v>64</v>
       </c>
     </row>
@@ -4074,11 +4132,11 @@
       <c r="C172" s="8">
         <v>46069</v>
       </c>
-      <c r="D172" s="23"/>
+      <c r="D172" s="26"/>
       <c r="E172" s="4">
         <v>1</v>
       </c>
-      <c r="F172" s="6" t="s">
+      <c r="F172" s="5" t="s">
         <v>68</v>
       </c>
     </row>
@@ -4092,11 +4150,11 @@
       <c r="C173" s="8">
         <v>46069</v>
       </c>
-      <c r="D173" s="22"/>
+      <c r="D173" s="27"/>
       <c r="E173" s="4">
         <v>1</v>
       </c>
-      <c r="F173" s="6" t="s">
+      <c r="F173" s="5" t="s">
         <v>74</v>
       </c>
     </row>
@@ -4110,13 +4168,13 @@
       <c r="C174" s="8">
         <v>46070</v>
       </c>
-      <c r="D174" s="21">
+      <c r="D174" s="25">
         <v>10</v>
       </c>
       <c r="E174" s="4">
         <v>10</v>
       </c>
-      <c r="F174" s="6" t="s">
+      <c r="F174" s="5" t="s">
         <v>58</v>
       </c>
     </row>
@@ -4130,11 +4188,11 @@
       <c r="C175" s="8">
         <v>46070</v>
       </c>
-      <c r="D175" s="23"/>
+      <c r="D175" s="26"/>
       <c r="E175" s="4">
         <v>10</v>
       </c>
-      <c r="F175" s="6" t="s">
+      <c r="F175" s="5" t="s">
         <v>62</v>
       </c>
     </row>
@@ -4148,11 +4206,11 @@
       <c r="C176" s="8">
         <v>46070</v>
       </c>
-      <c r="D176" s="22"/>
+      <c r="D176" s="27"/>
       <c r="E176" s="4">
         <v>10</v>
       </c>
-      <c r="F176" s="6" t="s">
+      <c r="F176" s="5" t="s">
         <v>82</v>
       </c>
     </row>
@@ -4166,13 +4224,13 @@
       <c r="C177" s="8">
         <v>46073</v>
       </c>
-      <c r="D177" s="21">
+      <c r="D177" s="25">
         <v>5</v>
       </c>
       <c r="E177" s="4">
         <v>5</v>
       </c>
-      <c r="F177" s="6" t="s">
+      <c r="F177" s="5" t="s">
         <v>58</v>
       </c>
     </row>
@@ -4186,11 +4244,11 @@
       <c r="C178" s="8">
         <v>46073</v>
       </c>
-      <c r="D178" s="23"/>
+      <c r="D178" s="26"/>
       <c r="E178" s="4">
         <v>5</v>
       </c>
-      <c r="F178" s="6" t="s">
+      <c r="F178" s="5" t="s">
         <v>62</v>
       </c>
     </row>
@@ -4204,11 +4262,11 @@
       <c r="C179" s="8">
         <v>46073</v>
       </c>
-      <c r="D179" s="22"/>
+      <c r="D179" s="27"/>
       <c r="E179" s="4">
         <v>5</v>
       </c>
-      <c r="F179" s="6" t="s">
+      <c r="F179" s="5" t="s">
         <v>61</v>
       </c>
     </row>
@@ -4222,13 +4280,13 @@
       <c r="C180" s="8">
         <v>46073</v>
       </c>
-      <c r="D180" s="21">
+      <c r="D180" s="25">
         <v>2</v>
       </c>
       <c r="E180" s="4">
         <v>2</v>
       </c>
-      <c r="F180" s="6" t="s">
+      <c r="F180" s="5" t="s">
         <v>58</v>
       </c>
     </row>
@@ -4242,11 +4300,11 @@
       <c r="C181" s="8">
         <v>46073</v>
       </c>
-      <c r="D181" s="23"/>
+      <c r="D181" s="26"/>
       <c r="E181" s="4">
         <v>2</v>
       </c>
-      <c r="F181" s="6" t="s">
+      <c r="F181" s="5" t="s">
         <v>62</v>
       </c>
     </row>
@@ -4260,11 +4318,11 @@
       <c r="C182" s="8">
         <v>46073</v>
       </c>
-      <c r="D182" s="22"/>
+      <c r="D182" s="27"/>
       <c r="E182" s="4">
         <v>2</v>
       </c>
-      <c r="F182" s="6" t="s">
+      <c r="F182" s="5" t="s">
         <v>61</v>
       </c>
     </row>
@@ -4278,13 +4336,13 @@
       <c r="C183" s="8">
         <v>46073</v>
       </c>
-      <c r="D183" s="21">
+      <c r="D183" s="25">
         <v>24</v>
       </c>
       <c r="E183" s="4">
         <v>24</v>
       </c>
-      <c r="F183" s="6" t="s">
+      <c r="F183" s="5" t="s">
         <v>58</v>
       </c>
     </row>
@@ -4298,11 +4356,11 @@
       <c r="C184" s="8">
         <v>46073</v>
       </c>
-      <c r="D184" s="23"/>
+      <c r="D184" s="26"/>
       <c r="E184" s="4">
         <v>24</v>
       </c>
-      <c r="F184" s="6" t="s">
+      <c r="F184" s="5" t="s">
         <v>62</v>
       </c>
     </row>
@@ -4316,11 +4374,11 @@
       <c r="C185" s="8">
         <v>46073</v>
       </c>
-      <c r="D185" s="22"/>
+      <c r="D185" s="27"/>
       <c r="E185" s="4">
         <v>24</v>
       </c>
-      <c r="F185" s="6" t="s">
+      <c r="F185" s="5" t="s">
         <v>61</v>
       </c>
     </row>
@@ -4334,16 +4392,16 @@
       <c r="C186" s="8">
         <v>46073</v>
       </c>
-      <c r="D186" s="21">
+      <c r="D186" s="25">
         <v>6</v>
       </c>
       <c r="E186" s="4">
         <v>1</v>
       </c>
-      <c r="F186" s="6" t="s">
+      <c r="F186" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="G186" s="20" t="s">
+      <c r="G186" s="18" t="s">
         <v>105</v>
       </c>
     </row>
@@ -4357,11 +4415,11 @@
       <c r="C187" s="8">
         <v>46073</v>
       </c>
-      <c r="D187" s="23"/>
+      <c r="D187" s="26"/>
       <c r="E187" s="4">
         <v>5</v>
       </c>
-      <c r="F187" s="6" t="s">
+      <c r="F187" s="5" t="s">
         <v>106</v>
       </c>
     </row>
@@ -4375,11 +4433,11 @@
       <c r="C188" s="8">
         <v>46073</v>
       </c>
-      <c r="D188" s="23"/>
+      <c r="D188" s="26"/>
       <c r="E188" s="4">
         <v>6</v>
       </c>
-      <c r="F188" s="6" t="s">
+      <c r="F188" s="5" t="s">
         <v>114</v>
       </c>
     </row>
@@ -4393,11 +4451,11 @@
       <c r="C189" s="8">
         <v>46073</v>
       </c>
-      <c r="D189" s="23"/>
+      <c r="D189" s="26"/>
       <c r="E189" s="4">
         <v>6</v>
       </c>
-      <c r="F189" s="6" t="s">
+      <c r="F189" s="5" t="s">
         <v>107</v>
       </c>
     </row>
@@ -4411,11 +4469,11 @@
       <c r="C190" s="8">
         <v>46073</v>
       </c>
-      <c r="D190" s="23"/>
+      <c r="D190" s="26"/>
       <c r="E190" s="4">
         <v>6</v>
       </c>
-      <c r="F190" s="6" t="s">
+      <c r="F190" s="5" t="s">
         <v>63</v>
       </c>
     </row>
@@ -4429,11 +4487,11 @@
       <c r="C191" s="8">
         <v>46073</v>
       </c>
-      <c r="D191" s="22"/>
+      <c r="D191" s="27"/>
       <c r="E191" s="4">
         <v>6</v>
       </c>
-      <c r="F191" s="6" t="s">
+      <c r="F191" s="5" t="s">
         <v>64</v>
       </c>
     </row>
@@ -4453,7 +4511,7 @@
       <c r="E192" s="4">
         <v>24</v>
       </c>
-      <c r="F192" s="6" t="s">
+      <c r="F192" s="5" t="s">
         <v>59</v>
       </c>
     </row>
@@ -4467,13 +4525,13 @@
       <c r="C193" s="8">
         <v>46076</v>
       </c>
-      <c r="D193" s="21">
+      <c r="D193" s="25">
         <v>22</v>
       </c>
       <c r="E193" s="4">
         <v>22</v>
       </c>
-      <c r="F193" s="6" t="s">
+      <c r="F193" s="5" t="s">
         <v>61</v>
       </c>
     </row>
@@ -4487,11 +4545,11 @@
       <c r="C194" s="8">
         <v>46076</v>
       </c>
-      <c r="D194" s="22"/>
+      <c r="D194" s="27"/>
       <c r="E194" s="4">
         <v>22</v>
       </c>
-      <c r="F194" s="6" t="s">
+      <c r="F194" s="5" t="s">
         <v>62</v>
       </c>
     </row>
@@ -4505,13 +4563,13 @@
       <c r="C195" s="8">
         <v>46077</v>
       </c>
-      <c r="D195" s="21">
+      <c r="D195" s="25">
         <v>4</v>
       </c>
       <c r="E195" s="4">
         <v>3</v>
       </c>
-      <c r="F195" s="6" t="s">
+      <c r="F195" s="5" t="s">
         <v>72</v>
       </c>
     </row>
@@ -4525,11 +4583,11 @@
       <c r="C196" s="8">
         <v>46077</v>
       </c>
-      <c r="D196" s="23"/>
+      <c r="D196" s="26"/>
       <c r="E196" s="4">
         <v>1</v>
       </c>
-      <c r="F196" s="6" t="s">
+      <c r="F196" s="5" t="s">
         <v>109</v>
       </c>
     </row>
@@ -4543,11 +4601,11 @@
       <c r="C197" s="8">
         <v>46077</v>
       </c>
-      <c r="D197" s="23"/>
+      <c r="D197" s="26"/>
       <c r="E197" s="4">
         <v>1</v>
       </c>
-      <c r="F197" s="6" t="s">
+      <c r="F197" s="5" t="s">
         <v>110</v>
       </c>
     </row>
@@ -4561,11 +4619,11 @@
       <c r="C198" s="8">
         <v>46077</v>
       </c>
-      <c r="D198" s="23"/>
+      <c r="D198" s="26"/>
       <c r="E198" s="4">
         <v>1</v>
       </c>
-      <c r="F198" s="6" t="s">
+      <c r="F198" s="5" t="s">
         <v>111</v>
       </c>
     </row>
@@ -4579,11 +4637,11 @@
       <c r="C199" s="8">
         <v>46077</v>
       </c>
-      <c r="D199" s="22"/>
+      <c r="D199" s="27"/>
       <c r="E199" s="4">
         <v>1</v>
       </c>
-      <c r="F199" s="6" t="s">
+      <c r="F199" s="5" t="s">
         <v>112</v>
       </c>
     </row>
@@ -4597,13 +4655,13 @@
       <c r="C200" s="8">
         <v>46076</v>
       </c>
-      <c r="D200" s="21">
+      <c r="D200" s="25">
         <v>1</v>
       </c>
       <c r="E200" s="4">
         <v>1</v>
       </c>
-      <c r="F200" s="6" t="s">
+      <c r="F200" s="5" t="s">
         <v>114</v>
       </c>
     </row>
@@ -4617,11 +4675,11 @@
       <c r="C201" s="8">
         <v>46076</v>
       </c>
-      <c r="D201" s="22"/>
+      <c r="D201" s="27"/>
       <c r="E201" s="4">
         <v>1</v>
       </c>
-      <c r="F201" s="6" t="s">
+      <c r="F201" s="5" t="s">
         <v>63</v>
       </c>
     </row>
@@ -4635,13 +4693,13 @@
       <c r="C202" s="8">
         <v>46080</v>
       </c>
-      <c r="D202" s="21">
+      <c r="D202" s="25">
         <v>34</v>
       </c>
       <c r="E202" s="4">
         <v>34</v>
       </c>
-      <c r="F202" s="6" t="s">
+      <c r="F202" s="5" t="s">
         <v>62</v>
       </c>
     </row>
@@ -4655,11 +4713,11 @@
       <c r="C203" s="8">
         <v>46080</v>
       </c>
-      <c r="D203" s="23"/>
+      <c r="D203" s="26"/>
       <c r="E203" s="4">
         <v>34</v>
       </c>
-      <c r="F203" s="6" t="s">
+      <c r="F203" s="5" t="s">
         <v>58</v>
       </c>
     </row>
@@ -4673,11 +4731,11 @@
       <c r="C204" s="8">
         <v>46080</v>
       </c>
-      <c r="D204" s="22"/>
+      <c r="D204" s="27"/>
       <c r="E204" s="4">
         <v>34</v>
       </c>
-      <c r="F204" s="6" t="s">
+      <c r="F204" s="5" t="s">
         <v>61</v>
       </c>
     </row>
@@ -4691,13 +4749,13 @@
       <c r="C205" s="8">
         <v>46083</v>
       </c>
-      <c r="D205" s="21">
+      <c r="D205" s="25">
         <v>2</v>
       </c>
       <c r="E205" s="4">
         <v>1</v>
       </c>
-      <c r="F205" s="6" t="s">
+      <c r="F205" s="5" t="s">
         <v>118</v>
       </c>
     </row>
@@ -4711,11 +4769,11 @@
       <c r="C206" s="8">
         <v>46083</v>
       </c>
-      <c r="D206" s="23"/>
+      <c r="D206" s="26"/>
       <c r="E206" s="4">
         <v>1</v>
       </c>
-      <c r="F206" s="6" t="s">
+      <c r="F206" s="5" t="s">
         <v>114</v>
       </c>
     </row>
@@ -4729,11 +4787,11 @@
       <c r="C207" s="8">
         <v>46083</v>
       </c>
-      <c r="D207" s="23"/>
+      <c r="D207" s="26"/>
       <c r="E207" s="4">
         <v>1</v>
       </c>
-      <c r="F207" s="6" t="s">
+      <c r="F207" s="5" t="s">
         <v>64</v>
       </c>
     </row>
@@ -4747,11 +4805,11 @@
       <c r="C208" s="8">
         <v>46083</v>
       </c>
-      <c r="D208" s="23"/>
+      <c r="D208" s="26"/>
       <c r="E208" s="4">
         <v>1</v>
       </c>
-      <c r="F208" s="6" t="s">
+      <c r="F208" s="5" t="s">
         <v>63</v>
       </c>
     </row>
@@ -4765,11 +4823,11 @@
       <c r="C209" s="8">
         <v>46083</v>
       </c>
-      <c r="D209" s="22"/>
+      <c r="D209" s="27"/>
       <c r="E209" s="4">
         <v>1</v>
       </c>
-      <c r="F209" s="6" t="s">
+      <c r="F209" s="5" t="s">
         <v>75</v>
       </c>
     </row>
@@ -4783,13 +4841,13 @@
       <c r="C210" s="8">
         <v>46083</v>
       </c>
-      <c r="D210" s="21">
+      <c r="D210" s="25">
         <v>19</v>
       </c>
       <c r="E210" s="4">
         <v>19</v>
       </c>
-      <c r="F210" s="6" t="s">
+      <c r="F210" s="5" t="s">
         <v>62</v>
       </c>
     </row>
@@ -4803,11 +4861,11 @@
       <c r="C211" s="8">
         <v>46083</v>
       </c>
-      <c r="D211" s="23"/>
+      <c r="D211" s="26"/>
       <c r="E211" s="4">
         <v>19</v>
       </c>
-      <c r="F211" s="6" t="s">
+      <c r="F211" s="5" t="s">
         <v>61</v>
       </c>
     </row>
@@ -4821,11 +4879,11 @@
       <c r="C212" s="8">
         <v>46083</v>
       </c>
-      <c r="D212" s="22"/>
+      <c r="D212" s="27"/>
       <c r="E212" s="4">
         <v>19</v>
       </c>
-      <c r="F212" s="6" t="s">
+      <c r="F212" s="5" t="s">
         <v>58</v>
       </c>
     </row>
@@ -4845,7 +4903,7 @@
       <c r="E213" s="4">
         <v>71</v>
       </c>
-      <c r="F213" s="6" t="s">
+      <c r="F213" s="5" t="s">
         <v>72</v>
       </c>
     </row>
@@ -4865,7 +4923,7 @@
       <c r="E214" s="4">
         <v>108</v>
       </c>
-      <c r="F214" s="6" t="s">
+      <c r="F214" s="5" t="s">
         <v>58</v>
       </c>
     </row>
@@ -4885,7 +4943,7 @@
       <c r="E215" s="4">
         <v>2</v>
       </c>
-      <c r="F215" s="6" t="s">
+      <c r="F215" s="5" t="s">
         <v>122</v>
       </c>
     </row>
@@ -4899,13 +4957,13 @@
       <c r="C216" s="8">
         <v>46086</v>
       </c>
-      <c r="D216" s="32">
+      <c r="D216" s="31">
         <v>7</v>
       </c>
       <c r="E216" s="4">
         <v>7</v>
       </c>
-      <c r="F216" s="6" t="s">
+      <c r="F216" s="5" t="s">
         <v>81</v>
       </c>
     </row>
@@ -4919,14 +4977,14 @@
       <c r="C217" s="8">
         <v>46086</v>
       </c>
-      <c r="D217" s="32"/>
+      <c r="D217" s="31"/>
       <c r="E217" s="4">
         <v>7</v>
       </c>
-      <c r="F217" s="33" t="s">
+      <c r="F217" s="23" t="s">
         <v>125</v>
       </c>
-      <c r="G217" s="34" t="s">
+      <c r="G217" s="19" t="s">
         <v>128</v>
       </c>
     </row>
@@ -4940,11 +4998,11 @@
       <c r="C218" s="8">
         <v>46086</v>
       </c>
-      <c r="D218" s="32"/>
+      <c r="D218" s="31"/>
       <c r="E218" s="4">
         <v>7</v>
       </c>
-      <c r="F218" s="6" t="s">
+      <c r="F218" s="5" t="s">
         <v>72</v>
       </c>
     </row>
@@ -4958,11 +5016,11 @@
       <c r="C219" s="8">
         <v>46086</v>
       </c>
-      <c r="D219" s="32"/>
+      <c r="D219" s="31"/>
       <c r="E219" s="4">
         <v>1</v>
       </c>
-      <c r="F219" s="6" t="s">
+      <c r="F219" s="5" t="s">
         <v>127</v>
       </c>
     </row>
@@ -4976,11 +5034,11 @@
       <c r="C220" s="8">
         <v>46086</v>
       </c>
-      <c r="D220" s="32"/>
+      <c r="D220" s="31"/>
       <c r="E220" s="4">
         <v>1</v>
       </c>
-      <c r="F220" s="6" t="s">
+      <c r="F220" s="5" t="s">
         <v>63</v>
       </c>
     </row>
@@ -4994,13 +5052,13 @@
       <c r="C221" s="8">
         <v>46086</v>
       </c>
-      <c r="D221" s="21">
+      <c r="D221" s="25">
         <v>120</v>
       </c>
       <c r="E221" s="4">
         <v>120</v>
       </c>
-      <c r="F221" s="6" t="s">
+      <c r="F221" s="5" t="s">
         <v>81</v>
       </c>
     </row>
@@ -5014,11 +5072,11 @@
       <c r="C222" s="8">
         <v>46086</v>
       </c>
-      <c r="D222" s="23"/>
+      <c r="D222" s="26"/>
       <c r="E222" s="4">
         <v>120</v>
       </c>
-      <c r="F222" s="6" t="s">
+      <c r="F222" s="5" t="s">
         <v>72</v>
       </c>
     </row>
@@ -5032,11 +5090,11 @@
       <c r="C223" s="8">
         <v>46086</v>
       </c>
-      <c r="D223" s="23"/>
+      <c r="D223" s="26"/>
       <c r="E223" s="4">
         <v>120</v>
       </c>
-      <c r="F223" s="6" t="s">
+      <c r="F223" s="5" t="s">
         <v>85</v>
       </c>
     </row>
@@ -5050,11 +5108,11 @@
       <c r="C224" s="8">
         <v>46086</v>
       </c>
-      <c r="D224" s="23"/>
+      <c r="D224" s="26"/>
       <c r="E224" s="4">
         <v>120</v>
       </c>
-      <c r="F224" s="6" t="s">
+      <c r="F224" s="5" t="s">
         <v>125</v>
       </c>
     </row>
@@ -5068,11 +5126,11 @@
       <c r="C225" s="8">
         <v>46086</v>
       </c>
-      <c r="D225" s="23"/>
+      <c r="D225" s="26"/>
       <c r="E225" s="4">
         <v>120</v>
       </c>
-      <c r="F225" s="6" t="s">
+      <c r="F225" s="5" t="s">
         <v>126</v>
       </c>
     </row>
@@ -5086,3137 +5144,3528 @@
       <c r="C226" s="8">
         <v>46086</v>
       </c>
-      <c r="D226" s="22"/>
+      <c r="D226" s="27"/>
       <c r="E226" s="4">
         <v>120</v>
       </c>
-      <c r="F226" s="6" t="s">
+      <c r="F226" s="5" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A227" s="4"/>
-      <c r="B227" s="6"/>
-      <c r="C227" s="13"/>
-      <c r="D227" s="6"/>
-      <c r="E227" s="4"/>
-      <c r="F227" s="6"/>
+      <c r="A227" s="4">
+        <v>388</v>
+      </c>
+      <c r="B227" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="C227" s="8">
+        <v>46087</v>
+      </c>
+      <c r="D227" s="25">
+        <v>7</v>
+      </c>
+      <c r="E227" s="4">
+        <v>7</v>
+      </c>
+      <c r="F227" s="5" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A228" s="4"/>
-      <c r="B228" s="6"/>
-      <c r="C228" s="13"/>
-      <c r="D228" s="6"/>
-      <c r="E228" s="4"/>
-      <c r="F228" s="6"/>
+      <c r="A228" s="4">
+        <v>388</v>
+      </c>
+      <c r="B228" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="C228" s="8">
+        <v>46087</v>
+      </c>
+      <c r="D228" s="26"/>
+      <c r="E228" s="4">
+        <v>7</v>
+      </c>
+      <c r="F228" s="5" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A229" s="4"/>
-      <c r="B229" s="6"/>
-      <c r="C229" s="13"/>
-      <c r="D229" s="6"/>
-      <c r="E229" s="4"/>
-      <c r="F229" s="6"/>
+      <c r="A229" s="4">
+        <v>388</v>
+      </c>
+      <c r="B229" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="C229" s="8">
+        <v>46087</v>
+      </c>
+      <c r="D229" s="27"/>
+      <c r="E229" s="4">
+        <v>7</v>
+      </c>
+      <c r="F229" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A230" s="4"/>
-      <c r="B230" s="6"/>
-      <c r="C230" s="13"/>
-      <c r="D230" s="6"/>
-      <c r="E230" s="4"/>
-      <c r="F230" s="6"/>
+      <c r="A230" s="4">
+        <v>389</v>
+      </c>
+      <c r="B230" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="C230" s="8">
+        <v>46090</v>
+      </c>
+      <c r="D230" s="25">
+        <v>30</v>
+      </c>
+      <c r="E230" s="4">
+        <v>30</v>
+      </c>
+      <c r="F230" s="5" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A231" s="4"/>
-      <c r="B231" s="6"/>
-      <c r="C231" s="13"/>
-      <c r="D231" s="6"/>
-      <c r="E231" s="4"/>
-      <c r="F231" s="6"/>
+      <c r="A231" s="4">
+        <v>389</v>
+      </c>
+      <c r="B231" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="C231" s="8">
+        <v>46090</v>
+      </c>
+      <c r="D231" s="26"/>
+      <c r="E231" s="4">
+        <v>30</v>
+      </c>
+      <c r="F231" s="5" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A232" s="4"/>
-      <c r="B232" s="6"/>
-      <c r="C232" s="13"/>
-      <c r="D232" s="6"/>
-      <c r="E232" s="4"/>
-      <c r="F232" s="6"/>
+      <c r="A232" s="4">
+        <v>389</v>
+      </c>
+      <c r="B232" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="C232" s="8">
+        <v>46090</v>
+      </c>
+      <c r="D232" s="27"/>
+      <c r="E232" s="4">
+        <v>30</v>
+      </c>
+      <c r="F232" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A233" s="4"/>
-      <c r="B233" s="6"/>
-      <c r="C233" s="13"/>
-      <c r="D233" s="6"/>
-      <c r="E233" s="4"/>
-      <c r="F233" s="6"/>
+      <c r="A233" s="4">
+        <v>390</v>
+      </c>
+      <c r="B233" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="C233" s="8">
+        <v>46091</v>
+      </c>
+      <c r="D233" s="25">
+        <v>50</v>
+      </c>
+      <c r="E233" s="4">
+        <v>50</v>
+      </c>
+      <c r="F233" s="5" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A234" s="4"/>
-      <c r="B234" s="6"/>
-      <c r="C234" s="13"/>
-      <c r="D234" s="6"/>
-      <c r="E234" s="4"/>
-      <c r="F234" s="6"/>
+      <c r="A234" s="4">
+        <v>390</v>
+      </c>
+      <c r="B234" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="C234" s="8">
+        <v>46091</v>
+      </c>
+      <c r="D234" s="26"/>
+      <c r="E234" s="4">
+        <v>50</v>
+      </c>
+      <c r="F234" s="5" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A235" s="4"/>
-      <c r="B235" s="6"/>
-      <c r="C235" s="13"/>
-      <c r="D235" s="6"/>
-      <c r="E235" s="4"/>
-      <c r="F235" s="6"/>
+      <c r="A235" s="4">
+        <v>390</v>
+      </c>
+      <c r="B235" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="C235" s="8">
+        <v>46091</v>
+      </c>
+      <c r="D235" s="26"/>
+      <c r="E235" s="4">
+        <v>50</v>
+      </c>
+      <c r="F235" s="5" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A236" s="4"/>
-      <c r="B236" s="6"/>
-      <c r="C236" s="13"/>
-      <c r="D236" s="6"/>
-      <c r="E236" s="4"/>
-      <c r="F236" s="6"/>
+      <c r="A236" s="4">
+        <v>390</v>
+      </c>
+      <c r="B236" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="C236" s="8">
+        <v>46091</v>
+      </c>
+      <c r="D236" s="26"/>
+      <c r="E236" s="4">
+        <v>50</v>
+      </c>
+      <c r="F236" s="5" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A237" s="4"/>
-      <c r="B237" s="6"/>
-      <c r="C237" s="13"/>
-      <c r="D237" s="6"/>
-      <c r="E237" s="4"/>
-      <c r="F237" s="6"/>
+      <c r="A237" s="4">
+        <v>390</v>
+      </c>
+      <c r="B237" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="C237" s="8">
+        <v>46091</v>
+      </c>
+      <c r="D237" s="26"/>
+      <c r="E237" s="4">
+        <v>50</v>
+      </c>
+      <c r="F237" s="5" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A238" s="4"/>
-      <c r="B238" s="6"/>
-      <c r="C238" s="13"/>
-      <c r="D238" s="6"/>
-      <c r="E238" s="4"/>
-      <c r="F238" s="6"/>
+      <c r="A238" s="4">
+        <v>390</v>
+      </c>
+      <c r="B238" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="C238" s="8">
+        <v>46091</v>
+      </c>
+      <c r="D238" s="27"/>
+      <c r="E238" s="4">
+        <v>50</v>
+      </c>
+      <c r="F238" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A239" s="4"/>
-      <c r="B239" s="6"/>
-      <c r="C239" s="13"/>
-      <c r="D239" s="6"/>
-      <c r="E239" s="4"/>
-      <c r="F239" s="6"/>
+      <c r="A239" s="4">
+        <v>391</v>
+      </c>
+      <c r="B239" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C239" s="8">
+        <v>46092</v>
+      </c>
+      <c r="D239" s="25">
+        <v>14</v>
+      </c>
+      <c r="E239" s="4">
+        <v>2</v>
+      </c>
+      <c r="F239" s="5" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A240" s="4"/>
-      <c r="B240" s="6"/>
-      <c r="C240" s="13"/>
-      <c r="D240" s="6"/>
-      <c r="E240" s="4"/>
-      <c r="F240" s="6"/>
+      <c r="A240" s="4">
+        <v>391</v>
+      </c>
+      <c r="B240" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C240" s="8">
+        <v>46092</v>
+      </c>
+      <c r="D240" s="26"/>
+      <c r="E240" s="4">
+        <v>2</v>
+      </c>
+      <c r="F240" s="5" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A241" s="4"/>
-      <c r="B241" s="6"/>
-      <c r="C241" s="13"/>
-      <c r="D241" s="6"/>
-      <c r="E241" s="4"/>
-      <c r="F241" s="6"/>
+      <c r="A241" s="4">
+        <v>391</v>
+      </c>
+      <c r="B241" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C241" s="8">
+        <v>46092</v>
+      </c>
+      <c r="D241" s="26"/>
+      <c r="E241" s="4">
+        <v>14</v>
+      </c>
+      <c r="F241" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A242" s="4"/>
-      <c r="B242" s="6"/>
-      <c r="C242" s="13"/>
-      <c r="D242" s="6"/>
-      <c r="E242" s="4"/>
-      <c r="F242" s="6"/>
+      <c r="A242" s="4">
+        <v>391</v>
+      </c>
+      <c r="B242" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C242" s="8">
+        <v>46092</v>
+      </c>
+      <c r="D242" s="26"/>
+      <c r="E242" s="4">
+        <v>14</v>
+      </c>
+      <c r="F242" s="5" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A243" s="4"/>
-      <c r="B243" s="6"/>
-      <c r="C243" s="13"/>
-      <c r="D243" s="6"/>
-      <c r="E243" s="4"/>
-      <c r="F243" s="6"/>
+      <c r="A243" s="4">
+        <v>391</v>
+      </c>
+      <c r="B243" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C243" s="8">
+        <v>46092</v>
+      </c>
+      <c r="D243" s="27"/>
+      <c r="E243" s="4">
+        <v>14</v>
+      </c>
+      <c r="F243" s="5" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A244" s="4"/>
-      <c r="B244" s="6"/>
-      <c r="C244" s="13"/>
-      <c r="D244" s="6"/>
-      <c r="E244" s="4"/>
-      <c r="F244" s="6"/>
+      <c r="A244" s="4">
+        <v>392</v>
+      </c>
+      <c r="B244" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="C244" s="8">
+        <v>46092</v>
+      </c>
+      <c r="D244" s="25">
+        <v>5</v>
+      </c>
+      <c r="E244" s="4">
+        <v>4</v>
+      </c>
+      <c r="F244" s="5" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A245" s="4"/>
-      <c r="B245" s="6"/>
-      <c r="C245" s="13"/>
-      <c r="D245" s="6"/>
-      <c r="E245" s="4"/>
-      <c r="F245" s="6"/>
+      <c r="A245" s="4">
+        <v>392</v>
+      </c>
+      <c r="B245" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="C245" s="8">
+        <v>46092</v>
+      </c>
+      <c r="D245" s="26"/>
+      <c r="E245" s="4">
+        <v>4</v>
+      </c>
+      <c r="F245" s="5" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A246" s="4"/>
-      <c r="B246" s="6"/>
-      <c r="C246" s="13"/>
-      <c r="D246" s="6"/>
-      <c r="E246" s="4"/>
-      <c r="F246" s="6"/>
+      <c r="A246" s="4">
+        <v>392</v>
+      </c>
+      <c r="B246" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="C246" s="8">
+        <v>46092</v>
+      </c>
+      <c r="D246" s="26"/>
+      <c r="E246" s="4">
+        <v>4</v>
+      </c>
+      <c r="F246" s="5" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A247" s="4"/>
-      <c r="B247" s="6"/>
-      <c r="C247" s="13"/>
-      <c r="D247" s="6"/>
-      <c r="E247" s="4"/>
-      <c r="F247" s="6"/>
+      <c r="A247" s="4">
+        <v>392</v>
+      </c>
+      <c r="B247" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="C247" s="8">
+        <v>46092</v>
+      </c>
+      <c r="D247" s="27"/>
+      <c r="E247" s="4">
+        <v>1</v>
+      </c>
+      <c r="F247" s="5" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A248" s="4"/>
-      <c r="B248" s="6"/>
-      <c r="C248" s="13"/>
-      <c r="D248" s="6"/>
-      <c r="E248" s="4"/>
-      <c r="F248" s="6"/>
+      <c r="A248" s="4">
+        <v>393</v>
+      </c>
+      <c r="B248" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="C248" s="20">
+        <v>46093</v>
+      </c>
+      <c r="D248" s="4">
+        <v>183</v>
+      </c>
+      <c r="E248" s="4">
+        <v>183</v>
+      </c>
+      <c r="F248" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A249" s="4"/>
-      <c r="B249" s="6"/>
-      <c r="C249" s="13"/>
-      <c r="D249" s="6"/>
-      <c r="E249" s="4"/>
-      <c r="F249" s="6"/>
+      <c r="A249" s="4">
+        <v>394</v>
+      </c>
+      <c r="B249" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="C249" s="20">
+        <v>46094</v>
+      </c>
+      <c r="D249" s="4">
+        <v>2</v>
+      </c>
+      <c r="E249" s="4">
+        <v>2</v>
+      </c>
+      <c r="F249" s="5" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A250" s="4"/>
-      <c r="B250" s="6"/>
-      <c r="C250" s="13"/>
-      <c r="D250" s="6"/>
-      <c r="E250" s="4"/>
-      <c r="F250" s="6"/>
+      <c r="A250" s="4">
+        <v>395</v>
+      </c>
+      <c r="B250" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C250" s="8">
+        <v>46094</v>
+      </c>
+      <c r="D250" s="4">
+        <v>25</v>
+      </c>
+      <c r="E250" s="4">
+        <v>25</v>
+      </c>
+      <c r="F250" s="5" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A251" s="4"/>
-      <c r="B251" s="6"/>
-      <c r="C251" s="13"/>
-      <c r="D251" s="6"/>
-      <c r="E251" s="4"/>
-      <c r="F251" s="6"/>
+      <c r="A251" s="4">
+        <v>396</v>
+      </c>
+      <c r="B251" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="C251" s="8">
+        <v>46097</v>
+      </c>
+      <c r="D251" s="25">
+        <v>4</v>
+      </c>
+      <c r="E251" s="4">
+        <v>4</v>
+      </c>
+      <c r="F251" s="5" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A252" s="4"/>
-      <c r="B252" s="6"/>
-      <c r="C252" s="13"/>
-      <c r="D252" s="6"/>
-      <c r="E252" s="4"/>
-      <c r="F252" s="6"/>
+      <c r="A252" s="4">
+        <v>396</v>
+      </c>
+      <c r="B252" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="C252" s="8">
+        <v>46097</v>
+      </c>
+      <c r="D252" s="26"/>
+      <c r="E252" s="4">
+        <v>4</v>
+      </c>
+      <c r="F252" s="5" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A253" s="4"/>
-      <c r="B253" s="6"/>
-      <c r="C253" s="13"/>
-      <c r="D253" s="6"/>
-      <c r="E253" s="4"/>
-      <c r="F253" s="6"/>
+      <c r="A253" s="4">
+        <v>396</v>
+      </c>
+      <c r="B253" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="C253" s="8">
+        <v>46097</v>
+      </c>
+      <c r="D253" s="27"/>
+      <c r="E253" s="4">
+        <v>4</v>
+      </c>
+      <c r="F253" s="5" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A254" s="4"/>
-      <c r="B254" s="6"/>
-      <c r="C254" s="13"/>
-      <c r="D254" s="6"/>
-      <c r="E254" s="4"/>
-      <c r="F254" s="6"/>
+      <c r="A254" s="4">
+        <v>397</v>
+      </c>
+      <c r="B254" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="C254" s="8">
+        <v>46097</v>
+      </c>
+      <c r="D254" s="25">
+        <v>10</v>
+      </c>
+      <c r="E254" s="4">
+        <v>10</v>
+      </c>
+      <c r="F254" s="5" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A255" s="4"/>
-      <c r="B255" s="6"/>
-      <c r="C255" s="13"/>
-      <c r="D255" s="6"/>
-      <c r="E255" s="4"/>
-      <c r="F255" s="6"/>
+      <c r="A255" s="4">
+        <v>397</v>
+      </c>
+      <c r="B255" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="C255" s="8">
+        <v>46097</v>
+      </c>
+      <c r="D255" s="26"/>
+      <c r="E255" s="4">
+        <v>10</v>
+      </c>
+      <c r="F255" s="5" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A256" s="4"/>
-      <c r="B256" s="6"/>
-      <c r="C256" s="13"/>
-      <c r="D256" s="6"/>
-      <c r="E256" s="4"/>
-      <c r="F256" s="6"/>
+      <c r="A256" s="4">
+        <v>397</v>
+      </c>
+      <c r="B256" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="C256" s="8">
+        <v>46097</v>
+      </c>
+      <c r="D256" s="27"/>
+      <c r="E256" s="4">
+        <v>10</v>
+      </c>
+      <c r="F256" s="5" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A257" s="4"/>
-      <c r="B257" s="6"/>
-      <c r="C257" s="13"/>
-      <c r="D257" s="6"/>
-      <c r="E257" s="4"/>
-      <c r="F257" s="6"/>
+      <c r="A257" s="4">
+        <v>398</v>
+      </c>
+      <c r="B257" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="C257" s="20">
+        <v>46098</v>
+      </c>
+      <c r="D257" s="4">
+        <v>11</v>
+      </c>
+      <c r="E257" s="4">
+        <v>11</v>
+      </c>
+      <c r="F257" s="5" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A258" s="4"/>
-      <c r="B258" s="6"/>
-      <c r="C258" s="13"/>
-      <c r="D258" s="6"/>
-      <c r="E258" s="4"/>
-      <c r="F258" s="6"/>
+      <c r="A258" s="4">
+        <v>399</v>
+      </c>
+      <c r="B258" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="C258" s="8">
+        <v>46097</v>
+      </c>
+      <c r="D258" s="4">
+        <v>127</v>
+      </c>
+      <c r="E258" s="4">
+        <v>127</v>
+      </c>
+      <c r="F258" s="5" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" s="4"/>
       <c r="B259" s="6"/>
       <c r="C259" s="13"/>
-      <c r="D259" s="6"/>
+      <c r="D259" s="4"/>
       <c r="E259" s="4"/>
-      <c r="F259" s="6"/>
+      <c r="F259" s="5"/>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" s="4"/>
       <c r="B260" s="6"/>
       <c r="C260" s="13"/>
-      <c r="D260" s="6"/>
+      <c r="D260" s="4"/>
       <c r="E260" s="4"/>
-      <c r="F260" s="6"/>
+      <c r="F260" s="5"/>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" s="4"/>
       <c r="B261" s="6"/>
       <c r="C261" s="13"/>
-      <c r="D261" s="6"/>
+      <c r="D261" s="4"/>
       <c r="E261" s="4"/>
-      <c r="F261" s="6"/>
+      <c r="F261" s="5"/>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" s="4"/>
       <c r="B262" s="6"/>
       <c r="C262" s="13"/>
-      <c r="D262" s="6"/>
+      <c r="D262" s="4"/>
       <c r="E262" s="4"/>
-      <c r="F262" s="6"/>
+      <c r="F262" s="5"/>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" s="4"/>
       <c r="B263" s="6"/>
       <c r="C263" s="13"/>
-      <c r="D263" s="6"/>
+      <c r="D263" s="4"/>
       <c r="E263" s="4"/>
-      <c r="F263" s="6"/>
+      <c r="F263" s="5"/>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" s="4"/>
       <c r="B264" s="6"/>
       <c r="C264" s="13"/>
-      <c r="D264" s="6"/>
+      <c r="D264" s="4"/>
       <c r="E264" s="4"/>
-      <c r="F264" s="6"/>
+      <c r="F264" s="5"/>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" s="4"/>
       <c r="B265" s="6"/>
       <c r="C265" s="13"/>
-      <c r="D265" s="6"/>
+      <c r="D265" s="4"/>
       <c r="E265" s="4"/>
-      <c r="F265" s="6"/>
+      <c r="F265" s="5"/>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" s="4"/>
       <c r="B266" s="6"/>
       <c r="C266" s="13"/>
-      <c r="D266" s="6"/>
+      <c r="D266" s="4"/>
       <c r="E266" s="4"/>
-      <c r="F266" s="6"/>
+      <c r="F266" s="5"/>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" s="4"/>
       <c r="B267" s="6"/>
       <c r="C267" s="13"/>
-      <c r="D267" s="6"/>
+      <c r="D267" s="4"/>
       <c r="E267" s="4"/>
-      <c r="F267" s="6"/>
+      <c r="F267" s="5"/>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" s="4"/>
       <c r="B268" s="6"/>
       <c r="C268" s="13"/>
-      <c r="D268" s="6"/>
+      <c r="D268" s="4"/>
       <c r="E268" s="4"/>
-      <c r="F268" s="6"/>
+      <c r="F268" s="5"/>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" s="4"/>
       <c r="B269" s="6"/>
       <c r="C269" s="13"/>
-      <c r="D269" s="6"/>
+      <c r="D269" s="4"/>
       <c r="E269" s="4"/>
-      <c r="F269" s="6"/>
+      <c r="F269" s="5"/>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" s="4"/>
       <c r="B270" s="6"/>
       <c r="C270" s="13"/>
-      <c r="D270" s="6"/>
+      <c r="D270" s="4"/>
       <c r="E270" s="4"/>
-      <c r="F270" s="6"/>
+      <c r="F270" s="5"/>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" s="4"/>
       <c r="B271" s="6"/>
       <c r="C271" s="13"/>
-      <c r="D271" s="6"/>
+      <c r="D271" s="4"/>
       <c r="E271" s="4"/>
-      <c r="F271" s="6"/>
+      <c r="F271" s="5"/>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" s="4"/>
       <c r="B272" s="6"/>
       <c r="C272" s="13"/>
-      <c r="D272" s="6"/>
+      <c r="D272" s="4"/>
       <c r="E272" s="4"/>
-      <c r="F272" s="6"/>
+      <c r="F272" s="5"/>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" s="4"/>
       <c r="B273" s="6"/>
       <c r="C273" s="13"/>
-      <c r="D273" s="6"/>
+      <c r="D273" s="4"/>
       <c r="E273" s="4"/>
-      <c r="F273" s="6"/>
+      <c r="F273" s="5"/>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" s="4"/>
       <c r="B274" s="6"/>
       <c r="C274" s="13"/>
-      <c r="D274" s="6"/>
+      <c r="D274" s="4"/>
       <c r="E274" s="4"/>
-      <c r="F274" s="6"/>
+      <c r="F274" s="5"/>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" s="4"/>
       <c r="B275" s="6"/>
       <c r="C275" s="13"/>
-      <c r="D275" s="6"/>
+      <c r="D275" s="4"/>
       <c r="E275" s="4"/>
-      <c r="F275" s="6"/>
+      <c r="F275" s="5"/>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" s="4"/>
       <c r="B276" s="6"/>
       <c r="C276" s="13"/>
-      <c r="D276" s="6"/>
+      <c r="D276" s="4"/>
       <c r="E276" s="4"/>
-      <c r="F276" s="6"/>
+      <c r="F276" s="5"/>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" s="4"/>
       <c r="B277" s="6"/>
       <c r="C277" s="13"/>
-      <c r="D277" s="6"/>
+      <c r="D277" s="4"/>
       <c r="E277" s="4"/>
-      <c r="F277" s="6"/>
+      <c r="F277" s="5"/>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" s="4"/>
       <c r="B278" s="6"/>
       <c r="C278" s="13"/>
-      <c r="D278" s="6"/>
+      <c r="D278" s="4"/>
       <c r="E278" s="4"/>
-      <c r="F278" s="6"/>
+      <c r="F278" s="5"/>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" s="4"/>
       <c r="B279" s="6"/>
       <c r="C279" s="13"/>
-      <c r="D279" s="6"/>
+      <c r="D279" s="4"/>
       <c r="E279" s="4"/>
-      <c r="F279" s="6"/>
+      <c r="F279" s="5"/>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" s="4"/>
       <c r="B280" s="6"/>
       <c r="C280" s="13"/>
-      <c r="D280" s="6"/>
+      <c r="D280" s="4"/>
       <c r="E280" s="4"/>
-      <c r="F280" s="6"/>
+      <c r="F280" s="5"/>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" s="4"/>
       <c r="B281" s="6"/>
       <c r="C281" s="13"/>
-      <c r="D281" s="6"/>
+      <c r="D281" s="4"/>
       <c r="E281" s="4"/>
-      <c r="F281" s="6"/>
+      <c r="F281" s="5"/>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" s="4"/>
       <c r="B282" s="6"/>
       <c r="C282" s="13"/>
-      <c r="D282" s="6"/>
+      <c r="D282" s="4"/>
       <c r="E282" s="4"/>
-      <c r="F282" s="6"/>
+      <c r="F282" s="5"/>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" s="4"/>
       <c r="B283" s="6"/>
       <c r="C283" s="13"/>
-      <c r="D283" s="6"/>
+      <c r="D283" s="4"/>
       <c r="E283" s="4"/>
-      <c r="F283" s="6"/>
+      <c r="F283" s="5"/>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" s="4"/>
       <c r="B284" s="6"/>
       <c r="C284" s="13"/>
-      <c r="D284" s="6"/>
+      <c r="D284" s="4"/>
       <c r="E284" s="4"/>
-      <c r="F284" s="6"/>
+      <c r="F284" s="5"/>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" s="4"/>
       <c r="B285" s="6"/>
       <c r="C285" s="13"/>
-      <c r="D285" s="6"/>
+      <c r="D285" s="4"/>
       <c r="E285" s="4"/>
-      <c r="F285" s="6"/>
+      <c r="F285" s="5"/>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286" s="4"/>
       <c r="B286" s="6"/>
       <c r="C286" s="13"/>
-      <c r="D286" s="6"/>
+      <c r="D286" s="4"/>
       <c r="E286" s="4"/>
-      <c r="F286" s="6"/>
+      <c r="F286" s="5"/>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287" s="4"/>
       <c r="B287" s="6"/>
       <c r="C287" s="13"/>
-      <c r="D287" s="6"/>
+      <c r="D287" s="4"/>
       <c r="E287" s="4"/>
-      <c r="F287" s="6"/>
+      <c r="F287" s="5"/>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" s="4"/>
       <c r="B288" s="6"/>
       <c r="C288" s="13"/>
-      <c r="D288" s="6"/>
+      <c r="D288" s="4"/>
       <c r="E288" s="4"/>
-      <c r="F288" s="6"/>
+      <c r="F288" s="5"/>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" s="4"/>
       <c r="B289" s="6"/>
       <c r="C289" s="13"/>
-      <c r="D289" s="6"/>
+      <c r="D289" s="4"/>
       <c r="E289" s="4"/>
-      <c r="F289" s="6"/>
+      <c r="F289" s="5"/>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" s="4"/>
       <c r="B290" s="6"/>
       <c r="C290" s="13"/>
-      <c r="D290" s="6"/>
+      <c r="D290" s="4"/>
       <c r="E290" s="4"/>
-      <c r="F290" s="6"/>
+      <c r="F290" s="5"/>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291" s="4"/>
       <c r="B291" s="6"/>
       <c r="C291" s="13"/>
-      <c r="D291" s="6"/>
+      <c r="D291" s="4"/>
       <c r="E291" s="4"/>
-      <c r="F291" s="6"/>
+      <c r="F291" s="5"/>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" s="4"/>
       <c r="B292" s="6"/>
       <c r="C292" s="13"/>
-      <c r="D292" s="6"/>
+      <c r="D292" s="4"/>
       <c r="E292" s="4"/>
-      <c r="F292" s="6"/>
+      <c r="F292" s="5"/>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293" s="4"/>
       <c r="B293" s="6"/>
       <c r="C293" s="13"/>
-      <c r="D293" s="6"/>
+      <c r="D293" s="4"/>
       <c r="E293" s="4"/>
-      <c r="F293" s="6"/>
+      <c r="F293" s="5"/>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294" s="4"/>
       <c r="B294" s="6"/>
       <c r="C294" s="13"/>
-      <c r="D294" s="6"/>
+      <c r="D294" s="4"/>
       <c r="E294" s="4"/>
-      <c r="F294" s="6"/>
+      <c r="F294" s="5"/>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295" s="4"/>
       <c r="B295" s="6"/>
       <c r="C295" s="13"/>
-      <c r="D295" s="6"/>
+      <c r="D295" s="4"/>
       <c r="E295" s="4"/>
-      <c r="F295" s="6"/>
+      <c r="F295" s="5"/>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A296" s="4"/>
       <c r="B296" s="6"/>
       <c r="C296" s="13"/>
-      <c r="D296" s="6"/>
+      <c r="D296" s="4"/>
       <c r="E296" s="4"/>
-      <c r="F296" s="6"/>
+      <c r="F296" s="5"/>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297" s="4"/>
       <c r="B297" s="6"/>
       <c r="C297" s="13"/>
-      <c r="D297" s="6"/>
+      <c r="D297" s="4"/>
       <c r="E297" s="4"/>
-      <c r="F297" s="6"/>
+      <c r="F297" s="5"/>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" s="4"/>
       <c r="B298" s="6"/>
       <c r="C298" s="13"/>
-      <c r="D298" s="6"/>
+      <c r="D298" s="4"/>
       <c r="E298" s="4"/>
-      <c r="F298" s="6"/>
+      <c r="F298" s="5"/>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299" s="4"/>
       <c r="B299" s="6"/>
       <c r="C299" s="13"/>
-      <c r="D299" s="6"/>
+      <c r="D299" s="4"/>
       <c r="E299" s="4"/>
-      <c r="F299" s="6"/>
+      <c r="F299" s="5"/>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300" s="4"/>
       <c r="B300" s="6"/>
       <c r="C300" s="13"/>
-      <c r="D300" s="6"/>
+      <c r="D300" s="4"/>
       <c r="E300" s="4"/>
-      <c r="F300" s="6"/>
+      <c r="F300" s="5"/>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301" s="4"/>
       <c r="B301" s="6"/>
       <c r="C301" s="13"/>
-      <c r="D301" s="6"/>
+      <c r="D301" s="4"/>
       <c r="E301" s="4"/>
-      <c r="F301" s="6"/>
+      <c r="F301" s="5"/>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302" s="4"/>
       <c r="B302" s="6"/>
       <c r="C302" s="13"/>
-      <c r="D302" s="6"/>
+      <c r="D302" s="4"/>
       <c r="E302" s="4"/>
-      <c r="F302" s="6"/>
+      <c r="F302" s="5"/>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A303" s="4"/>
       <c r="B303" s="6"/>
       <c r="C303" s="13"/>
-      <c r="D303" s="6"/>
+      <c r="D303" s="4"/>
       <c r="E303" s="4"/>
-      <c r="F303" s="6"/>
+      <c r="F303" s="5"/>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A304" s="4"/>
       <c r="B304" s="6"/>
       <c r="C304" s="13"/>
-      <c r="D304" s="6"/>
+      <c r="D304" s="4"/>
       <c r="E304" s="4"/>
-      <c r="F304" s="6"/>
+      <c r="F304" s="5"/>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A305" s="4"/>
       <c r="B305" s="6"/>
       <c r="C305" s="13"/>
-      <c r="D305" s="6"/>
+      <c r="D305" s="4"/>
       <c r="E305" s="4"/>
-      <c r="F305" s="6"/>
+      <c r="F305" s="5"/>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A306" s="4"/>
       <c r="B306" s="6"/>
       <c r="C306" s="13"/>
-      <c r="D306" s="6"/>
+      <c r="D306" s="4"/>
       <c r="E306" s="4"/>
-      <c r="F306" s="6"/>
+      <c r="F306" s="5"/>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A307" s="4"/>
       <c r="B307" s="6"/>
       <c r="C307" s="13"/>
-      <c r="D307" s="6"/>
+      <c r="D307" s="4"/>
       <c r="E307" s="4"/>
-      <c r="F307" s="6"/>
+      <c r="F307" s="5"/>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A308" s="4"/>
       <c r="B308" s="6"/>
       <c r="C308" s="13"/>
-      <c r="D308" s="6"/>
+      <c r="D308" s="4"/>
       <c r="E308" s="4"/>
-      <c r="F308" s="6"/>
+      <c r="F308" s="5"/>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A309" s="4"/>
       <c r="B309" s="6"/>
       <c r="C309" s="13"/>
-      <c r="D309" s="6"/>
+      <c r="D309" s="4"/>
       <c r="E309" s="4"/>
-      <c r="F309" s="6"/>
+      <c r="F309" s="5"/>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A310" s="4"/>
       <c r="B310" s="6"/>
       <c r="C310" s="13"/>
-      <c r="D310" s="6"/>
+      <c r="D310" s="4"/>
       <c r="E310" s="4"/>
-      <c r="F310" s="6"/>
+      <c r="F310" s="5"/>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A311" s="4"/>
       <c r="B311" s="6"/>
       <c r="C311" s="13"/>
-      <c r="D311" s="6"/>
+      <c r="D311" s="4"/>
       <c r="E311" s="4"/>
-      <c r="F311" s="6"/>
+      <c r="F311" s="5"/>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A312" s="4"/>
       <c r="B312" s="6"/>
       <c r="C312" s="13"/>
-      <c r="D312" s="6"/>
+      <c r="D312" s="4"/>
       <c r="E312" s="4"/>
-      <c r="F312" s="6"/>
+      <c r="F312" s="5"/>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A313" s="4"/>
       <c r="B313" s="6"/>
       <c r="C313" s="13"/>
-      <c r="D313" s="6"/>
+      <c r="D313" s="4"/>
       <c r="E313" s="4"/>
-      <c r="F313" s="6"/>
+      <c r="F313" s="5"/>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A314" s="4"/>
       <c r="B314" s="6"/>
       <c r="C314" s="13"/>
-      <c r="D314" s="6"/>
+      <c r="D314" s="4"/>
       <c r="E314" s="4"/>
-      <c r="F314" s="6"/>
+      <c r="F314" s="5"/>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A315" s="4"/>
       <c r="B315" s="6"/>
       <c r="C315" s="13"/>
-      <c r="D315" s="6"/>
+      <c r="D315" s="4"/>
       <c r="E315" s="4"/>
-      <c r="F315" s="6"/>
+      <c r="F315" s="5"/>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A316" s="4"/>
       <c r="B316" s="6"/>
       <c r="C316" s="13"/>
-      <c r="D316" s="6"/>
+      <c r="D316" s="4"/>
       <c r="E316" s="4"/>
-      <c r="F316" s="6"/>
+      <c r="F316" s="5"/>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A317" s="4"/>
       <c r="B317" s="6"/>
       <c r="C317" s="13"/>
-      <c r="D317" s="6"/>
+      <c r="D317" s="4"/>
       <c r="E317" s="4"/>
-      <c r="F317" s="6"/>
+      <c r="F317" s="5"/>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A318" s="4"/>
       <c r="B318" s="6"/>
       <c r="C318" s="13"/>
-      <c r="D318" s="6"/>
+      <c r="D318" s="4"/>
       <c r="E318" s="4"/>
-      <c r="F318" s="6"/>
+      <c r="F318" s="5"/>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A319" s="4"/>
       <c r="B319" s="6"/>
       <c r="C319" s="13"/>
-      <c r="D319" s="6"/>
+      <c r="D319" s="4"/>
       <c r="E319" s="4"/>
-      <c r="F319" s="6"/>
+      <c r="F319" s="5"/>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A320" s="4"/>
       <c r="B320" s="6"/>
       <c r="C320" s="13"/>
-      <c r="D320" s="6"/>
+      <c r="D320" s="4"/>
       <c r="E320" s="4"/>
-      <c r="F320" s="6"/>
+      <c r="F320" s="5"/>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A321" s="4"/>
       <c r="B321" s="6"/>
       <c r="C321" s="13"/>
-      <c r="D321" s="6"/>
+      <c r="D321" s="4"/>
       <c r="E321" s="4"/>
-      <c r="F321" s="6"/>
+      <c r="F321" s="5"/>
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A322" s="4"/>
       <c r="B322" s="6"/>
       <c r="C322" s="13"/>
-      <c r="D322" s="6"/>
+      <c r="D322" s="4"/>
       <c r="E322" s="4"/>
-      <c r="F322" s="6"/>
+      <c r="F322" s="5"/>
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A323" s="4"/>
       <c r="B323" s="6"/>
       <c r="C323" s="13"/>
-      <c r="D323" s="6"/>
+      <c r="D323" s="4"/>
       <c r="E323" s="4"/>
-      <c r="F323" s="6"/>
+      <c r="F323" s="5"/>
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A324" s="4"/>
       <c r="B324" s="6"/>
       <c r="C324" s="13"/>
-      <c r="D324" s="6"/>
+      <c r="D324" s="4"/>
       <c r="E324" s="4"/>
-      <c r="F324" s="6"/>
+      <c r="F324" s="5"/>
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A325" s="4"/>
       <c r="B325" s="6"/>
       <c r="C325" s="13"/>
-      <c r="D325" s="6"/>
+      <c r="D325" s="4"/>
       <c r="E325" s="4"/>
-      <c r="F325" s="6"/>
+      <c r="F325" s="5"/>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A326" s="4"/>
       <c r="B326" s="6"/>
       <c r="C326" s="13"/>
-      <c r="D326" s="6"/>
+      <c r="D326" s="4"/>
       <c r="E326" s="4"/>
-      <c r="F326" s="6"/>
+      <c r="F326" s="5"/>
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A327" s="4"/>
       <c r="B327" s="6"/>
       <c r="C327" s="13"/>
-      <c r="D327" s="6"/>
+      <c r="D327" s="4"/>
       <c r="E327" s="4"/>
-      <c r="F327" s="6"/>
+      <c r="F327" s="5"/>
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A328" s="4"/>
       <c r="B328" s="6"/>
       <c r="C328" s="13"/>
-      <c r="D328" s="6"/>
+      <c r="D328" s="4"/>
       <c r="E328" s="4"/>
-      <c r="F328" s="6"/>
+      <c r="F328" s="5"/>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A329" s="4"/>
       <c r="B329" s="6"/>
       <c r="C329" s="13"/>
-      <c r="D329" s="6"/>
+      <c r="D329" s="4"/>
       <c r="E329" s="4"/>
-      <c r="F329" s="6"/>
+      <c r="F329" s="5"/>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A330" s="4"/>
       <c r="B330" s="6"/>
       <c r="C330" s="13"/>
-      <c r="D330" s="6"/>
+      <c r="D330" s="4"/>
       <c r="E330" s="4"/>
-      <c r="F330" s="6"/>
+      <c r="F330" s="5"/>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A331" s="4"/>
       <c r="B331" s="6"/>
       <c r="C331" s="13"/>
-      <c r="D331" s="6"/>
+      <c r="D331" s="4"/>
       <c r="E331" s="4"/>
-      <c r="F331" s="6"/>
+      <c r="F331" s="5"/>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A332" s="4"/>
       <c r="B332" s="6"/>
       <c r="C332" s="13"/>
-      <c r="D332" s="6"/>
+      <c r="D332" s="4"/>
       <c r="E332" s="4"/>
-      <c r="F332" s="6"/>
+      <c r="F332" s="5"/>
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A333" s="4"/>
       <c r="B333" s="6"/>
       <c r="C333" s="13"/>
-      <c r="D333" s="6"/>
+      <c r="D333" s="4"/>
       <c r="E333" s="4"/>
-      <c r="F333" s="6"/>
+      <c r="F333" s="5"/>
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A334" s="4"/>
       <c r="B334" s="6"/>
       <c r="C334" s="13"/>
-      <c r="D334" s="6"/>
+      <c r="D334" s="4"/>
       <c r="E334" s="4"/>
-      <c r="F334" s="6"/>
+      <c r="F334" s="5"/>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A335" s="4"/>
       <c r="B335" s="6"/>
       <c r="C335" s="13"/>
-      <c r="D335" s="6"/>
+      <c r="D335" s="4"/>
       <c r="E335" s="4"/>
-      <c r="F335" s="6"/>
+      <c r="F335" s="5"/>
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A336" s="4"/>
       <c r="B336" s="6"/>
       <c r="C336" s="13"/>
-      <c r="D336" s="6"/>
+      <c r="D336" s="4"/>
       <c r="E336" s="4"/>
-      <c r="F336" s="6"/>
+      <c r="F336" s="5"/>
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A337" s="4"/>
       <c r="B337" s="6"/>
       <c r="C337" s="13"/>
-      <c r="D337" s="6"/>
+      <c r="D337" s="4"/>
       <c r="E337" s="4"/>
-      <c r="F337" s="6"/>
+      <c r="F337" s="5"/>
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A338" s="4"/>
       <c r="B338" s="6"/>
       <c r="C338" s="13"/>
-      <c r="D338" s="6"/>
+      <c r="D338" s="4"/>
       <c r="E338" s="4"/>
-      <c r="F338" s="6"/>
+      <c r="F338" s="5"/>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A339" s="4"/>
       <c r="B339" s="6"/>
       <c r="C339" s="13"/>
-      <c r="D339" s="6"/>
+      <c r="D339" s="4"/>
       <c r="E339" s="4"/>
-      <c r="F339" s="6"/>
+      <c r="F339" s="5"/>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A340" s="4"/>
       <c r="B340" s="6"/>
       <c r="C340" s="13"/>
-      <c r="D340" s="6"/>
+      <c r="D340" s="4"/>
       <c r="E340" s="4"/>
-      <c r="F340" s="6"/>
+      <c r="F340" s="5"/>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A341" s="4"/>
       <c r="B341" s="6"/>
       <c r="C341" s="13"/>
-      <c r="D341" s="6"/>
+      <c r="D341" s="4"/>
       <c r="E341" s="4"/>
-      <c r="F341" s="6"/>
+      <c r="F341" s="5"/>
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A342" s="4"/>
       <c r="B342" s="6"/>
       <c r="C342" s="13"/>
-      <c r="D342" s="6"/>
+      <c r="D342" s="4"/>
       <c r="E342" s="4"/>
-      <c r="F342" s="6"/>
+      <c r="F342" s="5"/>
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A343" s="4"/>
       <c r="B343" s="6"/>
       <c r="C343" s="13"/>
-      <c r="D343" s="6"/>
+      <c r="D343" s="4"/>
       <c r="E343" s="4"/>
-      <c r="F343" s="6"/>
+      <c r="F343" s="5"/>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A344" s="4"/>
       <c r="B344" s="6"/>
       <c r="C344" s="13"/>
-      <c r="D344" s="6"/>
+      <c r="D344" s="4"/>
       <c r="E344" s="4"/>
-      <c r="F344" s="6"/>
+      <c r="F344" s="5"/>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A345" s="4"/>
       <c r="B345" s="6"/>
       <c r="C345" s="13"/>
-      <c r="D345" s="6"/>
+      <c r="D345" s="4"/>
       <c r="E345" s="4"/>
-      <c r="F345" s="6"/>
+      <c r="F345" s="5"/>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A346" s="4"/>
       <c r="B346" s="6"/>
       <c r="C346" s="13"/>
-      <c r="D346" s="6"/>
+      <c r="D346" s="4"/>
       <c r="E346" s="4"/>
-      <c r="F346" s="6"/>
+      <c r="F346" s="5"/>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A347" s="4"/>
       <c r="B347" s="6"/>
       <c r="C347" s="13"/>
-      <c r="D347" s="6"/>
+      <c r="D347" s="4"/>
       <c r="E347" s="4"/>
-      <c r="F347" s="6"/>
+      <c r="F347" s="5"/>
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A348" s="4"/>
       <c r="B348" s="6"/>
       <c r="C348" s="13"/>
-      <c r="D348" s="6"/>
+      <c r="D348" s="4"/>
       <c r="E348" s="4"/>
-      <c r="F348" s="6"/>
+      <c r="F348" s="5"/>
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A349" s="4"/>
       <c r="B349" s="6"/>
       <c r="C349" s="13"/>
-      <c r="D349" s="6"/>
+      <c r="D349" s="4"/>
       <c r="E349" s="4"/>
-      <c r="F349" s="6"/>
+      <c r="F349" s="5"/>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A350" s="4"/>
       <c r="B350" s="6"/>
       <c r="C350" s="13"/>
-      <c r="D350" s="6"/>
+      <c r="D350" s="4"/>
       <c r="E350" s="4"/>
-      <c r="F350" s="6"/>
+      <c r="F350" s="5"/>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A351" s="4"/>
       <c r="B351" s="6"/>
       <c r="C351" s="13"/>
-      <c r="D351" s="6"/>
+      <c r="D351" s="4"/>
       <c r="E351" s="4"/>
-      <c r="F351" s="6"/>
+      <c r="F351" s="5"/>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A352" s="4"/>
       <c r="B352" s="6"/>
       <c r="C352" s="13"/>
-      <c r="D352" s="6"/>
+      <c r="D352" s="4"/>
       <c r="E352" s="4"/>
-      <c r="F352" s="6"/>
+      <c r="F352" s="5"/>
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A353" s="4"/>
       <c r="B353" s="6"/>
       <c r="C353" s="13"/>
-      <c r="D353" s="6"/>
+      <c r="D353" s="4"/>
       <c r="E353" s="4"/>
-      <c r="F353" s="6"/>
+      <c r="F353" s="5"/>
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A354" s="4"/>
       <c r="B354" s="6"/>
       <c r="C354" s="13"/>
-      <c r="D354" s="6"/>
+      <c r="D354" s="4"/>
       <c r="E354" s="4"/>
-      <c r="F354" s="6"/>
+      <c r="F354" s="5"/>
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A355" s="4"/>
       <c r="B355" s="6"/>
       <c r="C355" s="13"/>
-      <c r="D355" s="6"/>
+      <c r="D355" s="4"/>
       <c r="E355" s="4"/>
-      <c r="F355" s="6"/>
+      <c r="F355" s="5"/>
     </row>
     <row r="356" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A356" s="4"/>
       <c r="B356" s="6"/>
       <c r="C356" s="13"/>
-      <c r="D356" s="6"/>
+      <c r="D356" s="4"/>
       <c r="E356" s="4"/>
-      <c r="F356" s="6"/>
+      <c r="F356" s="5"/>
     </row>
     <row r="357" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A357" s="4"/>
       <c r="B357" s="6"/>
       <c r="C357" s="13"/>
-      <c r="D357" s="6"/>
+      <c r="D357" s="4"/>
       <c r="E357" s="4"/>
-      <c r="F357" s="6"/>
+      <c r="F357" s="5"/>
     </row>
     <row r="358" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A358" s="4"/>
       <c r="B358" s="6"/>
       <c r="C358" s="13"/>
-      <c r="D358" s="6"/>
+      <c r="D358" s="4"/>
       <c r="E358" s="4"/>
-      <c r="F358" s="6"/>
+      <c r="F358" s="5"/>
     </row>
     <row r="359" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A359" s="4"/>
       <c r="B359" s="6"/>
       <c r="C359" s="13"/>
-      <c r="D359" s="6"/>
+      <c r="D359" s="4"/>
       <c r="E359" s="4"/>
-      <c r="F359" s="6"/>
+      <c r="F359" s="5"/>
     </row>
     <row r="360" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A360" s="4"/>
       <c r="B360" s="6"/>
       <c r="C360" s="13"/>
-      <c r="D360" s="6"/>
+      <c r="D360" s="4"/>
       <c r="E360" s="4"/>
-      <c r="F360" s="6"/>
+      <c r="F360" s="5"/>
     </row>
     <row r="361" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A361" s="4"/>
       <c r="B361" s="6"/>
       <c r="C361" s="13"/>
-      <c r="D361" s="6"/>
+      <c r="D361" s="4"/>
       <c r="E361" s="4"/>
-      <c r="F361" s="6"/>
+      <c r="F361" s="5"/>
     </row>
     <row r="362" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A362" s="4"/>
       <c r="B362" s="6"/>
       <c r="C362" s="13"/>
-      <c r="D362" s="6"/>
+      <c r="D362" s="4"/>
       <c r="E362" s="4"/>
-      <c r="F362" s="6"/>
+      <c r="F362" s="5"/>
     </row>
     <row r="363" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A363" s="4"/>
       <c r="B363" s="6"/>
       <c r="C363" s="13"/>
-      <c r="D363" s="6"/>
+      <c r="D363" s="4"/>
       <c r="E363" s="4"/>
-      <c r="F363" s="6"/>
+      <c r="F363" s="5"/>
     </row>
     <row r="364" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A364" s="4"/>
       <c r="B364" s="6"/>
       <c r="C364" s="13"/>
-      <c r="D364" s="6"/>
+      <c r="D364" s="4"/>
       <c r="E364" s="4"/>
-      <c r="F364" s="6"/>
+      <c r="F364" s="5"/>
     </row>
     <row r="365" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A365" s="4"/>
       <c r="B365" s="6"/>
       <c r="C365" s="13"/>
-      <c r="D365" s="6"/>
+      <c r="D365" s="4"/>
       <c r="E365" s="4"/>
-      <c r="F365" s="6"/>
+      <c r="F365" s="5"/>
     </row>
     <row r="366" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A366" s="4"/>
       <c r="B366" s="6"/>
       <c r="C366" s="13"/>
-      <c r="D366" s="6"/>
+      <c r="D366" s="4"/>
       <c r="E366" s="4"/>
-      <c r="F366" s="6"/>
+      <c r="F366" s="5"/>
     </row>
     <row r="367" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A367" s="4"/>
       <c r="B367" s="6"/>
       <c r="C367" s="13"/>
-      <c r="D367" s="6"/>
+      <c r="D367" s="4"/>
       <c r="E367" s="4"/>
-      <c r="F367" s="6"/>
+      <c r="F367" s="5"/>
     </row>
     <row r="368" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A368" s="4"/>
       <c r="B368" s="6"/>
       <c r="C368" s="13"/>
-      <c r="D368" s="6"/>
+      <c r="D368" s="4"/>
       <c r="E368" s="4"/>
-      <c r="F368" s="6"/>
+      <c r="F368" s="5"/>
     </row>
     <row r="369" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A369" s="4"/>
       <c r="B369" s="6"/>
       <c r="C369" s="13"/>
-      <c r="D369" s="6"/>
+      <c r="D369" s="4"/>
       <c r="E369" s="4"/>
-      <c r="F369" s="6"/>
+      <c r="F369" s="5"/>
     </row>
     <row r="370" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A370" s="4"/>
       <c r="B370" s="6"/>
       <c r="C370" s="13"/>
-      <c r="D370" s="6"/>
+      <c r="D370" s="4"/>
       <c r="E370" s="4"/>
-      <c r="F370" s="6"/>
+      <c r="F370" s="5"/>
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A371" s="4"/>
       <c r="B371" s="6"/>
       <c r="C371" s="13"/>
-      <c r="D371" s="6"/>
+      <c r="D371" s="4"/>
       <c r="E371" s="4"/>
-      <c r="F371" s="6"/>
+      <c r="F371" s="5"/>
     </row>
     <row r="372" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A372" s="4"/>
       <c r="B372" s="6"/>
       <c r="C372" s="13"/>
-      <c r="D372" s="6"/>
+      <c r="D372" s="4"/>
       <c r="E372" s="4"/>
-      <c r="F372" s="6"/>
+      <c r="F372" s="5"/>
     </row>
     <row r="373" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A373" s="4"/>
       <c r="B373" s="6"/>
       <c r="C373" s="13"/>
-      <c r="D373" s="6"/>
+      <c r="D373" s="4"/>
       <c r="E373" s="4"/>
-      <c r="F373" s="6"/>
+      <c r="F373" s="5"/>
     </row>
     <row r="374" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A374" s="4"/>
       <c r="B374" s="6"/>
       <c r="C374" s="13"/>
-      <c r="D374" s="6"/>
+      <c r="D374" s="4"/>
       <c r="E374" s="4"/>
-      <c r="F374" s="6"/>
+      <c r="F374" s="5"/>
     </row>
     <row r="375" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A375" s="4"/>
       <c r="B375" s="6"/>
       <c r="C375" s="13"/>
-      <c r="D375" s="6"/>
+      <c r="D375" s="4"/>
       <c r="E375" s="4"/>
-      <c r="F375" s="6"/>
+      <c r="F375" s="5"/>
     </row>
     <row r="376" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A376" s="4"/>
       <c r="B376" s="6"/>
       <c r="C376" s="13"/>
-      <c r="D376" s="6"/>
+      <c r="D376" s="4"/>
       <c r="E376" s="4"/>
-      <c r="F376" s="6"/>
+      <c r="F376" s="5"/>
     </row>
     <row r="377" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A377" s="4"/>
       <c r="B377" s="6"/>
       <c r="C377" s="13"/>
-      <c r="D377" s="6"/>
+      <c r="D377" s="4"/>
       <c r="E377" s="4"/>
-      <c r="F377" s="6"/>
+      <c r="F377" s="5"/>
     </row>
     <row r="378" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A378" s="4"/>
       <c r="B378" s="6"/>
       <c r="C378" s="13"/>
-      <c r="D378" s="6"/>
+      <c r="D378" s="4"/>
       <c r="E378" s="4"/>
-      <c r="F378" s="6"/>
+      <c r="F378" s="5"/>
     </row>
     <row r="379" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A379" s="4"/>
       <c r="B379" s="6"/>
       <c r="C379" s="13"/>
-      <c r="D379" s="6"/>
+      <c r="D379" s="4"/>
       <c r="E379" s="4"/>
-      <c r="F379" s="6"/>
+      <c r="F379" s="5"/>
     </row>
     <row r="380" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A380" s="4"/>
       <c r="B380" s="6"/>
       <c r="C380" s="13"/>
-      <c r="D380" s="6"/>
+      <c r="D380" s="4"/>
       <c r="E380" s="4"/>
-      <c r="F380" s="6"/>
+      <c r="F380" s="5"/>
     </row>
     <row r="381" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A381" s="4"/>
       <c r="B381" s="6"/>
       <c r="C381" s="13"/>
-      <c r="D381" s="6"/>
+      <c r="D381" s="4"/>
       <c r="E381" s="4"/>
-      <c r="F381" s="6"/>
+      <c r="F381" s="5"/>
     </row>
     <row r="382" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A382" s="4"/>
       <c r="B382" s="6"/>
       <c r="C382" s="13"/>
-      <c r="D382" s="6"/>
+      <c r="D382" s="4"/>
       <c r="E382" s="4"/>
-      <c r="F382" s="6"/>
+      <c r="F382" s="5"/>
     </row>
     <row r="383" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A383" s="4"/>
       <c r="B383" s="6"/>
       <c r="C383" s="13"/>
-      <c r="D383" s="6"/>
+      <c r="D383" s="4"/>
       <c r="E383" s="4"/>
-      <c r="F383" s="6"/>
+      <c r="F383" s="5"/>
     </row>
     <row r="384" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A384" s="4"/>
       <c r="B384" s="6"/>
       <c r="C384" s="13"/>
-      <c r="D384" s="6"/>
+      <c r="D384" s="4"/>
       <c r="E384" s="4"/>
-      <c r="F384" s="6"/>
+      <c r="F384" s="5"/>
     </row>
     <row r="385" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A385" s="4"/>
       <c r="B385" s="6"/>
       <c r="C385" s="13"/>
-      <c r="D385" s="6"/>
+      <c r="D385" s="4"/>
       <c r="E385" s="4"/>
-      <c r="F385" s="6"/>
+      <c r="F385" s="5"/>
     </row>
     <row r="386" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A386" s="4"/>
       <c r="B386" s="6"/>
       <c r="C386" s="13"/>
-      <c r="D386" s="6"/>
+      <c r="D386" s="4"/>
       <c r="E386" s="4"/>
-      <c r="F386" s="6"/>
+      <c r="F386" s="5"/>
     </row>
     <row r="387" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A387" s="4"/>
       <c r="B387" s="6"/>
       <c r="C387" s="13"/>
-      <c r="D387" s="6"/>
+      <c r="D387" s="4"/>
       <c r="E387" s="4"/>
-      <c r="F387" s="6"/>
+      <c r="F387" s="5"/>
     </row>
     <row r="388" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A388" s="4"/>
       <c r="B388" s="6"/>
       <c r="C388" s="13"/>
-      <c r="D388" s="6"/>
+      <c r="D388" s="4"/>
       <c r="E388" s="4"/>
-      <c r="F388" s="6"/>
+      <c r="F388" s="5"/>
     </row>
     <row r="389" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A389" s="4"/>
       <c r="B389" s="6"/>
       <c r="C389" s="13"/>
-      <c r="D389" s="6"/>
+      <c r="D389" s="4"/>
       <c r="E389" s="4"/>
-      <c r="F389" s="6"/>
+      <c r="F389" s="5"/>
     </row>
     <row r="390" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A390" s="4"/>
       <c r="B390" s="6"/>
       <c r="C390" s="13"/>
-      <c r="D390" s="6"/>
+      <c r="D390" s="4"/>
       <c r="E390" s="4"/>
-      <c r="F390" s="6"/>
+      <c r="F390" s="5"/>
     </row>
     <row r="391" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A391" s="4"/>
       <c r="B391" s="6"/>
       <c r="C391" s="13"/>
-      <c r="D391" s="6"/>
+      <c r="D391" s="4"/>
       <c r="E391" s="4"/>
-      <c r="F391" s="6"/>
+      <c r="F391" s="5"/>
     </row>
     <row r="392" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A392" s="4"/>
       <c r="B392" s="6"/>
       <c r="C392" s="13"/>
-      <c r="D392" s="6"/>
+      <c r="D392" s="4"/>
       <c r="E392" s="4"/>
-      <c r="F392" s="6"/>
+      <c r="F392" s="5"/>
     </row>
     <row r="393" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A393" s="4"/>
       <c r="B393" s="6"/>
       <c r="C393" s="13"/>
-      <c r="D393" s="6"/>
+      <c r="D393" s="4"/>
       <c r="E393" s="4"/>
-      <c r="F393" s="6"/>
+      <c r="F393" s="5"/>
     </row>
     <row r="394" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A394" s="4"/>
       <c r="B394" s="6"/>
       <c r="C394" s="13"/>
-      <c r="D394" s="6"/>
+      <c r="D394" s="4"/>
       <c r="E394" s="4"/>
-      <c r="F394" s="6"/>
+      <c r="F394" s="5"/>
     </row>
     <row r="395" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A395" s="4"/>
       <c r="B395" s="6"/>
       <c r="C395" s="13"/>
-      <c r="D395" s="6"/>
+      <c r="D395" s="4"/>
       <c r="E395" s="4"/>
-      <c r="F395" s="6"/>
+      <c r="F395" s="5"/>
     </row>
     <row r="396" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A396" s="4"/>
       <c r="B396" s="6"/>
       <c r="C396" s="13"/>
-      <c r="D396" s="6"/>
+      <c r="D396" s="4"/>
       <c r="E396" s="4"/>
-      <c r="F396" s="6"/>
+      <c r="F396" s="5"/>
     </row>
     <row r="397" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A397" s="4"/>
       <c r="B397" s="6"/>
       <c r="C397" s="13"/>
-      <c r="D397" s="6"/>
+      <c r="D397" s="4"/>
       <c r="E397" s="4"/>
-      <c r="F397" s="6"/>
+      <c r="F397" s="5"/>
     </row>
     <row r="398" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A398" s="4"/>
       <c r="B398" s="6"/>
       <c r="C398" s="13"/>
-      <c r="D398" s="6"/>
+      <c r="D398" s="4"/>
       <c r="E398" s="4"/>
-      <c r="F398" s="6"/>
+      <c r="F398" s="5"/>
     </row>
     <row r="399" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A399" s="4"/>
       <c r="B399" s="6"/>
       <c r="C399" s="13"/>
-      <c r="D399" s="6"/>
+      <c r="D399" s="4"/>
       <c r="E399" s="4"/>
-      <c r="F399" s="6"/>
+      <c r="F399" s="5"/>
     </row>
     <row r="400" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A400" s="4"/>
       <c r="B400" s="6"/>
       <c r="C400" s="13"/>
-      <c r="D400" s="6"/>
+      <c r="D400" s="4"/>
       <c r="E400" s="4"/>
-      <c r="F400" s="6"/>
+      <c r="F400" s="5"/>
     </row>
     <row r="401" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A401" s="4"/>
       <c r="B401" s="6"/>
       <c r="C401" s="13"/>
-      <c r="D401" s="6"/>
+      <c r="D401" s="4"/>
       <c r="E401" s="4"/>
-      <c r="F401" s="6"/>
+      <c r="F401" s="5"/>
     </row>
     <row r="402" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A402" s="4"/>
       <c r="B402" s="6"/>
       <c r="C402" s="13"/>
-      <c r="D402" s="6"/>
+      <c r="D402" s="4"/>
       <c r="E402" s="4"/>
-      <c r="F402" s="6"/>
+      <c r="F402" s="5"/>
     </row>
     <row r="403" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A403" s="4"/>
       <c r="B403" s="6"/>
       <c r="C403" s="13"/>
-      <c r="D403" s="6"/>
+      <c r="D403" s="4"/>
       <c r="E403" s="4"/>
-      <c r="F403" s="6"/>
+      <c r="F403" s="5"/>
     </row>
     <row r="404" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A404" s="4"/>
       <c r="B404" s="6"/>
       <c r="C404" s="13"/>
-      <c r="D404" s="6"/>
+      <c r="D404" s="4"/>
       <c r="E404" s="4"/>
-      <c r="F404" s="6"/>
+      <c r="F404" s="5"/>
     </row>
     <row r="405" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A405" s="4"/>
       <c r="B405" s="6"/>
       <c r="C405" s="13"/>
-      <c r="D405" s="6"/>
+      <c r="D405" s="4"/>
       <c r="E405" s="4"/>
-      <c r="F405" s="6"/>
+      <c r="F405" s="5"/>
     </row>
     <row r="406" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A406" s="4"/>
       <c r="B406" s="6"/>
       <c r="C406" s="13"/>
-      <c r="D406" s="6"/>
+      <c r="D406" s="4"/>
       <c r="E406" s="4"/>
-      <c r="F406" s="6"/>
+      <c r="F406" s="5"/>
     </row>
     <row r="407" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A407" s="4"/>
       <c r="B407" s="6"/>
       <c r="C407" s="13"/>
-      <c r="D407" s="6"/>
+      <c r="D407" s="4"/>
       <c r="E407" s="4"/>
-      <c r="F407" s="6"/>
+      <c r="F407" s="5"/>
     </row>
     <row r="408" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A408" s="4"/>
       <c r="B408" s="6"/>
       <c r="C408" s="13"/>
-      <c r="D408" s="6"/>
+      <c r="D408" s="4"/>
       <c r="E408" s="4"/>
-      <c r="F408" s="6"/>
+      <c r="F408" s="5"/>
     </row>
     <row r="409" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A409" s="4"/>
       <c r="B409" s="6"/>
       <c r="C409" s="13"/>
-      <c r="D409" s="6"/>
+      <c r="D409" s="4"/>
       <c r="E409" s="4"/>
-      <c r="F409" s="6"/>
+      <c r="F409" s="5"/>
     </row>
     <row r="410" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A410" s="4"/>
       <c r="B410" s="6"/>
       <c r="C410" s="13"/>
-      <c r="D410" s="6"/>
+      <c r="D410" s="4"/>
       <c r="E410" s="4"/>
-      <c r="F410" s="6"/>
+      <c r="F410" s="5"/>
     </row>
     <row r="411" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A411" s="4"/>
       <c r="B411" s="6"/>
       <c r="C411" s="13"/>
-      <c r="D411" s="6"/>
+      <c r="D411" s="4"/>
       <c r="E411" s="4"/>
-      <c r="F411" s="6"/>
+      <c r="F411" s="5"/>
     </row>
     <row r="412" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A412" s="4"/>
       <c r="B412" s="6"/>
       <c r="C412" s="13"/>
-      <c r="D412" s="6"/>
+      <c r="D412" s="4"/>
       <c r="E412" s="4"/>
-      <c r="F412" s="6"/>
+      <c r="F412" s="5"/>
     </row>
     <row r="413" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A413" s="4"/>
       <c r="B413" s="6"/>
       <c r="C413" s="13"/>
-      <c r="D413" s="6"/>
+      <c r="D413" s="4"/>
       <c r="E413" s="4"/>
-      <c r="F413" s="6"/>
+      <c r="F413" s="5"/>
     </row>
     <row r="414" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A414" s="4"/>
       <c r="B414" s="6"/>
       <c r="C414" s="13"/>
-      <c r="D414" s="6"/>
+      <c r="D414" s="4"/>
       <c r="E414" s="4"/>
-      <c r="F414" s="6"/>
+      <c r="F414" s="5"/>
     </row>
     <row r="415" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A415" s="4"/>
       <c r="B415" s="6"/>
       <c r="C415" s="13"/>
-      <c r="D415" s="6"/>
+      <c r="D415" s="4"/>
       <c r="E415" s="4"/>
-      <c r="F415" s="6"/>
+      <c r="F415" s="5"/>
     </row>
     <row r="416" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A416" s="4"/>
       <c r="B416" s="6"/>
       <c r="C416" s="13"/>
-      <c r="D416" s="6"/>
+      <c r="D416" s="4"/>
       <c r="E416" s="4"/>
-      <c r="F416" s="6"/>
+      <c r="F416" s="5"/>
     </row>
     <row r="417" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A417" s="4"/>
       <c r="B417" s="6"/>
       <c r="C417" s="13"/>
-      <c r="D417" s="6"/>
+      <c r="D417" s="4"/>
       <c r="E417" s="4"/>
-      <c r="F417" s="6"/>
+      <c r="F417" s="5"/>
     </row>
     <row r="418" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A418" s="4"/>
       <c r="B418" s="6"/>
       <c r="C418" s="13"/>
-      <c r="D418" s="6"/>
+      <c r="D418" s="4"/>
       <c r="E418" s="4"/>
-      <c r="F418" s="6"/>
+      <c r="F418" s="5"/>
     </row>
     <row r="419" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A419" s="4"/>
       <c r="B419" s="6"/>
       <c r="C419" s="13"/>
-      <c r="D419" s="6"/>
+      <c r="D419" s="4"/>
       <c r="E419" s="4"/>
-      <c r="F419" s="6"/>
+      <c r="F419" s="5"/>
     </row>
     <row r="420" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A420" s="4"/>
       <c r="B420" s="6"/>
       <c r="C420" s="13"/>
-      <c r="D420" s="6"/>
+      <c r="D420" s="4"/>
       <c r="E420" s="4"/>
-      <c r="F420" s="6"/>
+      <c r="F420" s="5"/>
     </row>
     <row r="421" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A421" s="4"/>
       <c r="B421" s="6"/>
       <c r="C421" s="13"/>
-      <c r="D421" s="6"/>
+      <c r="D421" s="4"/>
       <c r="E421" s="4"/>
-      <c r="F421" s="6"/>
+      <c r="F421" s="5"/>
     </row>
     <row r="422" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A422" s="4"/>
       <c r="B422" s="6"/>
       <c r="C422" s="13"/>
-      <c r="D422" s="6"/>
+      <c r="D422" s="4"/>
       <c r="E422" s="4"/>
-      <c r="F422" s="6"/>
+      <c r="F422" s="5"/>
     </row>
     <row r="423" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A423" s="4"/>
       <c r="B423" s="6"/>
       <c r="C423" s="13"/>
-      <c r="D423" s="6"/>
+      <c r="D423" s="4"/>
       <c r="E423" s="4"/>
-      <c r="F423" s="6"/>
+      <c r="F423" s="5"/>
     </row>
     <row r="424" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A424" s="4"/>
       <c r="B424" s="6"/>
       <c r="C424" s="13"/>
-      <c r="D424" s="6"/>
+      <c r="D424" s="4"/>
       <c r="E424" s="4"/>
-      <c r="F424" s="6"/>
+      <c r="F424" s="5"/>
     </row>
     <row r="425" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A425" s="4"/>
       <c r="B425" s="6"/>
       <c r="C425" s="13"/>
-      <c r="D425" s="6"/>
+      <c r="D425" s="4"/>
       <c r="E425" s="4"/>
-      <c r="F425" s="6"/>
+      <c r="F425" s="5"/>
     </row>
     <row r="426" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A426" s="4"/>
       <c r="B426" s="6"/>
       <c r="C426" s="13"/>
-      <c r="D426" s="6"/>
+      <c r="D426" s="4"/>
       <c r="E426" s="4"/>
-      <c r="F426" s="6"/>
+      <c r="F426" s="5"/>
     </row>
     <row r="427" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A427" s="4"/>
       <c r="B427" s="6"/>
       <c r="C427" s="13"/>
-      <c r="D427" s="6"/>
+      <c r="D427" s="4"/>
       <c r="E427" s="4"/>
-      <c r="F427" s="6"/>
+      <c r="F427" s="5"/>
     </row>
     <row r="428" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A428" s="4"/>
       <c r="B428" s="6"/>
       <c r="C428" s="13"/>
-      <c r="D428" s="6"/>
+      <c r="D428" s="4"/>
       <c r="E428" s="4"/>
-      <c r="F428" s="6"/>
+      <c r="F428" s="5"/>
     </row>
     <row r="429" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A429" s="4"/>
       <c r="B429" s="6"/>
       <c r="C429" s="13"/>
-      <c r="D429" s="6"/>
+      <c r="D429" s="4"/>
       <c r="E429" s="4"/>
-      <c r="F429" s="6"/>
+      <c r="F429" s="5"/>
     </row>
     <row r="430" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A430" s="4"/>
       <c r="B430" s="6"/>
       <c r="C430" s="13"/>
-      <c r="D430" s="6"/>
+      <c r="D430" s="4"/>
       <c r="E430" s="4"/>
-      <c r="F430" s="6"/>
+      <c r="F430" s="5"/>
     </row>
     <row r="431" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A431" s="4"/>
       <c r="B431" s="6"/>
       <c r="C431" s="13"/>
-      <c r="D431" s="6"/>
+      <c r="D431" s="4"/>
       <c r="E431" s="4"/>
-      <c r="F431" s="6"/>
+      <c r="F431" s="5"/>
     </row>
     <row r="432" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A432" s="4"/>
       <c r="B432" s="6"/>
       <c r="C432" s="13"/>
-      <c r="D432" s="6"/>
+      <c r="D432" s="4"/>
       <c r="E432" s="4"/>
-      <c r="F432" s="6"/>
+      <c r="F432" s="5"/>
     </row>
     <row r="433" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A433" s="4"/>
       <c r="B433" s="6"/>
       <c r="C433" s="13"/>
-      <c r="D433" s="6"/>
+      <c r="D433" s="4"/>
       <c r="E433" s="4"/>
-      <c r="F433" s="6"/>
+      <c r="F433" s="5"/>
     </row>
     <row r="434" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A434" s="4"/>
       <c r="B434" s="6"/>
       <c r="C434" s="13"/>
-      <c r="D434" s="6"/>
+      <c r="D434" s="4"/>
       <c r="E434" s="4"/>
-      <c r="F434" s="6"/>
+      <c r="F434" s="5"/>
     </row>
     <row r="435" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A435" s="4"/>
       <c r="B435" s="6"/>
       <c r="C435" s="13"/>
-      <c r="D435" s="6"/>
+      <c r="D435" s="4"/>
       <c r="E435" s="4"/>
-      <c r="F435" s="6"/>
+      <c r="F435" s="5"/>
     </row>
     <row r="436" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A436" s="4"/>
       <c r="B436" s="6"/>
       <c r="C436" s="13"/>
-      <c r="D436" s="6"/>
+      <c r="D436" s="4"/>
       <c r="E436" s="4"/>
-      <c r="F436" s="6"/>
+      <c r="F436" s="5"/>
     </row>
     <row r="437" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A437" s="4"/>
       <c r="B437" s="6"/>
       <c r="C437" s="13"/>
-      <c r="D437" s="6"/>
+      <c r="D437" s="4"/>
       <c r="E437" s="4"/>
-      <c r="F437" s="6"/>
+      <c r="F437" s="5"/>
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A438" s="4"/>
       <c r="B438" s="6"/>
       <c r="C438" s="13"/>
-      <c r="D438" s="6"/>
+      <c r="D438" s="4"/>
       <c r="E438" s="4"/>
-      <c r="F438" s="6"/>
+      <c r="F438" s="5"/>
     </row>
     <row r="439" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A439" s="4"/>
       <c r="B439" s="6"/>
       <c r="C439" s="13"/>
-      <c r="D439" s="6"/>
+      <c r="D439" s="4"/>
       <c r="E439" s="4"/>
-      <c r="F439" s="6"/>
+      <c r="F439" s="5"/>
     </row>
     <row r="440" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A440" s="4"/>
       <c r="B440" s="6"/>
       <c r="C440" s="13"/>
-      <c r="D440" s="6"/>
+      <c r="D440" s="4"/>
       <c r="E440" s="4"/>
-      <c r="F440" s="6"/>
+      <c r="F440" s="5"/>
     </row>
     <row r="441" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A441" s="4"/>
       <c r="B441" s="6"/>
       <c r="C441" s="13"/>
-      <c r="D441" s="6"/>
+      <c r="D441" s="4"/>
       <c r="E441" s="4"/>
-      <c r="F441" s="6"/>
+      <c r="F441" s="5"/>
     </row>
     <row r="442" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A442" s="4"/>
       <c r="B442" s="6"/>
       <c r="C442" s="13"/>
-      <c r="D442" s="6"/>
+      <c r="D442" s="4"/>
       <c r="E442" s="4"/>
-      <c r="F442" s="6"/>
+      <c r="F442" s="5"/>
     </row>
     <row r="443" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A443" s="4"/>
       <c r="B443" s="6"/>
       <c r="C443" s="13"/>
-      <c r="D443" s="6"/>
+      <c r="D443" s="4"/>
       <c r="E443" s="4"/>
-      <c r="F443" s="6"/>
+      <c r="F443" s="5"/>
     </row>
     <row r="444" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A444" s="4"/>
       <c r="B444" s="6"/>
       <c r="C444" s="13"/>
-      <c r="D444" s="6"/>
+      <c r="D444" s="4"/>
       <c r="E444" s="4"/>
-      <c r="F444" s="6"/>
+      <c r="F444" s="5"/>
     </row>
     <row r="445" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A445" s="4"/>
       <c r="B445" s="6"/>
       <c r="C445" s="13"/>
-      <c r="D445" s="6"/>
+      <c r="D445" s="4"/>
       <c r="E445" s="4"/>
-      <c r="F445" s="6"/>
+      <c r="F445" s="5"/>
     </row>
     <row r="446" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A446" s="4"/>
       <c r="B446" s="6"/>
       <c r="C446" s="13"/>
-      <c r="D446" s="6"/>
+      <c r="D446" s="4"/>
       <c r="E446" s="4"/>
-      <c r="F446" s="6"/>
+      <c r="F446" s="5"/>
     </row>
     <row r="447" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A447" s="4"/>
       <c r="B447" s="6"/>
       <c r="C447" s="13"/>
-      <c r="D447" s="6"/>
+      <c r="D447" s="4"/>
       <c r="E447" s="4"/>
-      <c r="F447" s="6"/>
+      <c r="F447" s="5"/>
     </row>
     <row r="448" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A448" s="4"/>
       <c r="B448" s="6"/>
       <c r="C448" s="13"/>
-      <c r="D448" s="6"/>
+      <c r="D448" s="4"/>
       <c r="E448" s="4"/>
-      <c r="F448" s="6"/>
+      <c r="F448" s="5"/>
     </row>
     <row r="449" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A449" s="4"/>
       <c r="B449" s="6"/>
       <c r="C449" s="13"/>
-      <c r="D449" s="6"/>
+      <c r="D449" s="4"/>
       <c r="E449" s="4"/>
-      <c r="F449" s="6"/>
+      <c r="F449" s="5"/>
     </row>
     <row r="450" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A450" s="4"/>
       <c r="B450" s="6"/>
       <c r="C450" s="13"/>
-      <c r="D450" s="6"/>
+      <c r="D450" s="4"/>
       <c r="E450" s="4"/>
-      <c r="F450" s="6"/>
+      <c r="F450" s="5"/>
     </row>
     <row r="451" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A451" s="4"/>
       <c r="B451" s="6"/>
       <c r="C451" s="13"/>
-      <c r="D451" s="6"/>
+      <c r="D451" s="4"/>
       <c r="E451" s="4"/>
-      <c r="F451" s="6"/>
+      <c r="F451" s="5"/>
     </row>
     <row r="452" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A452" s="4"/>
       <c r="B452" s="6"/>
       <c r="C452" s="13"/>
-      <c r="D452" s="6"/>
+      <c r="D452" s="4"/>
       <c r="E452" s="4"/>
-      <c r="F452" s="6"/>
+      <c r="F452" s="5"/>
     </row>
     <row r="453" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A453" s="4"/>
       <c r="B453" s="6"/>
       <c r="C453" s="13"/>
-      <c r="D453" s="6"/>
+      <c r="D453" s="4"/>
       <c r="E453" s="4"/>
-      <c r="F453" s="6"/>
+      <c r="F453" s="5"/>
     </row>
     <row r="454" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A454" s="4"/>
       <c r="B454" s="6"/>
       <c r="C454" s="13"/>
-      <c r="D454" s="6"/>
+      <c r="D454" s="4"/>
       <c r="E454" s="4"/>
-      <c r="F454" s="6"/>
+      <c r="F454" s="5"/>
     </row>
     <row r="455" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A455" s="4"/>
       <c r="B455" s="6"/>
       <c r="C455" s="13"/>
-      <c r="D455" s="6"/>
+      <c r="D455" s="4"/>
       <c r="E455" s="4"/>
-      <c r="F455" s="6"/>
+      <c r="F455" s="5"/>
     </row>
     <row r="456" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A456" s="4"/>
       <c r="B456" s="6"/>
       <c r="C456" s="13"/>
-      <c r="D456" s="6"/>
+      <c r="D456" s="4"/>
       <c r="E456" s="4"/>
-      <c r="F456" s="6"/>
+      <c r="F456" s="5"/>
     </row>
     <row r="457" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A457" s="4"/>
       <c r="B457" s="6"/>
       <c r="C457" s="13"/>
-      <c r="D457" s="6"/>
+      <c r="D457" s="4"/>
       <c r="E457" s="4"/>
-      <c r="F457" s="6"/>
+      <c r="F457" s="5"/>
     </row>
     <row r="458" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A458" s="4"/>
       <c r="B458" s="6"/>
       <c r="C458" s="13"/>
-      <c r="D458" s="6"/>
+      <c r="D458" s="4"/>
       <c r="E458" s="4"/>
-      <c r="F458" s="6"/>
+      <c r="F458" s="5"/>
     </row>
     <row r="459" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A459" s="4"/>
       <c r="B459" s="6"/>
       <c r="C459" s="13"/>
-      <c r="D459" s="6"/>
+      <c r="D459" s="4"/>
       <c r="E459" s="4"/>
-      <c r="F459" s="6"/>
+      <c r="F459" s="5"/>
     </row>
     <row r="460" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A460" s="4"/>
       <c r="B460" s="6"/>
       <c r="C460" s="13"/>
-      <c r="D460" s="6"/>
+      <c r="D460" s="4"/>
       <c r="E460" s="4"/>
-      <c r="F460" s="6"/>
+      <c r="F460" s="5"/>
     </row>
     <row r="461" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A461" s="4"/>
       <c r="B461" s="6"/>
       <c r="C461" s="13"/>
-      <c r="D461" s="6"/>
+      <c r="D461" s="4"/>
       <c r="E461" s="4"/>
-      <c r="F461" s="6"/>
+      <c r="F461" s="5"/>
     </row>
     <row r="462" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A462" s="4"/>
       <c r="B462" s="6"/>
       <c r="C462" s="13"/>
-      <c r="D462" s="6"/>
+      <c r="D462" s="4"/>
       <c r="E462" s="4"/>
-      <c r="F462" s="6"/>
+      <c r="F462" s="5"/>
     </row>
     <row r="463" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A463" s="4"/>
       <c r="B463" s="6"/>
       <c r="C463" s="13"/>
-      <c r="D463" s="6"/>
+      <c r="D463" s="4"/>
       <c r="E463" s="4"/>
-      <c r="F463" s="6"/>
+      <c r="F463" s="5"/>
     </row>
     <row r="464" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A464" s="4"/>
       <c r="B464" s="6"/>
       <c r="C464" s="13"/>
-      <c r="D464" s="6"/>
+      <c r="D464" s="4"/>
       <c r="E464" s="4"/>
-      <c r="F464" s="6"/>
+      <c r="F464" s="5"/>
     </row>
     <row r="465" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A465" s="4"/>
       <c r="B465" s="6"/>
       <c r="C465" s="13"/>
-      <c r="D465" s="6"/>
+      <c r="D465" s="4"/>
       <c r="E465" s="4"/>
-      <c r="F465" s="6"/>
+      <c r="F465" s="5"/>
     </row>
     <row r="466" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A466" s="4"/>
       <c r="B466" s="6"/>
       <c r="C466" s="13"/>
-      <c r="D466" s="6"/>
+      <c r="D466" s="4"/>
       <c r="E466" s="4"/>
-      <c r="F466" s="6"/>
+      <c r="F466" s="5"/>
     </row>
     <row r="467" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A467" s="4"/>
       <c r="B467" s="6"/>
       <c r="C467" s="13"/>
-      <c r="D467" s="6"/>
+      <c r="D467" s="4"/>
       <c r="E467" s="4"/>
-      <c r="F467" s="6"/>
+      <c r="F467" s="5"/>
     </row>
     <row r="468" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A468" s="4"/>
       <c r="B468" s="6"/>
       <c r="C468" s="13"/>
-      <c r="D468" s="6"/>
+      <c r="D468" s="4"/>
       <c r="E468" s="4"/>
-      <c r="F468" s="6"/>
+      <c r="F468" s="5"/>
     </row>
     <row r="469" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A469" s="4"/>
       <c r="B469" s="6"/>
       <c r="C469" s="13"/>
-      <c r="D469" s="6"/>
+      <c r="D469" s="4"/>
       <c r="E469" s="4"/>
-      <c r="F469" s="6"/>
+      <c r="F469" s="5"/>
     </row>
     <row r="470" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A470" s="4"/>
       <c r="B470" s="6"/>
       <c r="C470" s="13"/>
-      <c r="D470" s="6"/>
+      <c r="D470" s="4"/>
       <c r="E470" s="4"/>
-      <c r="F470" s="6"/>
+      <c r="F470" s="5"/>
     </row>
     <row r="471" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A471" s="4"/>
       <c r="B471" s="6"/>
       <c r="C471" s="13"/>
-      <c r="D471" s="6"/>
+      <c r="D471" s="4"/>
       <c r="E471" s="4"/>
-      <c r="F471" s="6"/>
+      <c r="F471" s="5"/>
     </row>
     <row r="472" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A472" s="4"/>
       <c r="B472" s="6"/>
       <c r="C472" s="13"/>
-      <c r="D472" s="6"/>
+      <c r="D472" s="4"/>
       <c r="E472" s="4"/>
-      <c r="F472" s="6"/>
+      <c r="F472" s="5"/>
     </row>
     <row r="473" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A473" s="4"/>
       <c r="B473" s="6"/>
       <c r="C473" s="13"/>
-      <c r="D473" s="6"/>
+      <c r="D473" s="4"/>
       <c r="E473" s="4"/>
-      <c r="F473" s="6"/>
+      <c r="F473" s="5"/>
     </row>
     <row r="474" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A474" s="4"/>
       <c r="B474" s="6"/>
       <c r="C474" s="13"/>
-      <c r="D474" s="6"/>
+      <c r="D474" s="4"/>
       <c r="E474" s="4"/>
-      <c r="F474" s="6"/>
+      <c r="F474" s="5"/>
     </row>
     <row r="475" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A475" s="4"/>
       <c r="B475" s="6"/>
       <c r="C475" s="13"/>
-      <c r="D475" s="6"/>
+      <c r="D475" s="4"/>
       <c r="E475" s="4"/>
-      <c r="F475" s="6"/>
+      <c r="F475" s="5"/>
     </row>
     <row r="476" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A476" s="4"/>
       <c r="B476" s="6"/>
       <c r="C476" s="13"/>
-      <c r="D476" s="6"/>
+      <c r="D476" s="4"/>
       <c r="E476" s="4"/>
-      <c r="F476" s="6"/>
+      <c r="F476" s="5"/>
     </row>
     <row r="477" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A477" s="4"/>
       <c r="B477" s="6"/>
       <c r="C477" s="13"/>
-      <c r="D477" s="6"/>
+      <c r="D477" s="4"/>
       <c r="E477" s="4"/>
-      <c r="F477" s="6"/>
+      <c r="F477" s="5"/>
     </row>
     <row r="478" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A478" s="4"/>
       <c r="B478" s="6"/>
       <c r="C478" s="13"/>
-      <c r="D478" s="6"/>
+      <c r="D478" s="4"/>
       <c r="E478" s="4"/>
-      <c r="F478" s="6"/>
+      <c r="F478" s="5"/>
     </row>
     <row r="479" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A479" s="4"/>
       <c r="B479" s="6"/>
       <c r="C479" s="13"/>
-      <c r="D479" s="6"/>
+      <c r="D479" s="4"/>
       <c r="E479" s="4"/>
-      <c r="F479" s="6"/>
+      <c r="F479" s="5"/>
     </row>
     <row r="480" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A480" s="4"/>
       <c r="B480" s="6"/>
       <c r="C480" s="13"/>
-      <c r="D480" s="6"/>
+      <c r="D480" s="4"/>
       <c r="E480" s="4"/>
-      <c r="F480" s="6"/>
+      <c r="F480" s="5"/>
     </row>
     <row r="481" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A481" s="4"/>
       <c r="B481" s="6"/>
       <c r="C481" s="13"/>
-      <c r="D481" s="6"/>
+      <c r="D481" s="4"/>
       <c r="E481" s="4"/>
-      <c r="F481" s="6"/>
+      <c r="F481" s="5"/>
     </row>
     <row r="482" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A482" s="4"/>
       <c r="B482" s="6"/>
       <c r="C482" s="13"/>
-      <c r="D482" s="6"/>
+      <c r="D482" s="4"/>
       <c r="E482" s="4"/>
-      <c r="F482" s="6"/>
+      <c r="F482" s="5"/>
     </row>
     <row r="483" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A483" s="4"/>
       <c r="B483" s="6"/>
       <c r="C483" s="13"/>
-      <c r="D483" s="6"/>
+      <c r="D483" s="4"/>
       <c r="E483" s="4"/>
-      <c r="F483" s="6"/>
+      <c r="F483" s="5"/>
     </row>
     <row r="484" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A484" s="4"/>
       <c r="B484" s="6"/>
       <c r="C484" s="13"/>
-      <c r="D484" s="6"/>
+      <c r="D484" s="4"/>
       <c r="E484" s="4"/>
-      <c r="F484" s="6"/>
+      <c r="F484" s="5"/>
     </row>
     <row r="485" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A485" s="4"/>
       <c r="B485" s="6"/>
       <c r="C485" s="13"/>
-      <c r="D485" s="6"/>
+      <c r="D485" s="4"/>
       <c r="E485" s="4"/>
-      <c r="F485" s="6"/>
+      <c r="F485" s="5"/>
     </row>
     <row r="486" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A486" s="4"/>
       <c r="B486" s="6"/>
       <c r="C486" s="13"/>
-      <c r="D486" s="6"/>
+      <c r="D486" s="4"/>
       <c r="E486" s="4"/>
-      <c r="F486" s="6"/>
+      <c r="F486" s="5"/>
     </row>
     <row r="487" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A487" s="4"/>
       <c r="B487" s="6"/>
       <c r="C487" s="13"/>
-      <c r="D487" s="6"/>
+      <c r="D487" s="4"/>
       <c r="E487" s="4"/>
-      <c r="F487" s="6"/>
+      <c r="F487" s="5"/>
     </row>
     <row r="488" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A488" s="4"/>
       <c r="B488" s="6"/>
       <c r="C488" s="13"/>
-      <c r="D488" s="6"/>
+      <c r="D488" s="4"/>
       <c r="E488" s="4"/>
-      <c r="F488" s="6"/>
+      <c r="F488" s="5"/>
     </row>
     <row r="489" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A489" s="4"/>
       <c r="B489" s="6"/>
       <c r="C489" s="13"/>
-      <c r="D489" s="6"/>
+      <c r="D489" s="4"/>
       <c r="E489" s="4"/>
-      <c r="F489" s="6"/>
+      <c r="F489" s="5"/>
     </row>
     <row r="490" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A490" s="4"/>
       <c r="B490" s="6"/>
       <c r="C490" s="13"/>
-      <c r="D490" s="6"/>
+      <c r="D490" s="4"/>
       <c r="E490" s="4"/>
-      <c r="F490" s="6"/>
+      <c r="F490" s="5"/>
     </row>
     <row r="491" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A491" s="4"/>
       <c r="B491" s="6"/>
       <c r="C491" s="13"/>
-      <c r="D491" s="6"/>
+      <c r="D491" s="4"/>
       <c r="E491" s="4"/>
-      <c r="F491" s="6"/>
+      <c r="F491" s="5"/>
     </row>
     <row r="492" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A492" s="4"/>
       <c r="B492" s="6"/>
       <c r="C492" s="13"/>
-      <c r="D492" s="6"/>
+      <c r="D492" s="4"/>
       <c r="E492" s="4"/>
-      <c r="F492" s="6"/>
+      <c r="F492" s="5"/>
     </row>
     <row r="493" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A493" s="4"/>
       <c r="B493" s="6"/>
       <c r="C493" s="13"/>
-      <c r="D493" s="6"/>
+      <c r="D493" s="4"/>
       <c r="E493" s="4"/>
-      <c r="F493" s="6"/>
+      <c r="F493" s="5"/>
     </row>
     <row r="494" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A494" s="4"/>
       <c r="B494" s="6"/>
       <c r="C494" s="13"/>
-      <c r="D494" s="6"/>
+      <c r="D494" s="4"/>
       <c r="E494" s="4"/>
-      <c r="F494" s="6"/>
+      <c r="F494" s="5"/>
     </row>
     <row r="495" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A495" s="4"/>
       <c r="B495" s="6"/>
       <c r="C495" s="13"/>
-      <c r="D495" s="6"/>
+      <c r="D495" s="4"/>
       <c r="E495" s="4"/>
-      <c r="F495" s="6"/>
+      <c r="F495" s="5"/>
     </row>
     <row r="496" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A496" s="4"/>
       <c r="B496" s="6"/>
       <c r="C496" s="13"/>
-      <c r="D496" s="6"/>
+      <c r="D496" s="4"/>
       <c r="E496" s="4"/>
-      <c r="F496" s="6"/>
+      <c r="F496" s="5"/>
     </row>
     <row r="497" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A497" s="4"/>
       <c r="B497" s="6"/>
       <c r="C497" s="13"/>
-      <c r="D497" s="6"/>
+      <c r="D497" s="4"/>
       <c r="E497" s="4"/>
-      <c r="F497" s="6"/>
+      <c r="F497" s="5"/>
     </row>
     <row r="498" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A498" s="4"/>
       <c r="B498" s="6"/>
       <c r="C498" s="13"/>
-      <c r="D498" s="6"/>
+      <c r="D498" s="4"/>
       <c r="E498" s="4"/>
-      <c r="F498" s="6"/>
+      <c r="F498" s="5"/>
     </row>
     <row r="499" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A499" s="4"/>
       <c r="B499" s="6"/>
       <c r="C499" s="13"/>
-      <c r="D499" s="6"/>
+      <c r="D499" s="4"/>
       <c r="E499" s="4"/>
-      <c r="F499" s="6"/>
+      <c r="F499" s="5"/>
     </row>
     <row r="500" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A500" s="4"/>
       <c r="B500" s="6"/>
       <c r="C500" s="13"/>
-      <c r="D500" s="6"/>
+      <c r="D500" s="4"/>
       <c r="E500" s="4"/>
-      <c r="F500" s="6"/>
+      <c r="F500" s="5"/>
     </row>
     <row r="501" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A501" s="4"/>
       <c r="B501" s="6"/>
       <c r="C501" s="13"/>
-      <c r="D501" s="6"/>
+      <c r="D501" s="4"/>
       <c r="E501" s="4"/>
-      <c r="F501" s="6"/>
+      <c r="F501" s="5"/>
     </row>
     <row r="502" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A502" s="4"/>
       <c r="B502" s="6"/>
       <c r="C502" s="13"/>
-      <c r="D502" s="6"/>
+      <c r="D502" s="4"/>
       <c r="E502" s="4"/>
-      <c r="F502" s="6"/>
+      <c r="F502" s="5"/>
     </row>
     <row r="503" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A503" s="4"/>
       <c r="B503" s="6"/>
       <c r="C503" s="13"/>
-      <c r="D503" s="6"/>
+      <c r="D503" s="4"/>
       <c r="E503" s="4"/>
-      <c r="F503" s="6"/>
+      <c r="F503" s="5"/>
     </row>
     <row r="504" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A504" s="4"/>
       <c r="B504" s="6"/>
       <c r="C504" s="13"/>
-      <c r="D504" s="6"/>
+      <c r="D504" s="4"/>
       <c r="E504" s="4"/>
-      <c r="F504" s="6"/>
+      <c r="F504" s="5"/>
     </row>
     <row r="505" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A505" s="4"/>
       <c r="B505" s="6"/>
       <c r="C505" s="13"/>
-      <c r="D505" s="6"/>
+      <c r="D505" s="4"/>
       <c r="E505" s="4"/>
-      <c r="F505" s="6"/>
+      <c r="F505" s="5"/>
     </row>
     <row r="506" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A506" s="4"/>
       <c r="B506" s="6"/>
       <c r="C506" s="13"/>
-      <c r="D506" s="6"/>
+      <c r="D506" s="4"/>
       <c r="E506" s="4"/>
-      <c r="F506" s="6"/>
+      <c r="F506" s="5"/>
     </row>
     <row r="507" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A507" s="4"/>
       <c r="B507" s="6"/>
       <c r="C507" s="13"/>
-      <c r="D507" s="6"/>
+      <c r="D507" s="4"/>
       <c r="E507" s="4"/>
-      <c r="F507" s="6"/>
+      <c r="F507" s="5"/>
     </row>
     <row r="508" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A508" s="4"/>
       <c r="B508" s="6"/>
       <c r="C508" s="13"/>
-      <c r="D508" s="6"/>
+      <c r="D508" s="4"/>
       <c r="E508" s="4"/>
-      <c r="F508" s="6"/>
+      <c r="F508" s="5"/>
     </row>
     <row r="509" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A509" s="4"/>
       <c r="B509" s="6"/>
       <c r="C509" s="13"/>
-      <c r="D509" s="6"/>
+      <c r="D509" s="4"/>
       <c r="E509" s="4"/>
-      <c r="F509" s="6"/>
+      <c r="F509" s="5"/>
     </row>
     <row r="510" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A510" s="4"/>
       <c r="B510" s="6"/>
       <c r="C510" s="13"/>
-      <c r="D510" s="6"/>
+      <c r="D510" s="4"/>
       <c r="E510" s="4"/>
-      <c r="F510" s="6"/>
+      <c r="F510" s="5"/>
     </row>
     <row r="511" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A511" s="4"/>
       <c r="B511" s="6"/>
       <c r="C511" s="13"/>
-      <c r="D511" s="6"/>
+      <c r="D511" s="4"/>
       <c r="E511" s="4"/>
-      <c r="F511" s="6"/>
+      <c r="F511" s="5"/>
     </row>
     <row r="512" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A512" s="4"/>
       <c r="B512" s="6"/>
       <c r="C512" s="13"/>
-      <c r="D512" s="6"/>
+      <c r="D512" s="4"/>
       <c r="E512" s="4"/>
-      <c r="F512" s="6"/>
+      <c r="F512" s="5"/>
     </row>
     <row r="513" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A513" s="4"/>
       <c r="B513" s="6"/>
       <c r="C513" s="13"/>
-      <c r="D513" s="6"/>
+      <c r="D513" s="4"/>
       <c r="E513" s="4"/>
-      <c r="F513" s="6"/>
+      <c r="F513" s="5"/>
     </row>
     <row r="514" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A514" s="4"/>
       <c r="B514" s="6"/>
       <c r="C514" s="13"/>
-      <c r="D514" s="6"/>
+      <c r="D514" s="4"/>
       <c r="E514" s="4"/>
-      <c r="F514" s="6"/>
+      <c r="F514" s="5"/>
     </row>
     <row r="515" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A515" s="4"/>
       <c r="B515" s="6"/>
       <c r="C515" s="13"/>
-      <c r="D515" s="6"/>
+      <c r="D515" s="4"/>
       <c r="E515" s="4"/>
-      <c r="F515" s="6"/>
+      <c r="F515" s="5"/>
     </row>
     <row r="516" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A516" s="4"/>
       <c r="B516" s="6"/>
       <c r="C516" s="13"/>
-      <c r="D516" s="6"/>
+      <c r="D516" s="4"/>
       <c r="E516" s="4"/>
-      <c r="F516" s="6"/>
+      <c r="F516" s="5"/>
     </row>
     <row r="517" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A517" s="4"/>
       <c r="B517" s="6"/>
       <c r="C517" s="13"/>
-      <c r="D517" s="6"/>
+      <c r="D517" s="4"/>
       <c r="E517" s="4"/>
-      <c r="F517" s="6"/>
+      <c r="F517" s="5"/>
     </row>
     <row r="518" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A518" s="4"/>
       <c r="B518" s="6"/>
       <c r="C518" s="13"/>
-      <c r="D518" s="6"/>
+      <c r="D518" s="4"/>
       <c r="E518" s="4"/>
-      <c r="F518" s="6"/>
+      <c r="F518" s="5"/>
     </row>
     <row r="519" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A519" s="4"/>
       <c r="B519" s="6"/>
       <c r="C519" s="13"/>
-      <c r="D519" s="6"/>
+      <c r="D519" s="4"/>
       <c r="E519" s="4"/>
-      <c r="F519" s="6"/>
+      <c r="F519" s="5"/>
     </row>
     <row r="520" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A520" s="4"/>
       <c r="B520" s="6"/>
       <c r="C520" s="13"/>
-      <c r="D520" s="6"/>
+      <c r="D520" s="4"/>
       <c r="E520" s="4"/>
-      <c r="F520" s="6"/>
+      <c r="F520" s="5"/>
     </row>
     <row r="521" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A521" s="4"/>
       <c r="B521" s="6"/>
       <c r="C521" s="13"/>
-      <c r="D521" s="6"/>
+      <c r="D521" s="4"/>
       <c r="E521" s="4"/>
-      <c r="F521" s="6"/>
+      <c r="F521" s="5"/>
     </row>
     <row r="522" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A522" s="4"/>
       <c r="B522" s="6"/>
       <c r="C522" s="13"/>
-      <c r="D522" s="6"/>
+      <c r="D522" s="4"/>
       <c r="E522" s="4"/>
-      <c r="F522" s="6"/>
+      <c r="F522" s="5"/>
     </row>
     <row r="523" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A523" s="4"/>
       <c r="B523" s="6"/>
       <c r="C523" s="13"/>
-      <c r="D523" s="6"/>
+      <c r="D523" s="4"/>
       <c r="E523" s="4"/>
-      <c r="F523" s="6"/>
+      <c r="F523" s="5"/>
     </row>
     <row r="524" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A524" s="4"/>
       <c r="B524" s="6"/>
       <c r="C524" s="13"/>
-      <c r="D524" s="6"/>
+      <c r="D524" s="4"/>
       <c r="E524" s="4"/>
-      <c r="F524" s="6"/>
+      <c r="F524" s="5"/>
     </row>
     <row r="525" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A525" s="4"/>
       <c r="B525" s="6"/>
       <c r="C525" s="13"/>
-      <c r="D525" s="6"/>
+      <c r="D525" s="4"/>
       <c r="E525" s="4"/>
-      <c r="F525" s="6"/>
+      <c r="F525" s="5"/>
     </row>
     <row r="526" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A526" s="4"/>
       <c r="B526" s="6"/>
       <c r="C526" s="13"/>
-      <c r="D526" s="6"/>
+      <c r="D526" s="4"/>
       <c r="E526" s="4"/>
-      <c r="F526" s="6"/>
+      <c r="F526" s="5"/>
     </row>
     <row r="527" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A527" s="4"/>
       <c r="B527" s="6"/>
       <c r="C527" s="13"/>
-      <c r="D527" s="6"/>
+      <c r="D527" s="4"/>
       <c r="E527" s="4"/>
-      <c r="F527" s="6"/>
+      <c r="F527" s="5"/>
     </row>
     <row r="528" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A528" s="4"/>
       <c r="B528" s="6"/>
       <c r="C528" s="13"/>
-      <c r="D528" s="6"/>
+      <c r="D528" s="4"/>
       <c r="E528" s="4"/>
-      <c r="F528" s="6"/>
+      <c r="F528" s="5"/>
     </row>
     <row r="529" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A529" s="4"/>
       <c r="B529" s="6"/>
       <c r="C529" s="13"/>
-      <c r="D529" s="6"/>
+      <c r="D529" s="4"/>
       <c r="E529" s="4"/>
-      <c r="F529" s="6"/>
+      <c r="F529" s="5"/>
     </row>
     <row r="530" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A530" s="4"/>
       <c r="B530" s="6"/>
       <c r="C530" s="13"/>
-      <c r="D530" s="6"/>
+      <c r="D530" s="4"/>
       <c r="E530" s="4"/>
-      <c r="F530" s="6"/>
+      <c r="F530" s="5"/>
     </row>
     <row r="531" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A531" s="4"/>
       <c r="B531" s="6"/>
       <c r="C531" s="13"/>
-      <c r="D531" s="6"/>
+      <c r="D531" s="4"/>
       <c r="E531" s="4"/>
-      <c r="F531" s="6"/>
+      <c r="F531" s="5"/>
     </row>
     <row r="532" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A532" s="4"/>
       <c r="B532" s="6"/>
       <c r="C532" s="13"/>
-      <c r="D532" s="6"/>
+      <c r="D532" s="4"/>
       <c r="E532" s="4"/>
-      <c r="F532" s="6"/>
+      <c r="F532" s="5"/>
     </row>
     <row r="533" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A533" s="4"/>
       <c r="B533" s="6"/>
       <c r="C533" s="13"/>
-      <c r="D533" s="6"/>
+      <c r="D533" s="4"/>
       <c r="E533" s="4"/>
-      <c r="F533" s="6"/>
+      <c r="F533" s="5"/>
     </row>
     <row r="534" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A534" s="4"/>
       <c r="B534" s="6"/>
       <c r="C534" s="13"/>
-      <c r="D534" s="6"/>
+      <c r="D534" s="4"/>
       <c r="E534" s="4"/>
-      <c r="F534" s="6"/>
+      <c r="F534" s="5"/>
     </row>
     <row r="535" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A535" s="4"/>
       <c r="B535" s="6"/>
       <c r="C535" s="13"/>
-      <c r="D535" s="6"/>
+      <c r="D535" s="4"/>
       <c r="E535" s="4"/>
-      <c r="F535" s="6"/>
+      <c r="F535" s="5"/>
     </row>
     <row r="536" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A536" s="4"/>
       <c r="B536" s="6"/>
       <c r="C536" s="13"/>
-      <c r="D536" s="6"/>
+      <c r="D536" s="4"/>
       <c r="E536" s="4"/>
-      <c r="F536" s="6"/>
+      <c r="F536" s="5"/>
     </row>
     <row r="537" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A537" s="4"/>
       <c r="B537" s="6"/>
       <c r="C537" s="13"/>
-      <c r="D537" s="6"/>
+      <c r="D537" s="4"/>
       <c r="E537" s="4"/>
-      <c r="F537" s="6"/>
+      <c r="F537" s="5"/>
     </row>
     <row r="538" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A538" s="4"/>
       <c r="B538" s="6"/>
       <c r="C538" s="13"/>
-      <c r="D538" s="6"/>
+      <c r="D538" s="4"/>
       <c r="E538" s="4"/>
-      <c r="F538" s="6"/>
+      <c r="F538" s="5"/>
     </row>
     <row r="539" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A539" s="4"/>
       <c r="B539" s="6"/>
       <c r="C539" s="13"/>
-      <c r="D539" s="6"/>
+      <c r="D539" s="4"/>
       <c r="E539" s="4"/>
-      <c r="F539" s="6"/>
+      <c r="F539" s="5"/>
     </row>
     <row r="540" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A540" s="4"/>
       <c r="B540" s="6"/>
       <c r="C540" s="13"/>
-      <c r="D540" s="6"/>
+      <c r="D540" s="4"/>
       <c r="E540" s="4"/>
-      <c r="F540" s="6"/>
+      <c r="F540" s="5"/>
     </row>
     <row r="541" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A541" s="4"/>
       <c r="B541" s="6"/>
       <c r="C541" s="13"/>
-      <c r="D541" s="6"/>
+      <c r="D541" s="4"/>
       <c r="E541" s="4"/>
-      <c r="F541" s="6"/>
+      <c r="F541" s="5"/>
     </row>
     <row r="542" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A542" s="4"/>
       <c r="B542" s="6"/>
       <c r="C542" s="13"/>
-      <c r="D542" s="6"/>
+      <c r="D542" s="4"/>
       <c r="E542" s="4"/>
-      <c r="F542" s="6"/>
+      <c r="F542" s="5"/>
     </row>
     <row r="543" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A543" s="4"/>
       <c r="B543" s="6"/>
       <c r="C543" s="13"/>
-      <c r="D543" s="6"/>
+      <c r="D543" s="4"/>
       <c r="E543" s="4"/>
-      <c r="F543" s="6"/>
+      <c r="F543" s="5"/>
     </row>
     <row r="544" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A544" s="4"/>
       <c r="B544" s="6"/>
       <c r="C544" s="13"/>
-      <c r="D544" s="6"/>
+      <c r="D544" s="4"/>
       <c r="E544" s="4"/>
-      <c r="F544" s="6"/>
+      <c r="F544" s="5"/>
     </row>
     <row r="545" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A545" s="4"/>
       <c r="B545" s="6"/>
       <c r="C545" s="13"/>
-      <c r="D545" s="6"/>
+      <c r="D545" s="4"/>
       <c r="E545" s="4"/>
-      <c r="F545" s="6"/>
+      <c r="F545" s="5"/>
     </row>
     <row r="546" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A546" s="4"/>
       <c r="B546" s="6"/>
       <c r="C546" s="13"/>
-      <c r="D546" s="6"/>
+      <c r="D546" s="4"/>
       <c r="E546" s="4"/>
-      <c r="F546" s="6"/>
+      <c r="F546" s="5"/>
     </row>
     <row r="547" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A547" s="4"/>
       <c r="B547" s="6"/>
       <c r="C547" s="13"/>
-      <c r="D547" s="6"/>
+      <c r="D547" s="4"/>
       <c r="E547" s="4"/>
-      <c r="F547" s="6"/>
+      <c r="F547" s="5"/>
     </row>
     <row r="548" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A548" s="4"/>
       <c r="B548" s="6"/>
       <c r="C548" s="13"/>
-      <c r="D548" s="6"/>
+      <c r="D548" s="4"/>
       <c r="E548" s="4"/>
-      <c r="F548" s="6"/>
+      <c r="F548" s="5"/>
     </row>
     <row r="549" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A549" s="4"/>
       <c r="B549" s="6"/>
       <c r="C549" s="13"/>
-      <c r="D549" s="6"/>
+      <c r="D549" s="4"/>
       <c r="E549" s="4"/>
-      <c r="F549" s="6"/>
+      <c r="F549" s="5"/>
     </row>
     <row r="550" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A550" s="4"/>
       <c r="B550" s="6"/>
       <c r="C550" s="13"/>
-      <c r="D550" s="6"/>
+      <c r="D550" s="4"/>
       <c r="E550" s="4"/>
-      <c r="F550" s="6"/>
+      <c r="F550" s="5"/>
     </row>
     <row r="551" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A551" s="4"/>
       <c r="B551" s="6"/>
       <c r="C551" s="13"/>
-      <c r="D551" s="6"/>
+      <c r="D551" s="4"/>
       <c r="E551" s="4"/>
-      <c r="F551" s="6"/>
+      <c r="F551" s="5"/>
     </row>
     <row r="552" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A552" s="4"/>
       <c r="B552" s="6"/>
       <c r="C552" s="13"/>
-      <c r="D552" s="6"/>
+      <c r="D552" s="4"/>
       <c r="E552" s="4"/>
-      <c r="F552" s="6"/>
+      <c r="F552" s="5"/>
     </row>
     <row r="553" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A553" s="4"/>
       <c r="B553" s="6"/>
       <c r="C553" s="13"/>
-      <c r="D553" s="6"/>
+      <c r="D553" s="4"/>
       <c r="E553" s="4"/>
-      <c r="F553" s="6"/>
+      <c r="F553" s="5"/>
     </row>
     <row r="554" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A554" s="4"/>
       <c r="B554" s="6"/>
       <c r="C554" s="13"/>
-      <c r="D554" s="6"/>
+      <c r="D554" s="4"/>
       <c r="E554" s="4"/>
-      <c r="F554" s="6"/>
+      <c r="F554" s="5"/>
     </row>
     <row r="555" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A555" s="4"/>
       <c r="B555" s="6"/>
       <c r="C555" s="13"/>
-      <c r="D555" s="6"/>
+      <c r="D555" s="4"/>
       <c r="E555" s="4"/>
-      <c r="F555" s="6"/>
+      <c r="F555" s="5"/>
     </row>
     <row r="556" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A556" s="4"/>
       <c r="B556" s="6"/>
       <c r="C556" s="13"/>
-      <c r="D556" s="6"/>
+      <c r="D556" s="4"/>
       <c r="E556" s="4"/>
-      <c r="F556" s="6"/>
+      <c r="F556" s="5"/>
     </row>
     <row r="557" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A557" s="4"/>
       <c r="B557" s="6"/>
       <c r="C557" s="13"/>
-      <c r="D557" s="6"/>
+      <c r="D557" s="4"/>
       <c r="E557" s="4"/>
-      <c r="F557" s="6"/>
+      <c r="F557" s="5"/>
     </row>
     <row r="558" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A558" s="4"/>
       <c r="B558" s="6"/>
       <c r="C558" s="13"/>
-      <c r="D558" s="6"/>
+      <c r="D558" s="4"/>
       <c r="E558" s="4"/>
-      <c r="F558" s="6"/>
+      <c r="F558" s="5"/>
     </row>
     <row r="559" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A559" s="4"/>
       <c r="B559" s="6"/>
       <c r="C559" s="13"/>
-      <c r="D559" s="6"/>
+      <c r="D559" s="4"/>
       <c r="E559" s="4"/>
-      <c r="F559" s="6"/>
+      <c r="F559" s="5"/>
     </row>
     <row r="560" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A560" s="4"/>
       <c r="B560" s="6"/>
       <c r="C560" s="13"/>
-      <c r="D560" s="6"/>
+      <c r="D560" s="4"/>
       <c r="E560" s="4"/>
-      <c r="F560" s="6"/>
+      <c r="F560" s="5"/>
     </row>
     <row r="561" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A561" s="4"/>
       <c r="B561" s="6"/>
       <c r="C561" s="13"/>
-      <c r="D561" s="6"/>
+      <c r="D561" s="4"/>
       <c r="E561" s="4"/>
-      <c r="F561" s="6"/>
+      <c r="F561" s="5"/>
     </row>
     <row r="562" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A562" s="4"/>
       <c r="B562" s="6"/>
       <c r="C562" s="13"/>
-      <c r="D562" s="6"/>
+      <c r="D562" s="4"/>
       <c r="E562" s="4"/>
-      <c r="F562" s="6"/>
+      <c r="F562" s="5"/>
     </row>
     <row r="563" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A563" s="4"/>
       <c r="B563" s="6"/>
       <c r="C563" s="13"/>
-      <c r="D563" s="6"/>
+      <c r="D563" s="4"/>
       <c r="E563" s="4"/>
-      <c r="F563" s="6"/>
+      <c r="F563" s="5"/>
     </row>
     <row r="564" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A564" s="4"/>
       <c r="B564" s="6"/>
       <c r="C564" s="13"/>
-      <c r="D564" s="6"/>
+      <c r="D564" s="4"/>
       <c r="E564" s="4"/>
-      <c r="F564" s="6"/>
+      <c r="F564" s="5"/>
     </row>
     <row r="565" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A565" s="4"/>
       <c r="B565" s="6"/>
       <c r="C565" s="13"/>
-      <c r="D565" s="6"/>
+      <c r="D565" s="4"/>
       <c r="E565" s="4"/>
-      <c r="F565" s="6"/>
+      <c r="F565" s="5"/>
     </row>
     <row r="566" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A566" s="4"/>
       <c r="B566" s="6"/>
       <c r="C566" s="13"/>
-      <c r="D566" s="6"/>
+      <c r="D566" s="4"/>
       <c r="E566" s="4"/>
-      <c r="F566" s="6"/>
+      <c r="F566" s="5"/>
     </row>
     <row r="567" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A567" s="4"/>
       <c r="B567" s="6"/>
       <c r="C567" s="13"/>
-      <c r="D567" s="6"/>
+      <c r="D567" s="4"/>
       <c r="E567" s="4"/>
-      <c r="F567" s="6"/>
+      <c r="F567" s="5"/>
     </row>
     <row r="568" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A568" s="4"/>
       <c r="B568" s="6"/>
       <c r="C568" s="13"/>
-      <c r="D568" s="6"/>
+      <c r="D568" s="4"/>
       <c r="E568" s="4"/>
-      <c r="F568" s="6"/>
+      <c r="F568" s="5"/>
     </row>
     <row r="569" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A569" s="4"/>
       <c r="B569" s="6"/>
       <c r="C569" s="13"/>
-      <c r="D569" s="6"/>
+      <c r="D569" s="4"/>
       <c r="E569" s="4"/>
-      <c r="F569" s="6"/>
+      <c r="F569" s="5"/>
     </row>
     <row r="570" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A570" s="4"/>
       <c r="B570" s="6"/>
       <c r="C570" s="13"/>
-      <c r="D570" s="6"/>
+      <c r="D570" s="4"/>
       <c r="E570" s="4"/>
-      <c r="F570" s="6"/>
+      <c r="F570" s="5"/>
     </row>
     <row r="571" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A571" s="4"/>
       <c r="B571" s="6"/>
       <c r="C571" s="13"/>
-      <c r="D571" s="6"/>
+      <c r="D571" s="4"/>
       <c r="E571" s="4"/>
-      <c r="F571" s="6"/>
+      <c r="F571" s="5"/>
     </row>
     <row r="572" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A572" s="4"/>
       <c r="B572" s="6"/>
       <c r="C572" s="13"/>
-      <c r="D572" s="6"/>
+      <c r="D572" s="4"/>
       <c r="E572" s="4"/>
-      <c r="F572" s="6"/>
+      <c r="F572" s="5"/>
     </row>
     <row r="573" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A573" s="4"/>
       <c r="B573" s="6"/>
       <c r="C573" s="13"/>
-      <c r="D573" s="6"/>
+      <c r="D573" s="4"/>
       <c r="E573" s="4"/>
-      <c r="F573" s="6"/>
+      <c r="F573" s="5"/>
     </row>
     <row r="574" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A574" s="4"/>
       <c r="B574" s="6"/>
       <c r="C574" s="13"/>
-      <c r="D574" s="6"/>
+      <c r="D574" s="4"/>
       <c r="E574" s="4"/>
-      <c r="F574" s="6"/>
+      <c r="F574" s="5"/>
     </row>
     <row r="575" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A575" s="4"/>
       <c r="B575" s="6"/>
       <c r="C575" s="13"/>
-      <c r="D575" s="6"/>
+      <c r="D575" s="4"/>
       <c r="E575" s="4"/>
-      <c r="F575" s="6"/>
+      <c r="F575" s="5"/>
     </row>
     <row r="576" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A576" s="4"/>
       <c r="B576" s="6"/>
       <c r="C576" s="13"/>
-      <c r="D576" s="6"/>
+      <c r="D576" s="4"/>
       <c r="E576" s="4"/>
-      <c r="F576" s="6"/>
+      <c r="F576" s="5"/>
     </row>
     <row r="577" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A577" s="4"/>
       <c r="B577" s="6"/>
       <c r="C577" s="13"/>
-      <c r="D577" s="6"/>
+      <c r="D577" s="4"/>
       <c r="E577" s="4"/>
-      <c r="F577" s="6"/>
+      <c r="F577" s="5"/>
     </row>
     <row r="578" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A578" s="4"/>
       <c r="B578" s="6"/>
       <c r="C578" s="13"/>
-      <c r="D578" s="6"/>
+      <c r="D578" s="4"/>
       <c r="E578" s="4"/>
-      <c r="F578" s="6"/>
+      <c r="F578" s="5"/>
     </row>
     <row r="579" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A579" s="4"/>
       <c r="B579" s="6"/>
       <c r="C579" s="13"/>
-      <c r="D579" s="6"/>
+      <c r="D579" s="4"/>
       <c r="E579" s="4"/>
-      <c r="F579" s="6"/>
+      <c r="F579" s="5"/>
     </row>
     <row r="580" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A580" s="4"/>
       <c r="B580" s="6"/>
       <c r="C580" s="13"/>
-      <c r="D580" s="6"/>
+      <c r="D580" s="4"/>
       <c r="E580" s="4"/>
-      <c r="F580" s="6"/>
+      <c r="F580" s="5"/>
     </row>
     <row r="581" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A581" s="4"/>
       <c r="B581" s="6"/>
       <c r="C581" s="13"/>
-      <c r="D581" s="6"/>
+      <c r="D581" s="4"/>
       <c r="E581" s="4"/>
-      <c r="F581" s="6"/>
+      <c r="F581" s="5"/>
     </row>
     <row r="582" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A582" s="4"/>
       <c r="B582" s="6"/>
       <c r="C582" s="13"/>
-      <c r="D582" s="6"/>
+      <c r="D582" s="4"/>
       <c r="E582" s="4"/>
-      <c r="F582" s="6"/>
+      <c r="F582" s="5"/>
     </row>
     <row r="583" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A583" s="4"/>
       <c r="B583" s="6"/>
       <c r="C583" s="13"/>
-      <c r="D583" s="6"/>
+      <c r="D583" s="4"/>
       <c r="E583" s="4"/>
-      <c r="F583" s="6"/>
+      <c r="F583" s="5"/>
     </row>
     <row r="584" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A584" s="4"/>
       <c r="B584" s="6"/>
       <c r="C584" s="13"/>
-      <c r="D584" s="6"/>
+      <c r="D584" s="4"/>
       <c r="E584" s="4"/>
-      <c r="F584" s="6"/>
+      <c r="F584" s="5"/>
     </row>
     <row r="585" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A585" s="4"/>
       <c r="B585" s="6"/>
       <c r="C585" s="13"/>
-      <c r="D585" s="6"/>
+      <c r="D585" s="4"/>
       <c r="E585" s="4"/>
-      <c r="F585" s="6"/>
+      <c r="F585" s="5"/>
     </row>
     <row r="586" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A586" s="4"/>
       <c r="B586" s="6"/>
       <c r="C586" s="13"/>
-      <c r="D586" s="6"/>
+      <c r="D586" s="4"/>
       <c r="E586" s="4"/>
-      <c r="F586" s="6"/>
+      <c r="F586" s="5"/>
     </row>
     <row r="587" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A587" s="4"/>
       <c r="B587" s="6"/>
       <c r="C587" s="13"/>
-      <c r="D587" s="6"/>
+      <c r="D587" s="4"/>
       <c r="E587" s="4"/>
-      <c r="F587" s="6"/>
+      <c r="F587" s="5"/>
     </row>
     <row r="588" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A588" s="4"/>
       <c r="B588" s="6"/>
       <c r="C588" s="13"/>
-      <c r="D588" s="6"/>
+      <c r="D588" s="4"/>
       <c r="E588" s="4"/>
-      <c r="F588" s="6"/>
+      <c r="F588" s="5"/>
     </row>
     <row r="589" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A589" s="4"/>
       <c r="B589" s="6"/>
       <c r="C589" s="13"/>
-      <c r="D589" s="6"/>
+      <c r="D589" s="4"/>
       <c r="E589" s="4"/>
-      <c r="F589" s="6"/>
+      <c r="F589" s="5"/>
     </row>
     <row r="590" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A590" s="4"/>
       <c r="B590" s="6"/>
       <c r="C590" s="13"/>
-      <c r="D590" s="6"/>
+      <c r="D590" s="4"/>
       <c r="E590" s="4"/>
-      <c r="F590" s="6"/>
+      <c r="F590" s="5"/>
     </row>
     <row r="591" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A591" s="4"/>
       <c r="B591" s="6"/>
       <c r="C591" s="13"/>
-      <c r="D591" s="6"/>
+      <c r="D591" s="4"/>
       <c r="E591" s="4"/>
-      <c r="F591" s="6"/>
+      <c r="F591" s="5"/>
     </row>
     <row r="592" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A592" s="4"/>
       <c r="B592" s="6"/>
       <c r="C592" s="13"/>
-      <c r="D592" s="6"/>
+      <c r="D592" s="4"/>
       <c r="E592" s="4"/>
-      <c r="F592" s="6"/>
+      <c r="F592" s="5"/>
     </row>
     <row r="593" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A593" s="4"/>
       <c r="B593" s="6"/>
       <c r="C593" s="13"/>
-      <c r="D593" s="6"/>
+      <c r="D593" s="4"/>
       <c r="E593" s="4"/>
-      <c r="F593" s="6"/>
+      <c r="F593" s="5"/>
     </row>
     <row r="594" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A594" s="4"/>
       <c r="B594" s="6"/>
       <c r="C594" s="13"/>
-      <c r="D594" s="6"/>
+      <c r="D594" s="4"/>
       <c r="E594" s="4"/>
-      <c r="F594" s="6"/>
+      <c r="F594" s="5"/>
     </row>
     <row r="595" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A595" s="4"/>
       <c r="B595" s="6"/>
       <c r="C595" s="13"/>
-      <c r="D595" s="6"/>
+      <c r="D595" s="4"/>
       <c r="E595" s="4"/>
-      <c r="F595" s="6"/>
+      <c r="F595" s="5"/>
     </row>
     <row r="596" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A596" s="4"/>
       <c r="B596" s="6"/>
       <c r="C596" s="13"/>
-      <c r="D596" s="6"/>
+      <c r="D596" s="4"/>
       <c r="E596" s="4"/>
-      <c r="F596" s="6"/>
+      <c r="F596" s="5"/>
     </row>
     <row r="597" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A597" s="4"/>
       <c r="B597" s="6"/>
       <c r="C597" s="13"/>
-      <c r="D597" s="6"/>
+      <c r="D597" s="4"/>
       <c r="E597" s="4"/>
-      <c r="F597" s="6"/>
+      <c r="F597" s="5"/>
     </row>
     <row r="598" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A598" s="4"/>
       <c r="B598" s="6"/>
       <c r="C598" s="13"/>
-      <c r="D598" s="6"/>
+      <c r="D598" s="4"/>
       <c r="E598" s="4"/>
-      <c r="F598" s="6"/>
+      <c r="F598" s="5"/>
     </row>
     <row r="599" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A599" s="4"/>
       <c r="B599" s="6"/>
       <c r="C599" s="13"/>
-      <c r="D599" s="6"/>
+      <c r="D599" s="4"/>
       <c r="E599" s="4"/>
-      <c r="F599" s="6"/>
+      <c r="F599" s="5"/>
     </row>
     <row r="600" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A600" s="4"/>
       <c r="B600" s="6"/>
       <c r="C600" s="13"/>
-      <c r="D600" s="6"/>
+      <c r="D600" s="4"/>
       <c r="E600" s="4"/>
-      <c r="F600" s="6"/>
+      <c r="F600" s="5"/>
     </row>
     <row r="601" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A601" s="4"/>
       <c r="B601" s="6"/>
       <c r="C601" s="13"/>
-      <c r="D601" s="6"/>
+      <c r="D601" s="4"/>
       <c r="E601" s="4"/>
-      <c r="F601" s="6"/>
+      <c r="F601" s="5"/>
     </row>
     <row r="602" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A602" s="4"/>
       <c r="B602" s="6"/>
       <c r="C602" s="13"/>
-      <c r="D602" s="6"/>
+      <c r="D602" s="4"/>
       <c r="E602" s="4"/>
-      <c r="F602" s="6"/>
+      <c r="F602" s="5"/>
     </row>
     <row r="603" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A603" s="4"/>
       <c r="B603" s="6"/>
       <c r="C603" s="13"/>
-      <c r="D603" s="6"/>
+      <c r="D603" s="4"/>
       <c r="E603" s="4"/>
-      <c r="F603" s="6"/>
+      <c r="F603" s="5"/>
     </row>
     <row r="604" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A604" s="4"/>
       <c r="B604" s="6"/>
       <c r="C604" s="13"/>
-      <c r="D604" s="6"/>
+      <c r="D604" s="4"/>
       <c r="E604" s="4"/>
-      <c r="F604" s="6"/>
+      <c r="F604" s="5"/>
     </row>
     <row r="605" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A605" s="4"/>
       <c r="B605" s="6"/>
       <c r="C605" s="13"/>
-      <c r="D605" s="6"/>
+      <c r="D605" s="4"/>
       <c r="E605" s="4"/>
-      <c r="F605" s="6"/>
+      <c r="F605" s="5"/>
     </row>
     <row r="606" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A606" s="4"/>
       <c r="B606" s="6"/>
       <c r="C606" s="13"/>
-      <c r="D606" s="6"/>
+      <c r="D606" s="4"/>
       <c r="E606" s="4"/>
-      <c r="F606" s="6"/>
+      <c r="F606" s="5"/>
     </row>
     <row r="607" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A607" s="4"/>
       <c r="B607" s="6"/>
       <c r="C607" s="13"/>
-      <c r="D607" s="6"/>
+      <c r="D607" s="4"/>
       <c r="E607" s="4"/>
-      <c r="F607" s="6"/>
+      <c r="F607" s="5"/>
     </row>
     <row r="608" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A608" s="4"/>
       <c r="B608" s="6"/>
       <c r="C608" s="13"/>
-      <c r="D608" s="6"/>
+      <c r="D608" s="4"/>
       <c r="E608" s="4"/>
-      <c r="F608" s="6"/>
+      <c r="F608" s="5"/>
     </row>
     <row r="609" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A609" s="4"/>
       <c r="B609" s="6"/>
       <c r="C609" s="13"/>
-      <c r="D609" s="6"/>
+      <c r="D609" s="4"/>
       <c r="E609" s="4"/>
-      <c r="F609" s="6"/>
+      <c r="F609" s="5"/>
     </row>
     <row r="610" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A610" s="4"/>
       <c r="B610" s="6"/>
       <c r="C610" s="13"/>
-      <c r="D610" s="6"/>
+      <c r="D610" s="4"/>
       <c r="E610" s="4"/>
-      <c r="F610" s="6"/>
+      <c r="F610" s="5"/>
     </row>
     <row r="611" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A611" s="4"/>
       <c r="B611" s="6"/>
       <c r="C611" s="13"/>
-      <c r="D611" s="6"/>
+      <c r="D611" s="4"/>
       <c r="E611" s="4"/>
-      <c r="F611" s="6"/>
+      <c r="F611" s="5"/>
     </row>
     <row r="612" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A612" s="4"/>
       <c r="B612" s="6"/>
       <c r="C612" s="13"/>
-      <c r="D612" s="6"/>
+      <c r="D612" s="4"/>
       <c r="E612" s="4"/>
-      <c r="F612" s="6"/>
+      <c r="F612" s="5"/>
     </row>
     <row r="613" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A613" s="4"/>
       <c r="B613" s="6"/>
       <c r="C613" s="13"/>
-      <c r="D613" s="6"/>
+      <c r="D613" s="4"/>
       <c r="E613" s="4"/>
-      <c r="F613" s="6"/>
+      <c r="F613" s="5"/>
     </row>
     <row r="614" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A614" s="4"/>
       <c r="B614" s="6"/>
       <c r="C614" s="13"/>
-      <c r="D614" s="6"/>
+      <c r="D614" s="4"/>
       <c r="E614" s="4"/>
-      <c r="F614" s="6"/>
+      <c r="F614" s="5"/>
     </row>
     <row r="615" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A615" s="4"/>
       <c r="B615" s="6"/>
       <c r="C615" s="13"/>
-      <c r="D615" s="6"/>
+      <c r="D615" s="4"/>
       <c r="E615" s="4"/>
-      <c r="F615" s="6"/>
+      <c r="F615" s="5"/>
     </row>
     <row r="616" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A616" s="4"/>
       <c r="B616" s="6"/>
       <c r="C616" s="13"/>
-      <c r="D616" s="6"/>
+      <c r="D616" s="4"/>
       <c r="E616" s="4"/>
-      <c r="F616" s="6"/>
+      <c r="F616" s="5"/>
+    </row>
+    <row r="617" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A617" s="4"/>
+      <c r="B617" s="6"/>
+      <c r="C617" s="13"/>
+      <c r="D617" s="4"/>
+      <c r="E617" s="4"/>
+      <c r="F617" s="5"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:G204"/>
-  <mergeCells count="48">
+  <mergeCells count="55">
+    <mergeCell ref="D251:D253"/>
+    <mergeCell ref="D254:D256"/>
+    <mergeCell ref="D239:D243"/>
+    <mergeCell ref="D244:D247"/>
+    <mergeCell ref="D227:D229"/>
+    <mergeCell ref="D230:D232"/>
+    <mergeCell ref="D216:D220"/>
+    <mergeCell ref="D221:D226"/>
+    <mergeCell ref="D233:D238"/>
+    <mergeCell ref="D210:D212"/>
+    <mergeCell ref="D205:D209"/>
+    <mergeCell ref="D59:D61"/>
+    <mergeCell ref="D108:D110"/>
+    <mergeCell ref="D96:D98"/>
+    <mergeCell ref="D193:D194"/>
+    <mergeCell ref="D195:D199"/>
+    <mergeCell ref="D63:D68"/>
+    <mergeCell ref="D160:D165"/>
+    <mergeCell ref="D166:D168"/>
+    <mergeCell ref="D136:D145"/>
+    <mergeCell ref="D146:D147"/>
+    <mergeCell ref="D149:D157"/>
+    <mergeCell ref="D158:D159"/>
+    <mergeCell ref="D111:D120"/>
+    <mergeCell ref="D121:D125"/>
+    <mergeCell ref="D180:D182"/>
+    <mergeCell ref="D75:D76"/>
+    <mergeCell ref="D69:D71"/>
+    <mergeCell ref="D2:D6"/>
+    <mergeCell ref="D7:D11"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="D15:D19"/>
+    <mergeCell ref="D20:D23"/>
+    <mergeCell ref="D72:D74"/>
+    <mergeCell ref="D31:D33"/>
+    <mergeCell ref="D36:D41"/>
+    <mergeCell ref="D44:D49"/>
+    <mergeCell ref="D50:D51"/>
+    <mergeCell ref="D54:D58"/>
     <mergeCell ref="D202:D204"/>
     <mergeCell ref="D183:D185"/>
     <mergeCell ref="D186:D191"/>
@@ -8232,39 +8681,7 @@
     <mergeCell ref="D174:D176"/>
     <mergeCell ref="D200:D201"/>
     <mergeCell ref="D92:D95"/>
-    <mergeCell ref="D180:D182"/>
-    <mergeCell ref="D2:D6"/>
-    <mergeCell ref="D7:D11"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="D15:D19"/>
-    <mergeCell ref="D20:D23"/>
-    <mergeCell ref="D111:D120"/>
-    <mergeCell ref="D121:D125"/>
     <mergeCell ref="D126:D127"/>
-    <mergeCell ref="D72:D74"/>
-    <mergeCell ref="D31:D33"/>
-    <mergeCell ref="D36:D41"/>
-    <mergeCell ref="D44:D49"/>
-    <mergeCell ref="D50:D51"/>
-    <mergeCell ref="D54:D58"/>
-    <mergeCell ref="D75:D76"/>
-    <mergeCell ref="D69:D71"/>
-    <mergeCell ref="D216:D220"/>
-    <mergeCell ref="D221:D226"/>
-    <mergeCell ref="D210:D212"/>
-    <mergeCell ref="D205:D209"/>
-    <mergeCell ref="D59:D61"/>
-    <mergeCell ref="D108:D110"/>
-    <mergeCell ref="D96:D98"/>
-    <mergeCell ref="D193:D194"/>
-    <mergeCell ref="D195:D199"/>
-    <mergeCell ref="D63:D68"/>
-    <mergeCell ref="D160:D165"/>
-    <mergeCell ref="D166:D168"/>
-    <mergeCell ref="D136:D145"/>
-    <mergeCell ref="D146:D147"/>
-    <mergeCell ref="D149:D157"/>
-    <mergeCell ref="D158:D159"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
